--- a/Excel/SceneConfig.xlsx
+++ b/Excel/SceneConfig.xlsx
@@ -1,46 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6567A5D2-B78C-4CAE-80A5-0FCD6CFFE185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SceneProto" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>作者</author>
     <author>Administrator</author>
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="N3" authorId="0">
+    <comment ref="O3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>作者:</t>
@@ -49,6 +43,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -58,13 +53,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="O3" authorId="1">
+    <comment ref="P3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -73,6 +69,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -81,13 +78,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="P3" authorId="2">
+    <comment ref="Q3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>admin:</t>
@@ -96,6 +94,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -106,13 +105,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q3" authorId="1">
+    <comment ref="R3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -121,6 +121,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -129,13 +130,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="W3" authorId="0">
+    <comment ref="X3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>作者:</t>
@@ -144,6 +146,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -153,13 +156,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="X3" authorId="2">
+    <comment ref="Y3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>admin:</t>
@@ -168,6 +172,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -176,13 +181,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="AG3" authorId="0">
+    <comment ref="AI3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>作者:</t>
@@ -191,6 +197,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -198,13 +205,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="J4" authorId="0">
+    <comment ref="K4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>public const int NONE = 0;
@@ -237,13 +245,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="M4" authorId="0">
+    <comment ref="N4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>作者:</t>
@@ -252,6 +261,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -265,18 +275,18 @@
 </file>
 
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
-<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <connection id="1" name="Item_Template" type="4" background="1" refreshedVersion="2" saveData="1">
-    <webPr parsePre="1" consecutive="1" xl2000="1" sourceData="1" xml="1" url="D:\SVN_Work\S_数据表\XML映射模版\Item_Template.xml" htmlFormat="all" htmlTables="1"/>
+<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
+  <connection id="1" xr16:uid="{00000000-0015-0000-FFFF-FFFF00000000}" name="Item_Template" type="4" refreshedVersion="2" background="1" saveData="1">
+    <webPr xml="1" sourceData="1" parsePre="1" consecutive="1" xl2000="1" url="D:\SVN_Work\S_数据表\XML映射模版\Item_Template.xml" htmlTables="1" htmlFormat="all"/>
   </connection>
-  <connection id="2" name="Item_Template1" type="4" background="1" refreshedVersion="2" saveData="1">
-    <webPr parsePre="1" consecutive="1" xl2000="1" sourceData="1" xml="1" url="D:\SVN_Work\S_数据表\XML映射模版\Item_Template.xml" htmlFormat="all" htmlTables="1"/>
+  <connection id="2" xr16:uid="{00000000-0015-0000-FFFF-FFFF01000000}" name="Item_Template1" type="4" refreshedVersion="2" background="1" saveData="1">
+    <webPr xml="1" sourceData="1" parsePre="1" consecutive="1" xl2000="1" url="D:\SVN_Work\S_数据表\XML映射模版\Item_Template.xml" htmlTables="1" htmlFormat="all"/>
   </connection>
 </connections>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="220">
   <si>
     <t>c</t>
   </si>
@@ -700,6 +710,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>4,100,4,</t>
@@ -709,6 +720,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>40</t>
@@ -718,6 +730,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>,</t>
@@ -727,6 +740,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>30</t>
@@ -819,6 +833,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>战场(</t>
@@ -828,6 +843,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>1</t>
@@ -837,6 +853,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>0</t>
@@ -846,6 +863,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>-</t>
@@ -855,6 +873,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>29级)</t>
@@ -878,6 +897,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>战场(3</t>
@@ -887,6 +907,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>0-</t>
@@ -896,6 +917,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>60级</t>
@@ -905,6 +927,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>)</t>
@@ -955,18 +978,111 @@
   <si>
     <t>1V1挑战赛</t>
   </si>
+  <si>
+    <t>Name_EN</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>c</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Green Valley Village</t>
+  </si>
+  <si>
+    <t>Desert Domain</t>
+  </si>
+  <si>
+    <t>Frozen Land</t>
+  </si>
+  <si>
+    <t>Forest Nest</t>
+  </si>
+  <si>
+    <t>Ancient Ruins</t>
+  </si>
+  <si>
+    <t>Scorching Melted Flame</t>
+  </si>
+  <si>
+    <t>Treasure Land</t>
+  </si>
+  <si>
+    <t>Secret Realm</t>
+  </si>
+  <si>
+    <t>Challenging Land</t>
+  </si>
+  <si>
+    <t>Family Championship Map</t>
+  </si>
+  <si>
+    <t>Family Map</t>
+  </si>
+  <si>
+    <t>Arena</t>
+  </si>
+  <si>
+    <t>My home</t>
+  </si>
+  <si>
+    <t>Pet ladder</t>
+  </si>
+  <si>
+    <t>Pet Leveling Area</t>
+  </si>
+  <si>
+    <t>Random Encounter</t>
+  </si>
+  <si>
+    <t>Battlefield (Level 10 - 29)</t>
+  </si>
+  <si>
+    <t>Battlefield (30-60 levels)</t>
+  </si>
+  <si>
+    <t>Trial Grounds</t>
+  </si>
+  <si>
+    <t>Warrior Battle</t>
+  </si>
+  <si>
+    <t>Animal Running Competition</t>
+  </si>
+  <si>
+    <t>Demon Activity Map</t>
+  </si>
+  <si>
+    <t>Seal Tower</t>
+  </si>
+  <si>
+    <t>A Gift from Heaven</t>
+  </si>
+  <si>
+    <t>Pet Mine</t>
+  </si>
+  <si>
+    <t>Seasonal Tower</t>
+  </si>
+  <si>
+    <t>1v1 Challenge</t>
+  </si>
+  <si>
+    <t>Main City</t>
+  </si>
+  <si>
+    <t>ChapterDes_EN</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>In people's eyes, there is something very mysterious in this area. Dear adventurer, are you ready to start the exploration?</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="27">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -978,6 +1094,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -985,6 +1102,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -993,12 +1111,14 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="0"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1006,165 +1126,31 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="37">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1191,198 +1177,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.149540696432386"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="0" tint="-0.14951017792291024"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -1455,256 +1255,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="52">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1765,80 +1323,36 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="49" fontId="1" fillId="5" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="52">
+  <cellStyles count="4">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 2" xfId="49"/>
-    <cellStyle name="常规 5" xfId="50"/>
-    <cellStyle name="常规 6" xfId="51"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="常规 5" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
+    <cellStyle name="常规 6" xfId="3" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1875,17 +1389,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="C4:J6" totalsRowShown="0">
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="C4:J6" etc:filterBottomFollowUsedRange="0"/>
-  <tableColumns count="8">
-    <tableColumn id="1" name="Id"/>
-    <tableColumn id="2" name="Name"/>
-    <tableColumn id="3" name="Icon"/>
-    <tableColumn id="9" name="Icon2"/>
-    <tableColumn id="4" name="StallArea"/>
-    <tableColumn id="5" name="InitPos"/>
-    <tableColumn id="6" name="NpcList"/>
-    <tableColumn id="7" name="MapType"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="表1" displayName="表1" ref="C4:K6" totalsRowShown="0">
+  <autoFilter ref="C4:K6" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Name"/>
+    <tableColumn id="8" xr3:uid="{41F534E2-D6EA-4B79-ACD6-FD4565BD72AE}" name="Name_EN"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Icon"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Icon2"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="StallArea"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="InitPos"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="NpcList"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="MapType"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2172,45 +1687,51 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="C2:AG36"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B2:AI36"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="3" max="3" width="17.5" customWidth="1"/>
-    <col min="4" max="4" width="16.125" customWidth="1"/>
-    <col min="5" max="6" width="17.125" customWidth="1"/>
-    <col min="7" max="7" width="16.75" customWidth="1"/>
-    <col min="8" max="8" width="13.25" customWidth="1"/>
-    <col min="9" max="9" width="31.625" customWidth="1"/>
-    <col min="10" max="10" width="28.125" customWidth="1"/>
-    <col min="11" max="12" width="16.75" customWidth="1"/>
-    <col min="14" max="14" width="13.875" customWidth="1"/>
-    <col min="16" max="16" width="14.875" customWidth="1"/>
-    <col min="17" max="17" width="18.625" customWidth="1"/>
-    <col min="18" max="18" width="10.25" customWidth="1"/>
-    <col min="20" max="20" width="13.125" customWidth="1"/>
-    <col min="21" max="22" width="9" customWidth="1"/>
-    <col min="23" max="24" width="11.375" customWidth="1"/>
-    <col min="25" max="25" width="13.75" customWidth="1"/>
-    <col min="26" max="27" width="22" customWidth="1"/>
-    <col min="28" max="28" width="17.375" customWidth="1"/>
-    <col min="29" max="29" width="16.375" customWidth="1"/>
-    <col min="30" max="30" width="18" customWidth="1"/>
-    <col min="32" max="32" width="9.375" customWidth="1"/>
-    <col min="33" max="33" width="14.125" customWidth="1"/>
+    <col min="4" max="5" width="16.125" customWidth="1"/>
+    <col min="6" max="7" width="17.125" customWidth="1"/>
+    <col min="8" max="8" width="16.75" customWidth="1"/>
+    <col min="9" max="9" width="13.25" customWidth="1"/>
+    <col min="10" max="10" width="31.625" customWidth="1"/>
+    <col min="11" max="11" width="28.125" customWidth="1"/>
+    <col min="12" max="13" width="16.75" customWidth="1"/>
+    <col min="15" max="15" width="13.875" customWidth="1"/>
+    <col min="17" max="17" width="14.875" customWidth="1"/>
+    <col min="18" max="18" width="18.625" customWidth="1"/>
+    <col min="19" max="19" width="10.25" customWidth="1"/>
+    <col min="21" max="21" width="13.125" customWidth="1"/>
+    <col min="22" max="23" width="9" customWidth="1"/>
+    <col min="24" max="25" width="11.375" customWidth="1"/>
+    <col min="26" max="26" width="13.75" customWidth="1"/>
+    <col min="27" max="28" width="22" customWidth="1"/>
+    <col min="29" max="30" width="17.375" customWidth="1"/>
+    <col min="31" max="31" width="16.375" customWidth="1"/>
+    <col min="32" max="32" width="18" customWidth="1"/>
+    <col min="34" max="34" width="9.375" customWidth="1"/>
+    <col min="35" max="35" width="14.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="6:6">
-      <c r="F2" s="4" t="s">
-        <v>0</v>
+    <row r="2" spans="2:35" x14ac:dyDescent="0.15">
+      <c r="E2" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="4" t="s">
+        <v>189</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:33">
+    <row r="3" spans="2:35" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C3" s="5" t="s">
         <v>1</v>
       </c>
@@ -2218,189 +1739,201 @@
         <v>2</v>
       </c>
       <c r="E3" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="H3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="I3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="J3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="K3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="L3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="M3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="N3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="O3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="O3" s="6" t="s">
+      <c r="P3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="P3" s="6" t="s">
+      <c r="Q3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="Q3" s="6" t="s">
+      <c r="R3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="R3" s="6" t="s">
+      <c r="S3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="6" t="s">
+      <c r="T3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="T3" s="6" t="s">
+      <c r="U3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="U3" s="6" t="s">
+      <c r="V3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="V3" s="6" t="s">
+      <c r="W3" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="W3" s="6" t="s">
+      <c r="X3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="X3" s="6" t="s">
+      <c r="Y3" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="Y3" s="6" t="s">
+      <c r="Z3" s="6" t="s">
         <v>23</v>
-      </c>
-      <c r="Z3" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="AA3" s="6" t="s">
         <v>24</v>
       </c>
       <c r="AB3" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC3" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="AC3" s="6" t="s">
+      <c r="AD3" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE3" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="AD3" s="6" t="s">
+      <c r="AF3" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="AE3" s="6" t="s">
+      <c r="AG3" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="AF3" s="6" t="s">
+      <c r="AH3" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="AG3" s="6" t="s">
+      <c r="AI3" s="6" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:33">
+    <row r="4" spans="2:35" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="F4" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="G4" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="H4" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="I4" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="J4" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="K4" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="L4" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="M4" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="M4" s="6" t="s">
+      <c r="N4" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="N4" s="6" t="s">
+      <c r="O4" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="O4" s="6" t="s">
+      <c r="P4" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="P4" s="6" t="s">
+      <c r="Q4" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="Q4" s="6" t="s">
+      <c r="R4" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="R4" s="6" t="s">
+      <c r="S4" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="S4" s="6" t="s">
+      <c r="T4" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="T4" s="6" t="s">
+      <c r="U4" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="U4" s="6" t="s">
+      <c r="V4" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="V4" s="6" t="s">
+      <c r="W4" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="W4" s="6" t="s">
+      <c r="X4" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="X4" s="6" t="s">
+      <c r="Y4" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="Y4" s="6" t="s">
+      <c r="Z4" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="Z4" s="6" t="s">
+      <c r="AA4" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="AA4" s="6" t="s">
+      <c r="AB4" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="AB4" s="6" t="s">
+      <c r="AC4" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="AC4" s="6" t="s">
+      <c r="AD4" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="AE4" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="AD4" s="6" t="s">
+      <c r="AF4" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="AE4" s="6" t="s">
+      <c r="AG4" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="AF4" s="6" t="s">
+      <c r="AH4" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="AG4" s="6" t="s">
+      <c r="AI4" s="6" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:33">
+    <row r="5" spans="2:35" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C5" s="6" t="s">
         <v>61</v>
       </c>
@@ -2410,29 +1943,29 @@
       <c r="E5" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="6" t="s">
         <v>62</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J5" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="K5" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="K5" s="6" t="s">
+      <c r="L5" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="M5" s="6" t="s">
         <v>62</v>
-      </c>
-      <c r="M5" s="6" t="s">
-        <v>61</v>
       </c>
       <c r="N5" s="6" t="s">
         <v>61</v>
@@ -2447,19 +1980,19 @@
         <v>61</v>
       </c>
       <c r="R5" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="S5" s="6" t="s">
         <v>62</v>
-      </c>
-      <c r="S5" s="6" t="s">
-        <v>61</v>
       </c>
       <c r="T5" s="6" t="s">
         <v>61</v>
       </c>
       <c r="U5" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="V5" s="6" t="s">
         <v>63</v>
-      </c>
-      <c r="V5" s="6" t="s">
-        <v>61</v>
       </c>
       <c r="W5" s="6" t="s">
         <v>61</v>
@@ -2471,62 +2004,69 @@
         <v>61</v>
       </c>
       <c r="Z5" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA5" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="AA5" s="6" t="s">
+      <c r="AB5" s="6" t="s">
         <v>63</v>
-      </c>
-      <c r="AB5" s="6" t="s">
-        <v>62</v>
       </c>
       <c r="AC5" s="6" t="s">
         <v>62</v>
       </c>
       <c r="AD5" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AE5" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AF5" s="6" t="s">
         <v>61</v>
       </c>
       <c r="AG5" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH5" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI5" s="6" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:33">
+    <row r="6" spans="2:35" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B6"/>
       <c r="C6" s="8">
         <v>101</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="E6" s="9"/>
+      <c r="E6" s="9" t="s">
+        <v>217</v>
+      </c>
       <c r="F6" s="9"/>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="9"/>
+      <c r="H6" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="H6" s="22" t="s">
+      <c r="I6" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="J6" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="J6" s="9" t="s">
+      <c r="K6" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="K6" s="13">
+      <c r="L6" s="13">
         <v>101</v>
       </c>
-      <c r="L6" s="13">
-        <v>0</v>
-      </c>
       <c r="M6" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6" s="13">
         <v>0</v>
@@ -2535,21 +2075,21 @@
         <v>0</v>
       </c>
       <c r="Q6" s="13">
-        <v>1</v>
-      </c>
-      <c r="R6" s="9"/>
-      <c r="S6" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="R6" s="13">
+        <v>1</v>
+      </c>
+      <c r="S6" s="9"/>
+      <c r="T6" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="T6" s="13">
-        <v>0</v>
-      </c>
-      <c r="U6" s="9" t="s">
+      <c r="U6" s="13">
+        <v>0</v>
+      </c>
+      <c r="V6" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="V6" s="13">
-        <v>0</v>
-      </c>
       <c r="W6" s="13">
         <v>0</v>
       </c>
@@ -2559,24 +2099,29 @@
       <c r="Y6" s="13">
         <v>0</v>
       </c>
-      <c r="Z6" s="9"/>
+      <c r="Z6" s="13">
+        <v>0</v>
+      </c>
       <c r="AA6" s="9"/>
       <c r="AB6" s="9"/>
       <c r="AC6" s="9"/>
-      <c r="AD6" s="13">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="13">
-        <v>0</v>
-      </c>
+      <c r="AD6" s="9"/>
+      <c r="AE6" s="9"/>
       <c r="AF6" s="13">
         <v>0</v>
       </c>
-      <c r="AG6" s="20" t="s">
+      <c r="AG6" s="13">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="13">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="20" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="7" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:33">
+    <row r="7" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B7"/>
       <c r="C7" s="8">
         <v>110001</v>
       </c>
@@ -2584,30 +2129,30 @@
         <v>73</v>
       </c>
       <c r="E7" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="F7" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="G7" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="G7" s="9"/>
-      <c r="H7" s="22" t="s">
+      <c r="H7" s="9"/>
+      <c r="I7" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="I7" s="14"/>
-      <c r="J7" s="15">
+      <c r="J7" s="14"/>
+      <c r="K7" s="15">
         <v>5</v>
       </c>
-      <c r="K7" s="8">
+      <c r="L7" s="8">
         <v>100101</v>
       </c>
-      <c r="L7" s="16" t="s">
+      <c r="M7" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="M7" s="13">
-        <v>1</v>
-      </c>
       <c r="N7" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" s="13">
         <v>0</v>
@@ -2618,52 +2163,59 @@
       <c r="Q7" s="13">
         <v>0</v>
       </c>
-      <c r="R7" s="9" t="s">
+      <c r="R7" s="13">
+        <v>0</v>
+      </c>
+      <c r="S7" s="9" t="s">
         <v>78</v>
-      </c>
-      <c r="S7" s="9" t="s">
-        <v>79</v>
       </c>
       <c r="T7" s="9" t="s">
         <v>79</v>
       </c>
       <c r="U7" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="V7" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="V7" s="13">
+      <c r="W7" s="13">
         <v>2</v>
       </c>
-      <c r="W7" s="13">
-        <v>0</v>
-      </c>
       <c r="X7" s="13">
         <v>0</v>
       </c>
       <c r="Y7" s="13">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="13">
         <v>72001013</v>
       </c>
-      <c r="Z7" s="22" t="s">
+      <c r="AA7" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="AA7" s="9"/>
-      <c r="AB7" s="9" t="s">
+      <c r="AB7" s="9"/>
+      <c r="AC7" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="AC7" s="9"/>
-      <c r="AD7" s="13">
+      <c r="AD7" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="AE7" s="9"/>
+      <c r="AF7" s="13">
         <v>28000</v>
       </c>
-      <c r="AE7" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF7" s="13">
+      <c r="AG7" s="13">
+        <v>0</v>
+      </c>
+      <c r="AH7" s="13">
         <v>601500201</v>
       </c>
-      <c r="AG7" s="20" t="s">
+      <c r="AI7" s="20" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="8" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:33">
+    <row r="8" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B8"/>
       <c r="C8" s="8">
         <v>110002</v>
       </c>
@@ -2671,30 +2223,30 @@
         <v>84</v>
       </c>
       <c r="E8" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="F8" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="G8" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="G8" s="9"/>
-      <c r="H8" s="22" t="s">
+      <c r="H8" s="9"/>
+      <c r="I8" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8">
+      <c r="J8" s="8"/>
+      <c r="K8" s="8">
         <v>5</v>
       </c>
-      <c r="K8" s="8">
+      <c r="L8" s="8">
         <v>1000002</v>
       </c>
-      <c r="L8" s="13" t="s">
+      <c r="M8" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="M8" s="13">
-        <v>1</v>
-      </c>
       <c r="N8" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" s="13">
         <v>0</v>
@@ -2705,52 +2257,59 @@
       <c r="Q8" s="13">
         <v>0</v>
       </c>
-      <c r="R8" s="9" t="s">
+      <c r="R8" s="13">
+        <v>0</v>
+      </c>
+      <c r="S8" s="9" t="s">
         <v>89</v>
-      </c>
-      <c r="S8" s="9" t="s">
-        <v>90</v>
       </c>
       <c r="T8" s="9" t="s">
         <v>90</v>
       </c>
       <c r="U8" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="V8" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="V8" s="13">
+      <c r="W8" s="13">
         <v>2</v>
       </c>
-      <c r="W8" s="13">
-        <v>0</v>
-      </c>
       <c r="X8" s="13">
         <v>0</v>
       </c>
       <c r="Y8" s="13">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="13">
         <v>72002013</v>
       </c>
-      <c r="Z8" s="22" t="s">
+      <c r="AA8" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="AA8" s="9"/>
-      <c r="AB8" s="9" t="s">
+      <c r="AB8" s="9"/>
+      <c r="AC8" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="AC8" s="9"/>
-      <c r="AD8" s="13">
+      <c r="AD8" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="AE8" s="9"/>
+      <c r="AF8" s="13">
         <v>58000</v>
       </c>
-      <c r="AE8" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF8" s="13">
+      <c r="AG8" s="13">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="13">
         <v>601500301</v>
       </c>
-      <c r="AG8" s="20" t="s">
+      <c r="AI8" s="20" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:33">
+    <row r="9" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B9"/>
       <c r="C9" s="8">
         <v>110003</v>
       </c>
@@ -2758,30 +2317,30 @@
         <v>94</v>
       </c>
       <c r="E9" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="F9" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="G9" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="G9" s="9"/>
-      <c r="H9" s="22" t="s">
+      <c r="H9" s="9"/>
+      <c r="I9" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8">
+      <c r="J9" s="8"/>
+      <c r="K9" s="8">
         <v>5</v>
       </c>
-      <c r="K9" s="8">
+      <c r="L9" s="8">
         <v>100102</v>
       </c>
-      <c r="L9" s="16" t="s">
+      <c r="M9" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="M9" s="13">
-        <v>1</v>
-      </c>
       <c r="N9" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" s="13">
         <v>0</v>
@@ -2792,52 +2351,59 @@
       <c r="Q9" s="13">
         <v>0</v>
       </c>
-      <c r="R9" s="9" t="s">
+      <c r="R9" s="13">
+        <v>0</v>
+      </c>
+      <c r="S9" s="9" t="s">
         <v>99</v>
-      </c>
-      <c r="S9" s="9" t="s">
-        <v>100</v>
       </c>
       <c r="T9" s="9" t="s">
         <v>100</v>
       </c>
       <c r="U9" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="V9" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="V9" s="13">
+      <c r="W9" s="13">
         <v>2</v>
       </c>
-      <c r="W9" s="13">
-        <v>0</v>
-      </c>
       <c r="X9" s="13">
         <v>0</v>
       </c>
       <c r="Y9" s="13">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="13">
         <v>72003013</v>
       </c>
-      <c r="Z9" s="22" t="s">
+      <c r="AA9" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="AA9" s="9"/>
-      <c r="AB9" s="9" t="s">
+      <c r="AB9" s="9"/>
+      <c r="AC9" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="AC9" s="9"/>
-      <c r="AD9" s="13">
+      <c r="AD9" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="AE9" s="9"/>
+      <c r="AF9" s="13">
         <v>88000</v>
       </c>
-      <c r="AE9" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF9" s="13">
+      <c r="AG9" s="13">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="13">
         <v>601500401</v>
       </c>
-      <c r="AG9" s="20" t="s">
+      <c r="AI9" s="20" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:33">
+    <row r="10" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B10"/>
       <c r="C10" s="8">
         <v>110004</v>
       </c>
@@ -2845,30 +2411,30 @@
         <v>104</v>
       </c>
       <c r="E10" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="F10" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="G10" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="G10" s="9"/>
-      <c r="H10" s="22" t="s">
+      <c r="H10" s="9"/>
+      <c r="I10" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="I10" s="14"/>
-      <c r="J10" s="15">
+      <c r="J10" s="14"/>
+      <c r="K10" s="15">
         <v>5</v>
       </c>
-      <c r="K10" s="8">
+      <c r="L10" s="8">
         <v>1000001</v>
       </c>
-      <c r="L10" s="16" t="s">
+      <c r="M10" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="M10" s="13">
-        <v>1</v>
-      </c>
       <c r="N10" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10" s="13">
         <v>0</v>
@@ -2879,52 +2445,59 @@
       <c r="Q10" s="13">
         <v>0</v>
       </c>
-      <c r="R10" s="9" t="s">
+      <c r="R10" s="13">
+        <v>0</v>
+      </c>
+      <c r="S10" s="9" t="s">
         <v>109</v>
-      </c>
-      <c r="S10" s="9" t="s">
-        <v>110</v>
       </c>
       <c r="T10" s="9" t="s">
         <v>110</v>
       </c>
       <c r="U10" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="V10" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="V10" s="13">
+      <c r="W10" s="13">
         <v>2</v>
       </c>
-      <c r="W10" s="13">
-        <v>0</v>
-      </c>
       <c r="X10" s="13">
         <v>0</v>
       </c>
       <c r="Y10" s="13">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="13">
         <v>72004013</v>
       </c>
-      <c r="Z10" s="22" t="s">
+      <c r="AA10" s="22" t="s">
         <v>112</v>
       </c>
-      <c r="AA10" s="9"/>
-      <c r="AB10" s="9" t="s">
+      <c r="AB10" s="9"/>
+      <c r="AC10" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="AC10" s="9"/>
-      <c r="AD10" s="13">
+      <c r="AD10" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="AE10" s="9"/>
+      <c r="AF10" s="13">
         <v>118000</v>
       </c>
-      <c r="AE10" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF10" s="13">
+      <c r="AG10" s="13">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="13">
         <v>601500501</v>
       </c>
-      <c r="AG10" s="20" t="s">
+      <c r="AI10" s="20" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="11" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:33">
+    <row r="11" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B11"/>
       <c r="C11" s="8">
         <v>110005</v>
       </c>
@@ -2932,30 +2505,30 @@
         <v>114</v>
       </c>
       <c r="E11" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="F11" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="G11" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="G11" s="9"/>
-      <c r="H11" s="22" t="s">
+      <c r="H11" s="9"/>
+      <c r="I11" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="I11" s="14"/>
-      <c r="J11" s="15">
+      <c r="J11" s="14"/>
+      <c r="K11" s="15">
         <v>5</v>
       </c>
-      <c r="K11" s="8">
+      <c r="L11" s="8">
         <v>2000007</v>
       </c>
-      <c r="L11" s="16" t="s">
+      <c r="M11" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="M11" s="13">
-        <v>1</v>
-      </c>
       <c r="N11" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" s="13">
         <v>0</v>
@@ -2966,52 +2539,59 @@
       <c r="Q11" s="13">
         <v>0</v>
       </c>
-      <c r="R11" s="9" t="s">
+      <c r="R11" s="13">
+        <v>0</v>
+      </c>
+      <c r="S11" s="9" t="s">
         <v>118</v>
-      </c>
-      <c r="S11" s="9" t="s">
-        <v>119</v>
       </c>
       <c r="T11" s="9" t="s">
         <v>119</v>
       </c>
       <c r="U11" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="V11" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="V11" s="13">
+      <c r="W11" s="13">
         <v>2</v>
       </c>
-      <c r="W11" s="13">
-        <v>0</v>
-      </c>
       <c r="X11" s="13">
         <v>0</v>
       </c>
       <c r="Y11" s="13">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="13">
         <v>72005013</v>
       </c>
-      <c r="Z11" s="9"/>
-      <c r="AA11" s="9" t="s">
+      <c r="AA11" s="9"/>
+      <c r="AB11" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="AB11" s="9" t="s">
+      <c r="AC11" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="AC11" s="9"/>
-      <c r="AD11" s="13">
+      <c r="AD11" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="AE11" s="9"/>
+      <c r="AF11" s="13">
         <v>158000</v>
       </c>
-      <c r="AE11" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF11" s="13">
+      <c r="AG11" s="13">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="13">
         <v>601500501</v>
       </c>
-      <c r="AG11" s="20" t="s">
+      <c r="AI11" s="20" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="12" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:33">
+    <row r="12" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B12"/>
       <c r="C12" s="8">
         <v>110006</v>
       </c>
@@ -3019,30 +2599,30 @@
         <v>123</v>
       </c>
       <c r="E12" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="F12" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="G12" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="G12" s="9"/>
-      <c r="H12" s="22" t="s">
+      <c r="H12" s="9"/>
+      <c r="I12" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="I12" s="14"/>
-      <c r="J12" s="15">
+      <c r="J12" s="14"/>
+      <c r="K12" s="15">
         <v>5</v>
       </c>
-      <c r="K12" s="8">
+      <c r="L12" s="8">
         <v>2000012</v>
       </c>
-      <c r="L12" s="16" t="s">
+      <c r="M12" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="M12" s="13">
-        <v>1</v>
-      </c>
       <c r="N12" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" s="13">
         <v>0</v>
@@ -3053,150 +2633,162 @@
       <c r="Q12" s="13">
         <v>0</v>
       </c>
-      <c r="R12" s="9" t="s">
+      <c r="R12" s="13">
+        <v>0</v>
+      </c>
+      <c r="S12" s="9" t="s">
         <v>118</v>
-      </c>
-      <c r="S12" s="9" t="s">
-        <v>127</v>
       </c>
       <c r="T12" s="9" t="s">
         <v>127</v>
       </c>
       <c r="U12" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="V12" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="V12" s="13">
+      <c r="W12" s="13">
         <v>2</v>
       </c>
-      <c r="W12" s="13">
-        <v>0</v>
-      </c>
       <c r="X12" s="13">
         <v>0</v>
       </c>
       <c r="Y12" s="13">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="13">
         <v>72006013</v>
       </c>
-      <c r="Z12" s="9"/>
-      <c r="AA12" s="9" t="s">
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="AB12" s="9" t="s">
+      <c r="AC12" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="AC12" s="9"/>
-      <c r="AD12" s="13">
+      <c r="AD12" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="13">
         <v>206000</v>
       </c>
-      <c r="AE12" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF12" s="13">
+      <c r="AG12" s="13">
+        <v>0</v>
+      </c>
+      <c r="AH12" s="13">
         <v>601500501</v>
       </c>
-      <c r="AG12" s="20" t="s">
+      <c r="AI12" s="20" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="13" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:33">
+    <row r="13" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B13"/>
       <c r="C13" s="8">
         <v>2000001</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="E13" s="9"/>
+      <c r="E13" s="9" t="s">
+        <v>196</v>
+      </c>
       <c r="F13" s="9"/>
       <c r="G13" s="9"/>
-      <c r="H13" s="22" t="s">
+      <c r="H13" s="9"/>
+      <c r="I13" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8">
+      <c r="J13" s="8"/>
+      <c r="K13" s="8">
         <v>7</v>
       </c>
-      <c r="K13" s="8">
+      <c r="L13" s="8">
         <v>2000001</v>
       </c>
-      <c r="L13" s="16" t="s">
+      <c r="M13" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="M13" s="13">
-        <v>1</v>
-      </c>
       <c r="N13" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P13" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q13" s="13">
-        <v>1</v>
-      </c>
-      <c r="R13" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="R13" s="13">
+        <v>1</v>
+      </c>
+      <c r="S13" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="S13" s="9" t="s">
+      <c r="T13" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="T13" s="13">
-        <v>1</v>
-      </c>
-      <c r="U13" s="9"/>
-      <c r="V13" s="13">
+      <c r="U13" s="13">
+        <v>1</v>
+      </c>
+      <c r="V13" s="9"/>
+      <c r="W13" s="13">
         <v>300</v>
       </c>
-      <c r="W13" s="13">
-        <v>0</v>
-      </c>
       <c r="X13" s="13">
         <v>0</v>
       </c>
-      <c r="Y13" s="13"/>
-      <c r="Z13" s="19" t="s">
+      <c r="Y13" s="13">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="13"/>
+      <c r="AA13" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="AA13" s="9"/>
       <c r="AB13" s="9"/>
       <c r="AC13" s="9"/>
-      <c r="AD13" s="13"/>
-      <c r="AE13" s="13"/>
+      <c r="AD13" s="9"/>
+      <c r="AE13" s="9"/>
       <c r="AF13" s="13"/>
-      <c r="AG13" s="23" t="s">
+      <c r="AG13" s="13"/>
+      <c r="AH13" s="13"/>
+      <c r="AI13" s="23" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="14" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:33">
+    <row r="14" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B14"/>
       <c r="C14" s="8">
         <v>2000002</v>
       </c>
       <c r="D14" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="E14" s="9"/>
+      <c r="E14" s="9" t="s">
+        <v>197</v>
+      </c>
       <c r="F14" s="9"/>
       <c r="G14" s="9"/>
-      <c r="H14" s="22" t="s">
+      <c r="H14" s="9"/>
+      <c r="I14" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8">
+      <c r="J14" s="8"/>
+      <c r="K14" s="8">
         <v>14</v>
       </c>
-      <c r="K14" s="8">
+      <c r="L14" s="8">
         <v>2000002</v>
       </c>
-      <c r="L14" s="16" t="s">
+      <c r="M14" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="M14" s="13">
-        <v>1</v>
-      </c>
       <c r="N14" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14" s="13">
         <v>0</v>
@@ -3205,278 +2797,296 @@
         <v>0</v>
       </c>
       <c r="Q14" s="13">
-        <v>1</v>
-      </c>
-      <c r="R14" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="R14" s="13">
+        <v>1</v>
+      </c>
+      <c r="S14" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="S14" s="9" t="s">
+      <c r="T14" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="T14" s="13">
-        <v>1</v>
-      </c>
-      <c r="U14" s="9"/>
-      <c r="V14" s="13">
+      <c r="U14" s="13">
+        <v>1</v>
+      </c>
+      <c r="V14" s="9"/>
+      <c r="W14" s="13">
         <v>200</v>
       </c>
-      <c r="W14" s="13">
-        <v>0</v>
-      </c>
       <c r="X14" s="13">
         <v>0</v>
       </c>
-      <c r="Y14" s="13"/>
-      <c r="Z14" s="8"/>
-      <c r="AA14" s="13"/>
-      <c r="AB14" s="9"/>
+      <c r="Y14" s="13">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="13"/>
+      <c r="AA14" s="8"/>
+      <c r="AB14" s="13"/>
       <c r="AC14" s="9"/>
-      <c r="AD14" s="13"/>
-      <c r="AE14" s="13"/>
+      <c r="AD14" s="9"/>
+      <c r="AE14" s="9"/>
       <c r="AF14" s="13"/>
-      <c r="AG14" s="20" t="s">
+      <c r="AG14" s="13"/>
+      <c r="AH14" s="13"/>
+      <c r="AI14" s="20" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="15" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:33">
+    <row r="15" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B15"/>
       <c r="C15" s="8">
         <v>2000003</v>
       </c>
       <c r="D15" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="E15" s="9"/>
+      <c r="E15" s="9" t="s">
+        <v>198</v>
+      </c>
       <c r="F15" s="9"/>
       <c r="G15" s="9"/>
-      <c r="H15" s="22" t="s">
+      <c r="H15" s="9"/>
+      <c r="I15" s="22" t="s">
         <v>141</v>
       </c>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8">
+      <c r="J15" s="8"/>
+      <c r="K15" s="8">
         <v>8</v>
       </c>
-      <c r="K15" s="8">
+      <c r="L15" s="8">
         <v>2000003</v>
       </c>
-      <c r="L15" s="16" t="s">
+      <c r="M15" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="M15" s="13">
-        <v>0</v>
-      </c>
       <c r="N15" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P15" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="13">
         <v>1</v>
       </c>
-      <c r="R15" s="9" t="s">
+      <c r="R15" s="13">
+        <v>1</v>
+      </c>
+      <c r="S15" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="S15" s="9" t="s">
+      <c r="T15" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="T15" s="13">
-        <v>1</v>
-      </c>
-      <c r="U15" s="9"/>
-      <c r="V15" s="13">
-        <v>0</v>
-      </c>
+      <c r="U15" s="13">
+        <v>1</v>
+      </c>
+      <c r="V15" s="9"/>
       <c r="W15" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X15" s="13">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="13"/>
-      <c r="Z15" s="8"/>
-      <c r="AA15" s="13"/>
-      <c r="AB15" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="Y15" s="13">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="13"/>
+      <c r="AA15" s="8"/>
+      <c r="AB15" s="13"/>
       <c r="AC15" s="9"/>
-      <c r="AD15" s="13"/>
-      <c r="AE15" s="13"/>
+      <c r="AD15" s="9"/>
+      <c r="AE15" s="9"/>
       <c r="AF15" s="13"/>
-      <c r="AG15" s="20"/>
+      <c r="AG15" s="13"/>
+      <c r="AH15" s="13"/>
+      <c r="AI15" s="20"/>
     </row>
-    <row r="16" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:33">
+    <row r="16" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B16"/>
       <c r="C16" s="8">
         <v>2000004</v>
       </c>
       <c r="D16" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="E16" s="9"/>
+      <c r="E16" s="9" t="s">
+        <v>198</v>
+      </c>
       <c r="F16" s="9"/>
       <c r="G16" s="9"/>
-      <c r="H16" s="22" t="s">
+      <c r="H16" s="9"/>
+      <c r="I16" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8">
+      <c r="J16" s="8"/>
+      <c r="K16" s="8">
         <v>8</v>
       </c>
-      <c r="K16" s="8">
+      <c r="L16" s="8">
         <v>2000003</v>
       </c>
-      <c r="L16" s="16" t="s">
+      <c r="M16" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="M16" s="13">
-        <v>0</v>
-      </c>
       <c r="N16" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O16" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P16" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="13">
         <v>1</v>
       </c>
-      <c r="R16" s="9" t="s">
+      <c r="R16" s="13">
+        <v>1</v>
+      </c>
+      <c r="S16" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="S16" s="9" t="s">
+      <c r="T16" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="T16" s="13">
-        <v>1</v>
-      </c>
-      <c r="U16" s="9"/>
-      <c r="V16" s="13">
-        <v>1</v>
-      </c>
+      <c r="U16" s="13">
+        <v>1</v>
+      </c>
+      <c r="V16" s="9"/>
       <c r="W16" s="13">
         <v>1</v>
       </c>
       <c r="X16" s="13">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="13"/>
-      <c r="Z16" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y16" s="13">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="13"/>
+      <c r="AA16" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="AA16" s="13"/>
-      <c r="AB16" s="9"/>
+      <c r="AB16" s="13"/>
       <c r="AC16" s="9"/>
-      <c r="AD16" s="13"/>
-      <c r="AE16" s="13"/>
+      <c r="AD16" s="9"/>
+      <c r="AE16" s="9"/>
       <c r="AF16" s="13"/>
-      <c r="AG16" s="20"/>
+      <c r="AG16" s="13"/>
+      <c r="AH16" s="13"/>
+      <c r="AI16" s="20"/>
     </row>
-    <row r="17" ht="20.1" customHeight="1" spans="3:33">
+    <row r="17" spans="2:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C17" s="8">
         <v>2000008</v>
       </c>
       <c r="D17" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="E17" s="9"/>
+      <c r="E17" s="10" t="s">
+        <v>199</v>
+      </c>
       <c r="F17" s="9"/>
       <c r="G17" s="9"/>
-      <c r="H17" s="22" t="s">
+      <c r="H17" s="9"/>
+      <c r="I17" s="22" t="s">
         <v>146</v>
       </c>
-      <c r="I17" s="8">
+      <c r="J17" s="8">
         <v>20000038</v>
       </c>
-      <c r="J17" s="8">
+      <c r="K17" s="8">
         <v>18</v>
       </c>
-      <c r="K17" s="8">
+      <c r="L17" s="8">
         <v>2000008</v>
       </c>
-      <c r="L17" s="16" t="s">
+      <c r="M17" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="M17" s="13">
-        <v>1</v>
-      </c>
       <c r="N17" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P17" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="13">
-        <v>1</v>
-      </c>
-      <c r="R17" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="R17" s="13">
+        <v>1</v>
+      </c>
+      <c r="S17" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="S17" s="9" t="s">
+      <c r="T17" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="T17" s="13">
+      <c r="U17" s="13">
         <v>12</v>
       </c>
-      <c r="U17" s="9" t="s">
+      <c r="V17" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="V17" s="13">
-        <v>0</v>
-      </c>
       <c r="W17" s="13">
         <v>0</v>
       </c>
       <c r="X17" s="13">
         <v>0</v>
       </c>
-      <c r="Y17" s="13"/>
-      <c r="Z17" s="8" t="s">
+      <c r="Y17" s="13">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="13"/>
+      <c r="AA17" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="AA17" s="13"/>
-      <c r="AB17" s="9"/>
+      <c r="AB17" s="13"/>
       <c r="AC17" s="9"/>
-      <c r="AD17" s="13"/>
-      <c r="AE17" s="13"/>
+      <c r="AD17" s="9"/>
+      <c r="AE17" s="9"/>
       <c r="AF17" s="13"/>
-      <c r="AG17" s="23" t="s">
+      <c r="AG17" s="13"/>
+      <c r="AH17" s="13"/>
+      <c r="AI17" s="23" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="18" ht="20.1" customHeight="1" spans="3:33">
+    <row r="18" spans="2:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C18" s="8">
         <v>2000009</v>
       </c>
       <c r="D18" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="E18" s="9"/>
+      <c r="E18" s="10" t="s">
+        <v>200</v>
+      </c>
       <c r="F18" s="9"/>
       <c r="G18" s="9"/>
-      <c r="H18" s="22" t="s">
+      <c r="H18" s="9"/>
+      <c r="I18" s="22" t="s">
         <v>151</v>
       </c>
-      <c r="I18" s="24" t="s">
+      <c r="J18" s="24" t="s">
         <v>152</v>
       </c>
-      <c r="J18" s="8">
+      <c r="K18" s="8">
         <v>17</v>
       </c>
-      <c r="K18" s="8">
+      <c r="L18" s="8">
         <v>2000009</v>
       </c>
-      <c r="L18" s="16" t="s">
+      <c r="M18" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="M18" s="13">
-        <v>1</v>
-      </c>
       <c r="N18" s="13">
         <v>1</v>
       </c>
@@ -3484,26 +3094,26 @@
         <v>1</v>
       </c>
       <c r="P18" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q18" s="13">
-        <v>1</v>
-      </c>
-      <c r="R18" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="R18" s="13">
+        <v>1</v>
+      </c>
+      <c r="S18" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="S18" s="9" t="s">
+      <c r="T18" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="T18" s="13">
+      <c r="U18" s="13">
         <v>12</v>
       </c>
-      <c r="U18" s="9" t="s">
+      <c r="V18" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="V18" s="13">
-        <v>0</v>
-      </c>
       <c r="W18" s="13">
         <v>0</v>
       </c>
@@ -3511,44 +3121,48 @@
         <v>0</v>
       </c>
       <c r="Y18" s="13">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="13">
         <v>72005013</v>
       </c>
-      <c r="Z18" s="8"/>
-      <c r="AA18" s="13"/>
-      <c r="AB18" s="9"/>
+      <c r="AA18" s="8"/>
+      <c r="AB18" s="13"/>
       <c r="AC18" s="9"/>
-      <c r="AD18" s="13"/>
-      <c r="AE18" s="13"/>
+      <c r="AD18" s="9"/>
+      <c r="AE18" s="9"/>
       <c r="AF18" s="13"/>
-      <c r="AG18" s="23" t="s">
+      <c r="AG18" s="13"/>
+      <c r="AH18" s="13"/>
+      <c r="AI18" s="23" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="19" ht="20.1" customHeight="1" spans="3:33">
+    <row r="19" spans="2:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C19" s="8">
         <v>2000010</v>
       </c>
       <c r="D19" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="E19" s="9"/>
+      <c r="E19" s="10" t="s">
+        <v>201</v>
+      </c>
       <c r="F19" s="9"/>
       <c r="G19" s="9"/>
-      <c r="H19" s="22" t="s">
+      <c r="H19" s="9"/>
+      <c r="I19" s="22" t="s">
         <v>155</v>
       </c>
-      <c r="I19" s="8"/>
-      <c r="J19" s="8">
+      <c r="J19" s="8"/>
+      <c r="K19" s="8">
         <v>19</v>
       </c>
-      <c r="K19" s="8">
+      <c r="L19" s="8">
         <v>2000003</v>
       </c>
-      <c r="L19" s="13">
-        <v>0</v>
-      </c>
       <c r="M19" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" s="13">
         <v>1</v>
@@ -3557,74 +3171,79 @@
         <v>1</v>
       </c>
       <c r="P19" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="13">
-        <v>1</v>
-      </c>
-      <c r="R19" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="R19" s="13">
+        <v>1</v>
+      </c>
+      <c r="S19" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="S19" s="9" t="s">
+      <c r="T19" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="T19" s="13">
-        <v>1</v>
-      </c>
-      <c r="U19" s="9"/>
-      <c r="V19" s="13">
+      <c r="U19" s="13">
+        <v>1</v>
+      </c>
+      <c r="V19" s="9"/>
+      <c r="W19" s="13">
         <v>2</v>
       </c>
-      <c r="W19" s="13">
-        <v>0</v>
-      </c>
       <c r="X19" s="13">
-        <v>1</v>
-      </c>
-      <c r="Y19" s="13"/>
-      <c r="Z19" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="13">
+        <v>1</v>
+      </c>
+      <c r="Z19" s="13"/>
+      <c r="AA19" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="AA19" s="13"/>
-      <c r="AB19" s="9"/>
+      <c r="AB19" s="13"/>
       <c r="AC19" s="9"/>
-      <c r="AD19" s="13"/>
-      <c r="AE19" s="13"/>
+      <c r="AD19" s="9"/>
+      <c r="AE19" s="9"/>
       <c r="AF19" s="13"/>
-      <c r="AG19" s="20" t="s">
+      <c r="AG19" s="13"/>
+      <c r="AH19" s="13"/>
+      <c r="AI19" s="20" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:33">
+    <row r="20" spans="2:35" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B20"/>
       <c r="C20" s="8">
         <v>2000011</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="E20" s="9"/>
+      <c r="E20" s="9" t="s">
+        <v>202</v>
+      </c>
       <c r="F20" s="9"/>
       <c r="G20" s="9"/>
-      <c r="H20" s="22" t="s">
+      <c r="H20" s="9"/>
+      <c r="I20" s="22" t="s">
         <v>159</v>
       </c>
-      <c r="I20" s="9" t="s">
+      <c r="J20" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="J20" s="9" t="s">
+      <c r="K20" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="K20" s="13">
+      <c r="L20" s="13">
         <v>102</v>
       </c>
-      <c r="L20" s="13">
-        <v>0</v>
-      </c>
       <c r="M20" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N20" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20" s="13">
         <v>0</v>
@@ -3633,23 +3252,23 @@
         <v>0</v>
       </c>
       <c r="Q20" s="13">
-        <v>1</v>
-      </c>
-      <c r="R20" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="R20" s="13">
+        <v>1</v>
+      </c>
+      <c r="S20" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="S20" s="9" t="s">
+      <c r="T20" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="T20" s="13">
+      <c r="U20" s="13">
         <v>10</v>
       </c>
-      <c r="U20" s="9" t="s">
+      <c r="V20" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="V20" s="13">
-        <v>0</v>
-      </c>
       <c r="W20" s="13">
         <v>0</v>
       </c>
@@ -3659,537 +3278,574 @@
       <c r="Y20" s="13">
         <v>0</v>
       </c>
-      <c r="Z20" s="9"/>
+      <c r="Z20" s="13">
+        <v>0</v>
+      </c>
       <c r="AA20" s="9"/>
       <c r="AB20" s="9"/>
       <c r="AC20" s="9"/>
-      <c r="AD20" s="13">
-        <v>0</v>
-      </c>
-      <c r="AE20" s="13">
-        <v>0</v>
-      </c>
+      <c r="AD20" s="9"/>
+      <c r="AE20" s="9"/>
       <c r="AF20" s="13">
         <v>0</v>
       </c>
-      <c r="AG20" s="20" t="s">
+      <c r="AG20" s="13">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="13">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="20" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="21" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:33">
+    <row r="21" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B21"/>
       <c r="C21" s="8">
         <v>2100001</v>
       </c>
       <c r="D21" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="E21" s="9"/>
+      <c r="E21" s="9" t="s">
+        <v>203</v>
+      </c>
       <c r="F21" s="9"/>
       <c r="G21" s="9"/>
-      <c r="H21" s="22" t="s">
+      <c r="H21" s="9"/>
+      <c r="I21" s="22" t="s">
         <v>141</v>
       </c>
-      <c r="I21" s="8"/>
-      <c r="J21" s="8">
+      <c r="J21" s="8"/>
+      <c r="K21" s="8">
         <v>6</v>
       </c>
-      <c r="K21" s="8">
+      <c r="L21" s="8">
         <v>100001</v>
       </c>
-      <c r="L21" s="13">
-        <v>0</v>
-      </c>
       <c r="M21" s="13">
         <v>0</v>
       </c>
       <c r="N21" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P21" s="13">
         <v>0</v>
       </c>
       <c r="Q21" s="13">
-        <v>1</v>
-      </c>
-      <c r="R21" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="R21" s="13">
+        <v>1</v>
+      </c>
+      <c r="S21" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="S21" s="9" t="s">
+      <c r="T21" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="T21" s="13">
-        <v>1</v>
-      </c>
-      <c r="U21" s="9"/>
-      <c r="V21" s="13">
-        <v>1</v>
-      </c>
+      <c r="U21" s="13">
+        <v>1</v>
+      </c>
+      <c r="V21" s="9"/>
       <c r="W21" s="13">
+        <v>1</v>
+      </c>
+      <c r="X21" s="13">
         <v>5</v>
       </c>
-      <c r="X21" s="13">
-        <v>0</v>
-      </c>
-      <c r="Y21" s="13"/>
-      <c r="Z21" s="8"/>
-      <c r="AA21" s="13"/>
-      <c r="AB21" s="9"/>
+      <c r="Y21" s="13">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="13"/>
+      <c r="AA21" s="8"/>
+      <c r="AB21" s="13"/>
       <c r="AC21" s="9"/>
-      <c r="AD21" s="13"/>
-      <c r="AE21" s="13"/>
+      <c r="AD21" s="9"/>
+      <c r="AE21" s="9"/>
       <c r="AF21" s="13"/>
-      <c r="AG21" s="20"/>
+      <c r="AG21" s="13"/>
+      <c r="AH21" s="13"/>
+      <c r="AI21" s="20"/>
     </row>
-    <row r="22" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:33">
+    <row r="22" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B22"/>
       <c r="C22" s="8">
         <v>2100002</v>
       </c>
       <c r="D22" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="E22" s="9"/>
+      <c r="E22" s="9" t="s">
+        <v>204</v>
+      </c>
       <c r="F22" s="9"/>
       <c r="G22" s="9"/>
-      <c r="H22" s="22" t="s">
+      <c r="H22" s="9"/>
+      <c r="I22" s="22" t="s">
         <v>141</v>
       </c>
-      <c r="I22" s="8"/>
-      <c r="J22" s="8">
+      <c r="J22" s="8"/>
+      <c r="K22" s="8">
         <v>10</v>
       </c>
-      <c r="K22" s="8">
+      <c r="L22" s="8">
         <v>100001</v>
       </c>
-      <c r="L22" s="13">
-        <v>0</v>
-      </c>
       <c r="M22" s="13">
         <v>0</v>
       </c>
       <c r="N22" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O22" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P22" s="13">
         <v>0</v>
       </c>
       <c r="Q22" s="13">
-        <v>1</v>
-      </c>
-      <c r="R22" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="R22" s="13">
+        <v>1</v>
+      </c>
+      <c r="S22" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="S22" s="9" t="s">
+      <c r="T22" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="T22" s="13">
-        <v>1</v>
-      </c>
-      <c r="U22" s="9"/>
-      <c r="V22" s="13">
-        <v>1</v>
-      </c>
+      <c r="U22" s="13">
+        <v>1</v>
+      </c>
+      <c r="V22" s="9"/>
       <c r="W22" s="13">
+        <v>1</v>
+      </c>
+      <c r="X22" s="13">
         <v>10</v>
       </c>
-      <c r="X22" s="13">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="13"/>
-      <c r="Z22" s="8"/>
-      <c r="AA22" s="13"/>
-      <c r="AB22" s="9"/>
+      <c r="Y22" s="13">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="13"/>
+      <c r="AA22" s="8"/>
+      <c r="AB22" s="13"/>
       <c r="AC22" s="9"/>
-      <c r="AD22" s="13"/>
-      <c r="AE22" s="13"/>
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9"/>
       <c r="AF22" s="13"/>
-      <c r="AG22" s="20"/>
+      <c r="AG22" s="13"/>
+      <c r="AH22" s="13"/>
+      <c r="AI22" s="20"/>
     </row>
-    <row r="23" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:33">
+    <row r="23" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B23"/>
       <c r="C23" s="8">
         <v>2200001</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="E23" s="9"/>
+      <c r="E23" s="9" t="s">
+        <v>205</v>
+      </c>
       <c r="F23" s="9"/>
       <c r="G23" s="9"/>
-      <c r="H23" s="22" t="s">
+      <c r="H23" s="9"/>
+      <c r="I23" s="22" t="s">
         <v>166</v>
       </c>
-      <c r="I23" s="8"/>
-      <c r="J23" s="8">
+      <c r="J23" s="8"/>
+      <c r="K23" s="8">
         <v>11</v>
       </c>
-      <c r="K23" s="8">
+      <c r="L23" s="8">
         <v>10007</v>
       </c>
-      <c r="L23" s="13">
-        <v>0</v>
-      </c>
       <c r="M23" s="13">
         <v>0</v>
       </c>
       <c r="N23" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P23" s="13">
         <v>0</v>
       </c>
       <c r="Q23" s="13">
-        <v>1</v>
-      </c>
-      <c r="R23" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="R23" s="13">
+        <v>1</v>
+      </c>
+      <c r="S23" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="S23" s="9" t="s">
+      <c r="T23" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="T23" s="13">
-        <v>1</v>
-      </c>
-      <c r="U23" s="9"/>
-      <c r="V23" s="13">
-        <v>1</v>
-      </c>
+      <c r="U23" s="13">
+        <v>1</v>
+      </c>
+      <c r="V23" s="9"/>
       <c r="W23" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X23" s="13">
         <v>0</v>
       </c>
-      <c r="Y23" s="13"/>
-      <c r="Z23" s="9"/>
+      <c r="Y23" s="13">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="13"/>
       <c r="AA23" s="9"/>
       <c r="AB23" s="9"/>
       <c r="AC23" s="9"/>
-      <c r="AD23" s="13"/>
-      <c r="AE23" s="13"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="9"/>
       <c r="AF23" s="13"/>
-      <c r="AG23" s="20"/>
+      <c r="AG23" s="13"/>
+      <c r="AH23" s="13"/>
+      <c r="AI23" s="20"/>
     </row>
-    <row r="24" ht="20.1" customHeight="1" spans="3:33">
+    <row r="24" spans="2:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C24" s="8">
         <v>3000001</v>
       </c>
       <c r="D24" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="E24" s="9"/>
+      <c r="E24" s="9" t="s">
+        <v>206</v>
+      </c>
       <c r="F24" s="9"/>
       <c r="G24" s="9"/>
-      <c r="H24" s="22" t="s">
+      <c r="H24" s="9"/>
+      <c r="I24" s="22" t="s">
         <v>168</v>
       </c>
-      <c r="I24" s="17" t="s">
+      <c r="J24" s="17" t="s">
         <v>169</v>
       </c>
-      <c r="J24" s="8">
+      <c r="K24" s="8">
         <v>12</v>
       </c>
-      <c r="K24" s="8">
+      <c r="L24" s="8">
         <v>201</v>
       </c>
-      <c r="L24" s="13">
-        <v>0</v>
-      </c>
       <c r="M24" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O24" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P24" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q24" s="13">
-        <v>1</v>
-      </c>
-      <c r="R24" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="R24" s="13">
+        <v>1</v>
+      </c>
+      <c r="S24" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="S24" s="9" t="s">
+      <c r="T24" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="T24" s="13">
+      <c r="U24" s="13">
         <v>10</v>
       </c>
-      <c r="U24" s="9" t="s">
+      <c r="V24" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="V24" s="13">
+      <c r="W24" s="13">
         <v>40</v>
       </c>
-      <c r="W24" s="13">
-        <v>0</v>
-      </c>
       <c r="X24" s="13">
         <v>0</v>
       </c>
-      <c r="Y24" s="13"/>
-      <c r="Z24" s="8"/>
-      <c r="AA24" s="25" t="s">
+      <c r="Y24" s="13">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="13"/>
+      <c r="AA24" s="8"/>
+      <c r="AB24" s="25" t="s">
         <v>171</v>
       </c>
-      <c r="AB24" s="9"/>
       <c r="AC24" s="9"/>
-      <c r="AD24" s="13"/>
-      <c r="AE24" s="13"/>
+      <c r="AD24" s="9"/>
+      <c r="AE24" s="9"/>
       <c r="AF24" s="13"/>
-      <c r="AG24" s="20" t="s">
+      <c r="AG24" s="13"/>
+      <c r="AH24" s="13"/>
+      <c r="AI24" s="20" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="25" ht="20.1" customHeight="1" spans="3:33">
+    <row r="25" spans="2:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C25" s="8">
         <v>3000002</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="E25" s="9"/>
+      <c r="E25" s="9" t="s">
+        <v>207</v>
+      </c>
       <c r="F25" s="9"/>
       <c r="G25" s="9"/>
-      <c r="H25" s="22" t="s">
+      <c r="H25" s="9"/>
+      <c r="I25" s="22" t="s">
         <v>168</v>
       </c>
-      <c r="I25" s="17" t="s">
+      <c r="J25" s="17" t="s">
         <v>169</v>
       </c>
-      <c r="J25" s="8">
+      <c r="K25" s="8">
         <v>12</v>
       </c>
-      <c r="K25" s="8">
+      <c r="L25" s="8">
         <v>201</v>
       </c>
-      <c r="L25" s="13">
-        <v>0</v>
-      </c>
       <c r="M25" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O25" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P25" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="13">
-        <v>1</v>
-      </c>
-      <c r="R25" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="R25" s="13">
+        <v>1</v>
+      </c>
+      <c r="S25" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="S25" s="9" t="s">
+      <c r="T25" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="T25" s="13">
+      <c r="U25" s="13">
         <v>30</v>
       </c>
-      <c r="U25" s="9" t="s">
+      <c r="V25" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="V25" s="13">
+      <c r="W25" s="13">
         <v>40</v>
       </c>
-      <c r="W25" s="13">
-        <v>0</v>
-      </c>
       <c r="X25" s="13">
         <v>0</v>
       </c>
-      <c r="Y25" s="13"/>
-      <c r="Z25" s="8"/>
-      <c r="AA25" s="25" t="s">
+      <c r="Y25" s="13">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="13"/>
+      <c r="AA25" s="8"/>
+      <c r="AB25" s="25" t="s">
         <v>174</v>
       </c>
-      <c r="AB25" s="9"/>
       <c r="AC25" s="9"/>
-      <c r="AD25" s="13"/>
-      <c r="AE25" s="13"/>
+      <c r="AD25" s="9"/>
+      <c r="AE25" s="9"/>
       <c r="AF25" s="13"/>
-      <c r="AG25" s="20" t="s">
+      <c r="AG25" s="13"/>
+      <c r="AH25" s="13"/>
+      <c r="AI25" s="20" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="26" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:33">
+    <row r="26" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B26"/>
       <c r="C26" s="8">
         <v>4000001</v>
       </c>
       <c r="D26" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="E26" s="9"/>
+      <c r="E26" s="9" t="s">
+        <v>208</v>
+      </c>
       <c r="F26" s="9"/>
       <c r="G26" s="9"/>
-      <c r="H26" s="22" t="s">
+      <c r="H26" s="9"/>
+      <c r="I26" s="22" t="s">
         <v>141</v>
       </c>
-      <c r="I26" s="8"/>
-      <c r="J26" s="8">
+      <c r="J26" s="8"/>
+      <c r="K26" s="8">
         <v>13</v>
       </c>
-      <c r="K26" s="8">
+      <c r="L26" s="8">
         <v>2000004</v>
       </c>
-      <c r="L26" s="13">
-        <v>0</v>
-      </c>
       <c r="M26" s="13">
         <v>0</v>
       </c>
       <c r="N26" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O26" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P26" s="13">
         <v>0</v>
       </c>
       <c r="Q26" s="13">
-        <v>1</v>
-      </c>
-      <c r="R26" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="R26" s="13">
+        <v>1</v>
+      </c>
+      <c r="S26" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="S26" s="9" t="s">
+      <c r="T26" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="T26" s="13">
+      <c r="U26" s="13">
         <v>10</v>
       </c>
-      <c r="U26" s="9"/>
-      <c r="V26" s="13">
-        <v>0</v>
-      </c>
+      <c r="V26" s="9"/>
       <c r="W26" s="13">
         <v>0</v>
       </c>
       <c r="X26" s="13">
         <v>0</v>
       </c>
-      <c r="Y26" s="13"/>
-      <c r="Z26" s="8" t="s">
+      <c r="Y26" s="13">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="13"/>
+      <c r="AA26" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="AA26" s="13"/>
-      <c r="AB26" s="9"/>
+      <c r="AB26" s="13"/>
       <c r="AC26" s="9"/>
-      <c r="AD26" s="13"/>
-      <c r="AE26" s="13"/>
+      <c r="AD26" s="9"/>
+      <c r="AE26" s="9"/>
       <c r="AF26" s="13"/>
-      <c r="AG26" s="20"/>
+      <c r="AG26" s="13"/>
+      <c r="AH26" s="13"/>
+      <c r="AI26" s="20"/>
     </row>
-    <row r="27" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:33">
+    <row r="27" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B27"/>
       <c r="C27" s="8">
         <v>5000001</v>
       </c>
       <c r="D27" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="E27" s="9"/>
+      <c r="E27" s="9" t="s">
+        <v>208</v>
+      </c>
       <c r="F27" s="9"/>
       <c r="G27" s="9"/>
-      <c r="H27" s="22" t="s">
+      <c r="H27" s="9"/>
+      <c r="I27" s="22" t="s">
         <v>141</v>
       </c>
-      <c r="I27" s="8"/>
-      <c r="J27" s="8">
+      <c r="J27" s="8"/>
+      <c r="K27" s="8">
         <v>13</v>
       </c>
-      <c r="K27" s="8">
+      <c r="L27" s="8">
         <v>2000004</v>
       </c>
-      <c r="L27" s="13">
-        <v>0</v>
-      </c>
       <c r="M27" s="13">
         <v>0</v>
       </c>
       <c r="N27" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O27" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P27" s="13">
         <v>0</v>
       </c>
       <c r="Q27" s="13">
-        <v>1</v>
-      </c>
-      <c r="R27" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="R27" s="13">
+        <v>1</v>
+      </c>
+      <c r="S27" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="S27" s="9" t="s">
+      <c r="T27" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="T27" s="13">
+      <c r="U27" s="13">
         <v>10</v>
       </c>
-      <c r="U27" s="9"/>
-      <c r="V27" s="13">
-        <v>0</v>
-      </c>
+      <c r="V27" s="9"/>
       <c r="W27" s="13">
         <v>0</v>
       </c>
       <c r="X27" s="13">
         <v>0</v>
       </c>
-      <c r="Y27" s="13"/>
-      <c r="Z27" s="8" t="s">
+      <c r="Y27" s="13">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="13"/>
+      <c r="AA27" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="AA27" s="13"/>
-      <c r="AB27" s="9"/>
+      <c r="AB27" s="13"/>
       <c r="AC27" s="9"/>
-      <c r="AD27" s="13"/>
-      <c r="AE27" s="13"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9"/>
       <c r="AF27" s="13"/>
-      <c r="AG27" s="20"/>
+      <c r="AG27" s="13"/>
+      <c r="AH27" s="13"/>
+      <c r="AI27" s="20"/>
     </row>
-    <row r="28" ht="20.1" customHeight="1" spans="3:33">
+    <row r="28" spans="2:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C28" s="8">
         <v>6000001</v>
       </c>
       <c r="D28" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="E28" s="9"/>
+      <c r="E28" s="10" t="s">
+        <v>209</v>
+      </c>
       <c r="F28" s="9"/>
       <c r="G28" s="9"/>
-      <c r="H28" s="22" t="s">
+      <c r="H28" s="9"/>
+      <c r="I28" s="22" t="s">
         <v>177</v>
       </c>
-      <c r="I28" s="8"/>
-      <c r="J28" s="8">
+      <c r="J28" s="8"/>
+      <c r="K28" s="8">
         <v>15</v>
       </c>
-      <c r="K28" s="8">
+      <c r="L28" s="8">
         <v>2000006</v>
       </c>
-      <c r="L28" s="13">
-        <v>0</v>
-      </c>
       <c r="M28" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" s="13">
         <v>1</v>
@@ -4198,485 +3854,519 @@
         <v>1</v>
       </c>
       <c r="P28" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q28" s="13">
-        <v>1</v>
-      </c>
-      <c r="R28" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="R28" s="13">
+        <v>1</v>
+      </c>
+      <c r="S28" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="S28" s="9" t="s">
+      <c r="T28" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="T28" s="13">
+      <c r="U28" s="13">
         <v>12</v>
       </c>
-      <c r="U28" s="9" t="s">
+      <c r="V28" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="V28" s="13">
+      <c r="W28" s="13">
         <v>100</v>
       </c>
-      <c r="W28" s="13">
-        <v>0</v>
-      </c>
       <c r="X28" s="13">
         <v>0</v>
       </c>
-      <c r="Y28" s="13"/>
-      <c r="Z28" s="8" t="s">
+      <c r="Y28" s="13">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="13"/>
+      <c r="AA28" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="AA28" s="13"/>
-      <c r="AB28" s="9"/>
+      <c r="AB28" s="13"/>
       <c r="AC28" s="9"/>
-      <c r="AD28" s="13"/>
-      <c r="AE28" s="13"/>
+      <c r="AD28" s="9"/>
+      <c r="AE28" s="9"/>
       <c r="AF28" s="13"/>
-      <c r="AG28" s="20" t="s">
+      <c r="AG28" s="13"/>
+      <c r="AH28" s="13"/>
+      <c r="AI28" s="20" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="29" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:33">
+    <row r="29" spans="2:35" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B29"/>
       <c r="C29" s="11">
         <v>6000002</v>
       </c>
       <c r="D29" s="12" t="s">
         <v>180</v>
       </c>
-      <c r="E29" s="12"/>
+      <c r="E29" s="12" t="s">
+        <v>210</v>
+      </c>
       <c r="F29" s="12"/>
       <c r="G29" s="12"/>
-      <c r="H29" s="26" t="s">
+      <c r="H29" s="12"/>
+      <c r="I29" s="26" t="s">
         <v>181</v>
       </c>
-      <c r="I29" s="11"/>
-      <c r="J29" s="11">
+      <c r="J29" s="11"/>
+      <c r="K29" s="11">
         <v>22</v>
       </c>
-      <c r="K29" s="11">
+      <c r="L29" s="11">
         <v>2000011</v>
       </c>
-      <c r="L29" s="18">
-        <v>0</v>
-      </c>
       <c r="M29" s="18">
         <v>0</v>
       </c>
       <c r="N29" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O29" s="18">
         <v>1</v>
       </c>
       <c r="P29" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q29" s="18">
-        <v>1</v>
-      </c>
-      <c r="R29" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="R29" s="18">
+        <v>1</v>
+      </c>
+      <c r="S29" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="S29" s="12" t="s">
+      <c r="T29" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="T29" s="18">
-        <v>1</v>
-      </c>
-      <c r="U29" s="12"/>
-      <c r="V29" s="18">
-        <v>0</v>
-      </c>
+      <c r="U29" s="18">
+        <v>1</v>
+      </c>
+      <c r="V29" s="12"/>
       <c r="W29" s="18">
         <v>0</v>
       </c>
       <c r="X29" s="18">
-        <v>1</v>
-      </c>
-      <c r="Y29" s="18"/>
-      <c r="Z29" s="11"/>
-      <c r="AA29" s="18">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="18">
+        <v>1</v>
+      </c>
+      <c r="Z29" s="18"/>
+      <c r="AA29" s="11"/>
+      <c r="AB29" s="18">
         <v>100101</v>
       </c>
-      <c r="AB29" s="12"/>
       <c r="AC29" s="12"/>
-      <c r="AD29" s="18"/>
-      <c r="AE29" s="18"/>
+      <c r="AD29" s="12"/>
+      <c r="AE29" s="12"/>
       <c r="AF29" s="18"/>
-      <c r="AG29" s="21" t="s">
+      <c r="AG29" s="18"/>
+      <c r="AH29" s="18"/>
+      <c r="AI29" s="21" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="30" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:33">
+    <row r="30" spans="2:35" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B30"/>
       <c r="C30" s="11">
         <v>6000003</v>
       </c>
       <c r="D30" s="12" t="s">
         <v>182</v>
       </c>
-      <c r="E30" s="12"/>
+      <c r="E30" s="12" t="s">
+        <v>211</v>
+      </c>
       <c r="F30" s="12"/>
       <c r="G30" s="12"/>
-      <c r="H30" s="26" t="s">
+      <c r="H30" s="12"/>
+      <c r="I30" s="26" t="s">
         <v>181</v>
       </c>
-      <c r="I30" s="11"/>
-      <c r="J30" s="11">
+      <c r="J30" s="11"/>
+      <c r="K30" s="11">
         <v>23</v>
       </c>
-      <c r="K30" s="11">
+      <c r="L30" s="11">
         <v>2000011</v>
       </c>
-      <c r="L30" s="18">
-        <v>0</v>
-      </c>
       <c r="M30" s="18">
         <v>0</v>
       </c>
       <c r="N30" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O30" s="18">
         <v>1</v>
       </c>
       <c r="P30" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q30" s="18">
-        <v>1</v>
-      </c>
-      <c r="R30" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="R30" s="18">
+        <v>1</v>
+      </c>
+      <c r="S30" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="S30" s="12" t="s">
+      <c r="T30" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="T30" s="18">
-        <v>1</v>
-      </c>
-      <c r="U30" s="12"/>
-      <c r="V30" s="18">
-        <v>0</v>
-      </c>
+      <c r="U30" s="18">
+        <v>1</v>
+      </c>
+      <c r="V30" s="12"/>
       <c r="W30" s="18">
         <v>0</v>
       </c>
       <c r="X30" s="18">
-        <v>1</v>
-      </c>
-      <c r="Y30" s="18"/>
-      <c r="Z30" s="11"/>
-      <c r="AA30" s="18"/>
-      <c r="AB30" s="12"/>
+        <v>0</v>
+      </c>
+      <c r="Y30" s="18">
+        <v>1</v>
+      </c>
+      <c r="Z30" s="18"/>
+      <c r="AA30" s="11"/>
+      <c r="AB30" s="18"/>
       <c r="AC30" s="12"/>
-      <c r="AD30" s="18"/>
-      <c r="AE30" s="18"/>
+      <c r="AD30" s="12"/>
+      <c r="AE30" s="12"/>
       <c r="AF30" s="18"/>
-      <c r="AG30" s="21" t="s">
+      <c r="AG30" s="18"/>
+      <c r="AH30" s="18"/>
+      <c r="AI30" s="21" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="31" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:33">
+    <row r="31" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B31"/>
       <c r="C31" s="8">
         <v>7000001</v>
       </c>
       <c r="D31" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="E31" s="9"/>
+      <c r="E31" s="9" t="s">
+        <v>212</v>
+      </c>
       <c r="F31" s="9"/>
       <c r="G31" s="9"/>
-      <c r="H31" s="22" t="s">
+      <c r="H31" s="9"/>
+      <c r="I31" s="22" t="s">
         <v>141</v>
       </c>
-      <c r="I31" s="8"/>
-      <c r="J31" s="8">
+      <c r="J31" s="8"/>
+      <c r="K31" s="8">
         <v>20</v>
       </c>
-      <c r="K31" s="8">
+      <c r="L31" s="8">
         <v>2000004</v>
       </c>
-      <c r="L31" s="13">
-        <v>0</v>
-      </c>
       <c r="M31" s="13">
         <v>0</v>
       </c>
       <c r="N31" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O31" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P31" s="13">
         <v>0</v>
       </c>
       <c r="Q31" s="13">
-        <v>1</v>
-      </c>
-      <c r="R31" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="R31" s="13">
+        <v>1</v>
+      </c>
+      <c r="S31" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="S31" s="9" t="s">
+      <c r="T31" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="T31" s="13">
-        <v>1</v>
-      </c>
-      <c r="U31" s="9"/>
-      <c r="V31" s="13">
-        <v>0</v>
-      </c>
+      <c r="U31" s="13">
+        <v>1</v>
+      </c>
+      <c r="V31" s="9"/>
       <c r="W31" s="13">
         <v>0</v>
       </c>
       <c r="X31" s="13">
         <v>0</v>
       </c>
-      <c r="Y31" s="13"/>
-      <c r="Z31" s="8" t="s">
+      <c r="Y31" s="13">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="13"/>
+      <c r="AA31" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="AA31" s="13"/>
-      <c r="AB31" s="9"/>
+      <c r="AB31" s="13"/>
       <c r="AC31" s="9"/>
-      <c r="AD31" s="13"/>
-      <c r="AE31" s="13"/>
+      <c r="AD31" s="9"/>
+      <c r="AE31" s="9"/>
       <c r="AF31" s="13"/>
-      <c r="AG31" s="20"/>
+      <c r="AG31" s="13"/>
+      <c r="AH31" s="13"/>
+      <c r="AI31" s="20"/>
     </row>
-    <row r="32" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:33">
+    <row r="32" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B32"/>
       <c r="C32" s="8">
         <v>8000001</v>
       </c>
       <c r="D32" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="E32" s="9"/>
+      <c r="E32" s="9" t="s">
+        <v>213</v>
+      </c>
       <c r="F32" s="9"/>
       <c r="G32" s="9"/>
-      <c r="H32" s="22" t="s">
+      <c r="H32" s="9"/>
+      <c r="I32" s="22" t="s">
         <v>141</v>
       </c>
-      <c r="I32" s="8"/>
-      <c r="J32" s="8">
+      <c r="J32" s="8"/>
+      <c r="K32" s="8">
         <v>21</v>
       </c>
-      <c r="K32" s="8">
+      <c r="L32" s="8">
         <v>2000010</v>
       </c>
-      <c r="L32" s="13">
-        <v>0</v>
-      </c>
       <c r="M32" s="13">
         <v>0</v>
       </c>
       <c r="N32" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O32" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P32" s="13">
         <v>0</v>
       </c>
       <c r="Q32" s="13">
-        <v>1</v>
-      </c>
-      <c r="R32" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="R32" s="13">
+        <v>1</v>
+      </c>
+      <c r="S32" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="S32" s="9" t="s">
+      <c r="T32" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="T32" s="13">
-        <v>1</v>
-      </c>
-      <c r="U32" s="9"/>
-      <c r="V32" s="13">
-        <v>0</v>
-      </c>
+      <c r="U32" s="13">
+        <v>1</v>
+      </c>
+      <c r="V32" s="9"/>
       <c r="W32" s="13">
         <v>0</v>
       </c>
       <c r="X32" s="13">
         <v>0</v>
       </c>
-      <c r="Y32" s="13"/>
-      <c r="Z32" s="8"/>
-      <c r="AA32" s="13"/>
-      <c r="AB32" s="9"/>
+      <c r="Y32" s="13">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="13"/>
+      <c r="AA32" s="8"/>
+      <c r="AB32" s="13"/>
       <c r="AC32" s="9"/>
-      <c r="AD32" s="13"/>
-      <c r="AE32" s="13"/>
+      <c r="AD32" s="9"/>
+      <c r="AE32" s="9"/>
       <c r="AF32" s="13"/>
-      <c r="AG32" s="20" t="s">
+      <c r="AG32" s="13"/>
+      <c r="AH32" s="13"/>
+      <c r="AI32" s="20" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="33" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:33">
+    <row r="33" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B33"/>
       <c r="C33" s="8">
         <v>2400001</v>
       </c>
       <c r="D33" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="E33" s="9"/>
+      <c r="E33" s="9" t="s">
+        <v>214</v>
+      </c>
       <c r="F33" s="9"/>
       <c r="G33" s="9"/>
-      <c r="H33" s="22" t="s">
+      <c r="H33" s="9"/>
+      <c r="I33" s="22" t="s">
         <v>141</v>
       </c>
-      <c r="I33" s="8"/>
-      <c r="J33" s="8">
+      <c r="J33" s="8"/>
+      <c r="K33" s="8">
         <v>24</v>
       </c>
-      <c r="K33" s="8">
+      <c r="L33" s="8">
         <v>100001</v>
       </c>
-      <c r="L33" s="13">
-        <v>0</v>
-      </c>
       <c r="M33" s="13">
         <v>0</v>
       </c>
       <c r="N33" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O33" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P33" s="13">
         <v>0</v>
       </c>
       <c r="Q33" s="13">
-        <v>1</v>
-      </c>
-      <c r="R33" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="R33" s="13">
+        <v>1</v>
+      </c>
+      <c r="S33" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="S33" s="9" t="s">
+      <c r="T33" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="T33" s="13">
-        <v>1</v>
-      </c>
-      <c r="U33" s="9"/>
-      <c r="V33" s="13">
-        <v>1</v>
-      </c>
+      <c r="U33" s="13">
+        <v>1</v>
+      </c>
+      <c r="V33" s="9"/>
       <c r="W33" s="13">
+        <v>1</v>
+      </c>
+      <c r="X33" s="13">
         <v>10</v>
       </c>
-      <c r="X33" s="13">
-        <v>0</v>
-      </c>
-      <c r="Y33" s="13"/>
-      <c r="Z33" s="8"/>
-      <c r="AA33" s="13"/>
-      <c r="AB33" s="9"/>
+      <c r="Y33" s="13">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="13"/>
+      <c r="AA33" s="8"/>
+      <c r="AB33" s="13"/>
       <c r="AC33" s="9"/>
-      <c r="AD33" s="13"/>
-      <c r="AE33" s="13"/>
+      <c r="AD33" s="9"/>
+      <c r="AE33" s="9"/>
       <c r="AF33" s="13"/>
-      <c r="AG33" s="20"/>
+      <c r="AG33" s="13"/>
+      <c r="AH33" s="13"/>
+      <c r="AI33" s="20"/>
     </row>
-    <row r="34" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:33">
+    <row r="34" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B34"/>
       <c r="C34" s="8">
         <v>2500001</v>
       </c>
       <c r="D34" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="E34" s="9"/>
+      <c r="E34" s="9" t="s">
+        <v>215</v>
+      </c>
       <c r="F34" s="9"/>
       <c r="G34" s="9"/>
-      <c r="H34" s="22" t="s">
+      <c r="H34" s="9"/>
+      <c r="I34" s="22" t="s">
         <v>141</v>
       </c>
-      <c r="I34" s="8"/>
-      <c r="J34" s="8">
+      <c r="J34" s="8"/>
+      <c r="K34" s="8">
         <v>25</v>
       </c>
-      <c r="K34" s="8">
+      <c r="L34" s="8">
         <v>2000004</v>
       </c>
-      <c r="L34" s="13">
-        <v>0</v>
-      </c>
       <c r="M34" s="13">
         <v>0</v>
       </c>
       <c r="N34" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O34" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P34" s="13">
         <v>0</v>
       </c>
       <c r="Q34" s="13">
-        <v>1</v>
-      </c>
-      <c r="R34" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="R34" s="13">
+        <v>1</v>
+      </c>
+      <c r="S34" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="S34" s="9" t="s">
+      <c r="T34" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="T34" s="13">
-        <v>1</v>
-      </c>
-      <c r="U34" s="9"/>
-      <c r="V34" s="13">
-        <v>0</v>
-      </c>
+      <c r="U34" s="13">
+        <v>1</v>
+      </c>
+      <c r="V34" s="9"/>
       <c r="W34" s="13">
         <v>0</v>
       </c>
       <c r="X34" s="13">
         <v>0</v>
       </c>
-      <c r="Y34" s="13"/>
-      <c r="Z34" s="8" t="s">
+      <c r="Y34" s="13">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="13"/>
+      <c r="AA34" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="AA34" s="13"/>
-      <c r="AB34" s="9"/>
+      <c r="AB34" s="13"/>
       <c r="AC34" s="9"/>
-      <c r="AD34" s="13"/>
-      <c r="AE34" s="13"/>
+      <c r="AD34" s="9"/>
+      <c r="AE34" s="9"/>
       <c r="AF34" s="13"/>
-      <c r="AG34" s="20"/>
+      <c r="AG34" s="13"/>
+      <c r="AH34" s="13"/>
+      <c r="AI34" s="20"/>
     </row>
-    <row r="35" ht="20.1" customHeight="1" spans="3:33">
+    <row r="35" spans="2:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C35" s="8">
         <v>2600001</v>
       </c>
       <c r="D35" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="E35" s="9"/>
+      <c r="E35" s="10" t="s">
+        <v>216</v>
+      </c>
       <c r="F35" s="9"/>
       <c r="G35" s="9"/>
-      <c r="H35" s="22" t="s">
+      <c r="H35" s="9"/>
+      <c r="I35" s="22" t="s">
         <v>155</v>
       </c>
-      <c r="I35" s="8"/>
-      <c r="J35" s="8">
+      <c r="J35" s="8"/>
+      <c r="K35" s="8">
         <v>26</v>
       </c>
-      <c r="K35" s="8">
+      <c r="L35" s="8">
         <v>2000003</v>
       </c>
-      <c r="L35" s="13">
-        <v>0</v>
-      </c>
       <c r="M35" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N35" s="13">
         <v>1</v>
@@ -4685,50 +4375,54 @@
         <v>1</v>
       </c>
       <c r="P35" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q35" s="13">
-        <v>1</v>
-      </c>
-      <c r="R35" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="R35" s="13">
+        <v>1</v>
+      </c>
+      <c r="S35" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="S35" s="9" t="s">
+      <c r="T35" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="T35" s="13">
-        <v>1</v>
-      </c>
-      <c r="U35" s="9"/>
-      <c r="V35" s="13">
+      <c r="U35" s="13">
+        <v>1</v>
+      </c>
+      <c r="V35" s="9"/>
+      <c r="W35" s="13">
         <v>2</v>
       </c>
-      <c r="W35" s="13">
-        <v>0</v>
-      </c>
       <c r="X35" s="13">
-        <v>1</v>
-      </c>
-      <c r="Y35" s="13"/>
-      <c r="Z35" s="8"/>
-      <c r="AA35" s="13"/>
-      <c r="AB35" s="9"/>
+        <v>0</v>
+      </c>
+      <c r="Y35" s="13">
+        <v>1</v>
+      </c>
+      <c r="Z35" s="13"/>
+      <c r="AA35" s="8"/>
+      <c r="AB35" s="13"/>
       <c r="AC35" s="9"/>
-      <c r="AD35" s="13"/>
-      <c r="AE35" s="13"/>
+      <c r="AD35" s="9"/>
+      <c r="AE35" s="9"/>
       <c r="AF35" s="13"/>
-      <c r="AG35" s="20" t="s">
+      <c r="AG35" s="13"/>
+      <c r="AH35" s="13"/>
+      <c r="AI35" s="20" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="36" ht="20.1" customHeight="1"/>
+    <row r="36" spans="2:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <phoneticPr fontId="8" type="noConversion"/>
+  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Excel/SceneConfig.xlsx
+++ b/Excel/SceneConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6567A5D2-B78C-4CAE-80A5-0FCD6CFFE185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9AA1214-EF46-4450-81B1-9A7BEE0A7A35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SceneProto" sheetId="1" r:id="rId1"/>
@@ -987,9 +987,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>Green Valley Village</t>
-  </si>
-  <si>
     <t>Desert Domain</t>
   </si>
   <si>
@@ -1000,9 +997,6 @@
   </si>
   <si>
     <t>Ancient Ruins</t>
-  </si>
-  <si>
-    <t>Scorching Melted Flame</t>
   </si>
   <si>
     <t>Treasure Land</t>
@@ -1076,6 +1070,14 @@
   </si>
   <si>
     <t>In people's eyes, there is something very mysterious in this area. Dear adventurer, are you ready to start the exploration?</t>
+  </si>
+  <si>
+    <t>Green Valley</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Scorching Flame</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1915,7 +1917,7 @@
         <v>55</v>
       </c>
       <c r="AD4" s="6" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="AE4" s="6" t="s">
         <v>56</v>
@@ -2043,7 +2045,7 @@
         <v>65</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F6" s="9"/>
       <c r="G6" s="9"/>
@@ -2129,7 +2131,7 @@
         <v>73</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>190</v>
+        <v>218</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>74</v>
@@ -2198,7 +2200,7 @@
         <v>82</v>
       </c>
       <c r="AD7" s="9" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="AE7" s="9"/>
       <c r="AF7" s="13">
@@ -2223,7 +2225,7 @@
         <v>84</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>85</v>
@@ -2292,7 +2294,7 @@
         <v>82</v>
       </c>
       <c r="AD8" s="9" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="AE8" s="9"/>
       <c r="AF8" s="13">
@@ -2317,7 +2319,7 @@
         <v>94</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>95</v>
@@ -2386,7 +2388,7 @@
         <v>82</v>
       </c>
       <c r="AD9" s="9" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="AE9" s="9"/>
       <c r="AF9" s="13">
@@ -2411,7 +2413,7 @@
         <v>104</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>105</v>
@@ -2480,7 +2482,7 @@
         <v>82</v>
       </c>
       <c r="AD10" s="9" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="AE10" s="9"/>
       <c r="AF10" s="13">
@@ -2505,7 +2507,7 @@
         <v>114</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>115</v>
@@ -2574,7 +2576,7 @@
         <v>82</v>
       </c>
       <c r="AD11" s="9" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="AE11" s="9"/>
       <c r="AF11" s="13">
@@ -2599,7 +2601,7 @@
         <v>123</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>195</v>
+        <v>219</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>124</v>
@@ -2668,7 +2670,7 @@
         <v>82</v>
       </c>
       <c r="AD12" s="9" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="AE12" s="9"/>
       <c r="AF12" s="13">
@@ -2693,7 +2695,7 @@
         <v>131</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F13" s="9"/>
       <c r="G13" s="9"/>
@@ -2769,7 +2771,7 @@
         <v>136</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F14" s="9"/>
       <c r="G14" s="9"/>
@@ -2843,7 +2845,7 @@
         <v>140</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F15" s="9"/>
       <c r="G15" s="9"/>
@@ -2915,7 +2917,7 @@
         <v>140</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F16" s="9"/>
       <c r="G16" s="9"/>
@@ -2988,7 +2990,7 @@
         <v>145</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F17" s="9"/>
       <c r="G17" s="9"/>
@@ -3067,7 +3069,7 @@
         <v>150</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F18" s="9"/>
       <c r="G18" s="9"/>
@@ -3146,7 +3148,7 @@
         <v>154</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F19" s="9"/>
       <c r="G19" s="9"/>
@@ -3222,7 +3224,7 @@
         <v>158</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F20" s="9"/>
       <c r="G20" s="9"/>
@@ -3308,7 +3310,7 @@
         <v>163</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F21" s="9"/>
       <c r="G21" s="9"/>
@@ -3380,7 +3382,7 @@
         <v>164</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F22" s="9"/>
       <c r="G22" s="9"/>
@@ -3452,7 +3454,7 @@
         <v>165</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F23" s="9"/>
       <c r="G23" s="9"/>
@@ -3523,7 +3525,7 @@
         <v>167</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F24" s="9"/>
       <c r="G24" s="9"/>
@@ -3602,7 +3604,7 @@
         <v>172</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F25" s="9"/>
       <c r="G25" s="9"/>
@@ -3682,7 +3684,7 @@
         <v>175</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F26" s="9"/>
       <c r="G26" s="9"/>
@@ -3756,7 +3758,7 @@
         <v>175</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F27" s="9"/>
       <c r="G27" s="9"/>
@@ -3829,7 +3831,7 @@
         <v>176</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F28" s="9"/>
       <c r="G28" s="9"/>
@@ -3907,7 +3909,7 @@
         <v>180</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F29" s="12"/>
       <c r="G29" s="12"/>
@@ -3983,7 +3985,7 @@
         <v>182</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F30" s="12"/>
       <c r="G30" s="12"/>
@@ -4057,7 +4059,7 @@
         <v>183</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F31" s="9"/>
       <c r="G31" s="9"/>
@@ -4131,7 +4133,7 @@
         <v>184</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F32" s="9"/>
       <c r="G32" s="9"/>
@@ -4205,7 +4207,7 @@
         <v>185</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F33" s="9"/>
       <c r="G33" s="9"/>
@@ -4277,7 +4279,7 @@
         <v>186</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F34" s="9"/>
       <c r="G34" s="9"/>
@@ -4350,7 +4352,7 @@
         <v>187</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F35" s="9"/>
       <c r="G35" s="9"/>

--- a/Excel/SceneConfig.xlsx
+++ b/Excel/SceneConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9AA1214-EF46-4450-81B1-9A7BEE0A7A35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9E30608-A6F0-4DC0-9C93-DC6279891DBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1008,9 +1008,6 @@
     <t>Challenging Land</t>
   </si>
   <si>
-    <t>Family Championship Map</t>
-  </si>
-  <si>
     <t>Family Map</t>
   </si>
   <si>
@@ -1039,12 +1036,6 @@
   </si>
   <si>
     <t>Warrior Battle</t>
-  </si>
-  <si>
-    <t>Animal Running Competition</t>
-  </si>
-  <si>
-    <t>Demon Activity Map</t>
   </si>
   <si>
     <t>Seal Tower</t>
@@ -1077,6 +1068,18 @@
   </si>
   <si>
     <t>Scorching Flame</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Animal Running</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Demon Activity</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Family Fight</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -1699,7 +1702,8 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="3" max="3" width="17.5" customWidth="1"/>
-    <col min="4" max="5" width="16.125" customWidth="1"/>
+    <col min="4" max="4" width="16.125" customWidth="1"/>
+    <col min="5" max="5" width="26.75" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="17.125" customWidth="1"/>
     <col min="8" max="8" width="16.75" customWidth="1"/>
     <col min="9" max="9" width="13.25" customWidth="1"/>
@@ -1917,7 +1921,7 @@
         <v>55</v>
       </c>
       <c r="AD4" s="6" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="AE4" s="6" t="s">
         <v>56</v>
@@ -2045,7 +2049,7 @@
         <v>65</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F6" s="9"/>
       <c r="G6" s="9"/>
@@ -2131,7 +2135,7 @@
         <v>73</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>74</v>
@@ -2200,7 +2204,7 @@
         <v>82</v>
       </c>
       <c r="AD7" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="AE7" s="9"/>
       <c r="AF7" s="13">
@@ -2294,7 +2298,7 @@
         <v>82</v>
       </c>
       <c r="AD8" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="AE8" s="9"/>
       <c r="AF8" s="13">
@@ -2388,7 +2392,7 @@
         <v>82</v>
       </c>
       <c r="AD9" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="AE9" s="9"/>
       <c r="AF9" s="13">
@@ -2482,7 +2486,7 @@
         <v>82</v>
       </c>
       <c r="AD10" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="AE10" s="9"/>
       <c r="AF10" s="13">
@@ -2576,7 +2580,7 @@
         <v>82</v>
       </c>
       <c r="AD11" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="AE11" s="9"/>
       <c r="AF11" s="13">
@@ -2601,7 +2605,7 @@
         <v>123</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>124</v>
@@ -2670,7 +2674,7 @@
         <v>82</v>
       </c>
       <c r="AD12" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="AE12" s="9"/>
       <c r="AF12" s="13">
@@ -2990,7 +2994,7 @@
         <v>145</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="F17" s="9"/>
       <c r="G17" s="9"/>
@@ -3069,7 +3073,7 @@
         <v>150</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F18" s="9"/>
       <c r="G18" s="9"/>
@@ -3148,7 +3152,7 @@
         <v>154</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F19" s="9"/>
       <c r="G19" s="9"/>
@@ -3224,7 +3228,7 @@
         <v>158</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F20" s="9"/>
       <c r="G20" s="9"/>
@@ -3310,7 +3314,7 @@
         <v>163</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F21" s="9"/>
       <c r="G21" s="9"/>
@@ -3382,7 +3386,7 @@
         <v>164</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F22" s="9"/>
       <c r="G22" s="9"/>
@@ -3454,7 +3458,7 @@
         <v>165</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F23" s="9"/>
       <c r="G23" s="9"/>
@@ -3525,7 +3529,7 @@
         <v>167</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F24" s="9"/>
       <c r="G24" s="9"/>
@@ -3604,7 +3608,7 @@
         <v>172</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F25" s="9"/>
       <c r="G25" s="9"/>
@@ -3684,7 +3688,7 @@
         <v>175</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F26" s="9"/>
       <c r="G26" s="9"/>
@@ -3758,7 +3762,7 @@
         <v>175</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F27" s="9"/>
       <c r="G27" s="9"/>
@@ -3831,7 +3835,7 @@
         <v>176</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F28" s="9"/>
       <c r="G28" s="9"/>
@@ -3909,7 +3913,7 @@
         <v>180</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="F29" s="12"/>
       <c r="G29" s="12"/>
@@ -3985,7 +3989,7 @@
         <v>182</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="F30" s="12"/>
       <c r="G30" s="12"/>
@@ -4059,7 +4063,7 @@
         <v>183</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F31" s="9"/>
       <c r="G31" s="9"/>
@@ -4133,7 +4137,7 @@
         <v>184</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F32" s="9"/>
       <c r="G32" s="9"/>
@@ -4207,7 +4211,7 @@
         <v>185</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F33" s="9"/>
       <c r="G33" s="9"/>
@@ -4279,7 +4283,7 @@
         <v>186</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F34" s="9"/>
       <c r="G34" s="9"/>
@@ -4352,7 +4356,7 @@
         <v>187</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F35" s="9"/>
       <c r="G35" s="9"/>

--- a/Excel/SceneConfig.xlsx
+++ b/Excel/SceneConfig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9E30608-A6F0-4DC0-9C93-DC6279891DBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCF514FD-ABDF-4E89-97C1-4D748700D83A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -286,7 +286,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="224">
   <si>
     <t>c</t>
   </si>
@@ -651,9 +651,6 @@
     <t>60,69</t>
   </si>
   <si>
-    <t>40001</t>
-  </si>
-  <si>
     <t>35,89,10,0,90</t>
   </si>
   <si>
@@ -669,13 +666,7 @@
     <t>15545,2978,25967</t>
   </si>
   <si>
-    <t>70</t>
-  </si>
-  <si>
     <t>70,70</t>
-  </si>
-  <si>
-    <t>41001</t>
   </si>
   <si>
     <t>142,89,81.8,0,190</t>
@@ -1080,6 +1071,34 @@
   </si>
   <si>
     <t>Family Fight</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰蚀幽城</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Frostveil</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>ImgBig_17</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>110006</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>68</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>72</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>72,72</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -1267,7 +1286,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1341,6 +1360,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1698,7 +1720,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:AI36"/>
+  <dimension ref="B2:AI37"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="3" max="3" width="17.5" customWidth="1"/>
@@ -1728,13 +1750,13 @@
   <sheetData>
     <row r="2" spans="2:35" x14ac:dyDescent="0.15">
       <c r="E2" s="4" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>0</v>
       </c>
       <c r="AD2" s="4" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" spans="2:35" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -1846,7 +1868,7 @@
         <v>31</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>32</v>
@@ -1921,7 +1943,7 @@
         <v>55</v>
       </c>
       <c r="AD4" s="6" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="AE4" s="6" t="s">
         <v>56</v>
@@ -2049,7 +2071,7 @@
         <v>65</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F6" s="9"/>
       <c r="G6" s="9"/>
@@ -2135,7 +2157,7 @@
         <v>73</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>74</v>
@@ -2204,7 +2226,7 @@
         <v>82</v>
       </c>
       <c r="AD7" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AE7" s="9"/>
       <c r="AF7" s="13">
@@ -2229,7 +2251,7 @@
         <v>84</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>85</v>
@@ -2298,7 +2320,7 @@
         <v>82</v>
       </c>
       <c r="AD8" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AE8" s="9"/>
       <c r="AF8" s="13">
@@ -2323,7 +2345,7 @@
         <v>94</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>95</v>
@@ -2392,7 +2414,7 @@
         <v>82</v>
       </c>
       <c r="AD9" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AE9" s="9"/>
       <c r="AF9" s="13">
@@ -2417,7 +2439,7 @@
         <v>104</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>105</v>
@@ -2486,7 +2508,7 @@
         <v>82</v>
       </c>
       <c r="AD10" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AE10" s="9"/>
       <c r="AF10" s="13">
@@ -2511,7 +2533,7 @@
         <v>114</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>115</v>
@@ -2573,14 +2595,14 @@
         <v>72005013</v>
       </c>
       <c r="AA11" s="9"/>
-      <c r="AB11" s="9" t="s">
-        <v>121</v>
+      <c r="AB11" s="27">
+        <v>40001</v>
       </c>
       <c r="AC11" s="9" t="s">
         <v>82</v>
       </c>
       <c r="AD11" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AE11" s="9"/>
       <c r="AF11" s="13">
@@ -2593,7 +2615,7 @@
         <v>601500501</v>
       </c>
       <c r="AI11" s="20" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -2602,20 +2624,20 @@
         <v>110006</v>
       </c>
       <c r="D12" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="F12" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="E12" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="F12" s="9" t="s">
+      <c r="G12" s="9" t="s">
         <v>124</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>125</v>
       </c>
       <c r="H12" s="9"/>
       <c r="I12" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J12" s="14"/>
       <c r="K12" s="15">
@@ -2646,13 +2668,13 @@
         <v>118</v>
       </c>
       <c r="T12" s="9" t="s">
-        <v>127</v>
+        <v>221</v>
       </c>
       <c r="U12" s="9" t="s">
-        <v>127</v>
+        <v>221</v>
       </c>
       <c r="V12" s="9" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="W12" s="13">
         <v>2</v>
@@ -2667,14 +2689,14 @@
         <v>72006013</v>
       </c>
       <c r="AA12" s="9"/>
-      <c r="AB12" s="9" t="s">
-        <v>129</v>
+      <c r="AB12" s="27">
+        <v>41001</v>
       </c>
       <c r="AC12" s="9" t="s">
         <v>82</v>
       </c>
       <c r="AD12" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AE12" s="9"/>
       <c r="AF12" s="13">
@@ -2687,35 +2709,39 @@
         <v>601500501</v>
       </c>
       <c r="AI12" s="20" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13"/>
       <c r="C13" s="8">
-        <v>2000001</v>
+        <v>110007</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>131</v>
+        <v>217</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
+        <v>218</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>220</v>
+      </c>
       <c r="H13" s="9"/>
       <c r="I13" s="22" t="s">
-        <v>132</v>
-      </c>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8">
-        <v>7</v>
+        <v>125</v>
+      </c>
+      <c r="J13" s="14"/>
+      <c r="K13" s="15">
+        <v>5</v>
       </c>
       <c r="L13" s="8">
-        <v>2000001</v>
+        <v>2000012</v>
       </c>
       <c r="M13" s="16" t="s">
-        <v>133</v>
+        <v>108</v>
       </c>
       <c r="N13" s="13">
         <v>1</v>
@@ -2724,26 +2750,28 @@
         <v>0</v>
       </c>
       <c r="P13" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q13" s="13">
         <v>0</v>
       </c>
       <c r="R13" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" s="9" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="T13" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="U13" s="13">
-        <v>1</v>
-      </c>
-      <c r="V13" s="9"/>
+        <v>222</v>
+      </c>
+      <c r="U13" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="V13" s="9" t="s">
+        <v>223</v>
+      </c>
       <c r="W13" s="13">
-        <v>300</v>
+        <v>2</v>
       </c>
       <c r="X13" s="13">
         <v>0</v>
@@ -2751,47 +2779,59 @@
       <c r="Y13" s="13">
         <v>0</v>
       </c>
-      <c r="Z13" s="13"/>
-      <c r="AA13" s="19" t="s">
-        <v>134</v>
-      </c>
-      <c r="AB13" s="9"/>
-      <c r="AC13" s="9"/>
-      <c r="AD13" s="9"/>
+      <c r="Z13" s="13">
+        <v>72006013</v>
+      </c>
+      <c r="AA13" s="9"/>
+      <c r="AB13" s="27">
+        <v>41001</v>
+      </c>
+      <c r="AC13" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="AD13" s="9" t="s">
+        <v>211</v>
+      </c>
       <c r="AE13" s="9"/>
-      <c r="AF13" s="13"/>
-      <c r="AG13" s="13"/>
-      <c r="AH13" s="13"/>
-      <c r="AI13" s="23" t="s">
-        <v>135</v>
+      <c r="AF13" s="13">
+        <v>206000</v>
+      </c>
+      <c r="AG13" s="13">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="13">
+        <v>601500501</v>
+      </c>
+      <c r="AI13" s="20" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="14" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14"/>
       <c r="C14" s="8">
-        <v>2000002</v>
+        <v>2000001</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="F14" s="9"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
       <c r="I14" s="22" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="J14" s="8"/>
       <c r="K14" s="8">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="L14" s="8">
-        <v>2000002</v>
+        <v>2000001</v>
       </c>
       <c r="M14" s="16" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="N14" s="13">
         <v>1</v>
@@ -2800,7 +2840,7 @@
         <v>0</v>
       </c>
       <c r="P14" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q14" s="13">
         <v>0</v>
@@ -2809,7 +2849,7 @@
         <v>1</v>
       </c>
       <c r="S14" s="9" t="s">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="T14" s="9" t="s">
         <v>70</v>
@@ -2819,7 +2859,7 @@
       </c>
       <c r="V14" s="9"/>
       <c r="W14" s="13">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="X14" s="13">
         <v>0</v>
@@ -2828,62 +2868,64 @@
         <v>0</v>
       </c>
       <c r="Z14" s="13"/>
-      <c r="AA14" s="8"/>
-      <c r="AB14" s="13"/>
+      <c r="AA14" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="AB14" s="9"/>
       <c r="AC14" s="9"/>
       <c r="AD14" s="9"/>
       <c r="AE14" s="9"/>
       <c r="AF14" s="13"/>
       <c r="AG14" s="13"/>
       <c r="AH14" s="13"/>
-      <c r="AI14" s="20" t="s">
-        <v>139</v>
+      <c r="AI14" s="23" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="15" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15"/>
       <c r="C15" s="8">
-        <v>2000003</v>
+        <v>2000002</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="F15" s="9"/>
       <c r="G15" s="9"/>
       <c r="H15" s="9"/>
       <c r="I15" s="22" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="J15" s="8"/>
       <c r="K15" s="8">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="L15" s="8">
-        <v>2000003</v>
+        <v>2000002</v>
       </c>
       <c r="M15" s="16" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="N15" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P15" s="13">
         <v>0</v>
       </c>
       <c r="Q15" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" s="13">
         <v>1</v>
       </c>
       <c r="S15" s="9" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="T15" s="9" t="s">
         <v>70</v>
@@ -2893,10 +2935,10 @@
       </c>
       <c r="V15" s="9"/>
       <c r="W15" s="13">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="X15" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y15" s="13">
         <v>0</v>
@@ -2910,24 +2952,26 @@
       <c r="AF15" s="13"/>
       <c r="AG15" s="13"/>
       <c r="AH15" s="13"/>
-      <c r="AI15" s="20"/>
+      <c r="AI15" s="20" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="16" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16"/>
       <c r="C16" s="8">
-        <v>2000004</v>
+        <v>2000003</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F16" s="9"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
       <c r="I16" s="22" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="J16" s="8"/>
       <c r="K16" s="8">
@@ -2937,7 +2981,7 @@
         <v>2000003</v>
       </c>
       <c r="M16" s="16" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="N16" s="13">
         <v>0</v>
@@ -2955,7 +2999,7 @@
         <v>1</v>
       </c>
       <c r="S16" s="9" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="T16" s="9" t="s">
         <v>70</v>
@@ -2965,7 +3009,7 @@
       </c>
       <c r="V16" s="9"/>
       <c r="W16" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X16" s="13">
         <v>1</v>
@@ -2974,9 +3018,7 @@
         <v>0</v>
       </c>
       <c r="Z16" s="13"/>
-      <c r="AA16" s="8" t="s">
-        <v>144</v>
-      </c>
+      <c r="AA16" s="8"/>
       <c r="AB16" s="13"/>
       <c r="AC16" s="9"/>
       <c r="AD16" s="9"/>
@@ -2986,73 +3028,70 @@
       <c r="AH16" s="13"/>
       <c r="AI16" s="20"/>
     </row>
-    <row r="17" spans="2:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B17"/>
       <c r="C17" s="8">
-        <v>2000008</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>219</v>
+        <v>2000004</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>193</v>
       </c>
       <c r="F17" s="9"/>
       <c r="G17" s="9"/>
       <c r="H17" s="9"/>
       <c r="I17" s="22" t="s">
-        <v>146</v>
-      </c>
-      <c r="J17" s="8">
-        <v>20000038</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="J17" s="8"/>
       <c r="K17" s="8">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="L17" s="8">
-        <v>2000008</v>
+        <v>2000003</v>
       </c>
       <c r="M17" s="16" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="N17" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P17" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" s="13">
         <v>1</v>
       </c>
       <c r="S17" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="T17" s="9" t="s">
         <v>70</v>
       </c>
       <c r="U17" s="13">
-        <v>12</v>
-      </c>
-      <c r="V17" s="9" t="s">
-        <v>147</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="V17" s="9"/>
       <c r="W17" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X17" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y17" s="13">
         <v>0</v>
       </c>
       <c r="Z17" s="13"/>
       <c r="AA17" s="8" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="AB17" s="13"/>
       <c r="AC17" s="9"/>
@@ -3061,43 +3100,41 @@
       <c r="AF17" s="13"/>
       <c r="AG17" s="13"/>
       <c r="AH17" s="13"/>
-      <c r="AI17" s="23" t="s">
-        <v>149</v>
-      </c>
+      <c r="AI17" s="20"/>
     </row>
     <row r="18" spans="2:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C18" s="8">
-        <v>2000009</v>
+        <v>2000008</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>197</v>
+        <v>216</v>
       </c>
       <c r="F18" s="9"/>
       <c r="G18" s="9"/>
       <c r="H18" s="9"/>
       <c r="I18" s="22" t="s">
-        <v>151</v>
-      </c>
-      <c r="J18" s="24" t="s">
-        <v>152</v>
+        <v>143</v>
+      </c>
+      <c r="J18" s="8">
+        <v>20000038</v>
       </c>
       <c r="K18" s="8">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L18" s="8">
-        <v>2000009</v>
+        <v>2000008</v>
       </c>
       <c r="M18" s="16" t="s">
-        <v>153</v>
+        <v>130</v>
       </c>
       <c r="N18" s="13">
         <v>1</v>
       </c>
       <c r="O18" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P18" s="13">
         <v>1</v>
@@ -3109,7 +3146,7 @@
         <v>1</v>
       </c>
       <c r="S18" s="9" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="T18" s="9" t="s">
         <v>70</v>
@@ -3118,7 +3155,7 @@
         <v>12</v>
       </c>
       <c r="V18" s="9" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="W18" s="13">
         <v>0</v>
@@ -3129,10 +3166,10 @@
       <c r="Y18" s="13">
         <v>0</v>
       </c>
-      <c r="Z18" s="13">
-        <v>72005013</v>
-      </c>
-      <c r="AA18" s="8"/>
+      <c r="Z18" s="13"/>
+      <c r="AA18" s="8" t="s">
+        <v>145</v>
+      </c>
       <c r="AB18" s="13"/>
       <c r="AC18" s="9"/>
       <c r="AD18" s="9"/>
@@ -3141,34 +3178,36 @@
       <c r="AG18" s="13"/>
       <c r="AH18" s="13"/>
       <c r="AI18" s="23" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="19" spans="2:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C19" s="8">
-        <v>2000010</v>
+        <v>2000009</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="F19" s="9"/>
       <c r="G19" s="9"/>
       <c r="H19" s="9"/>
       <c r="I19" s="22" t="s">
-        <v>155</v>
-      </c>
-      <c r="J19" s="8"/>
+        <v>148</v>
+      </c>
+      <c r="J19" s="24" t="s">
+        <v>149</v>
+      </c>
       <c r="K19" s="8">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L19" s="8">
-        <v>2000003</v>
-      </c>
-      <c r="M19" s="13">
-        <v>0</v>
+        <v>2000009</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>150</v>
       </c>
       <c r="N19" s="13">
         <v>1</v>
@@ -3186,28 +3225,30 @@
         <v>1</v>
       </c>
       <c r="S19" s="9" t="s">
-        <v>142</v>
+        <v>109</v>
       </c>
       <c r="T19" s="9" t="s">
         <v>70</v>
       </c>
       <c r="U19" s="13">
-        <v>1</v>
-      </c>
-      <c r="V19" s="9"/>
+        <v>12</v>
+      </c>
+      <c r="V19" s="9" t="s">
+        <v>144</v>
+      </c>
       <c r="W19" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X19" s="13">
         <v>0</v>
       </c>
       <c r="Y19" s="13">
-        <v>1</v>
-      </c>
-      <c r="Z19" s="13"/>
-      <c r="AA19" s="8" t="s">
-        <v>156</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Z19" s="13">
+        <v>72005013</v>
+      </c>
+      <c r="AA19" s="8"/>
       <c r="AB19" s="13"/>
       <c r="AC19" s="9"/>
       <c r="AD19" s="9"/>
@@ -3215,35 +3256,32 @@
       <c r="AF19" s="13"/>
       <c r="AG19" s="13"/>
       <c r="AH19" s="13"/>
-      <c r="AI19" s="20" t="s">
-        <v>157</v>
+      <c r="AI19" s="23" t="s">
+        <v>146</v>
       </c>
     </row>
-    <row r="20" spans="2:35" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B20"/>
+    <row r="20" spans="2:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C20" s="8">
-        <v>2000011</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>199</v>
+        <v>2000010</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>195</v>
       </c>
       <c r="F20" s="9"/>
       <c r="G20" s="9"/>
       <c r="H20" s="9"/>
       <c r="I20" s="22" t="s">
-        <v>159</v>
-      </c>
-      <c r="J20" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="K20" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="L20" s="13">
-        <v>102</v>
+        <v>152</v>
+      </c>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8">
+        <v>19</v>
+      </c>
+      <c r="L20" s="8">
+        <v>2000003</v>
       </c>
       <c r="M20" s="13">
         <v>0</v>
@@ -3252,10 +3290,10 @@
         <v>1</v>
       </c>
       <c r="O20" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P20" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q20" s="13">
         <v>0</v>
@@ -3264,79 +3302,73 @@
         <v>1</v>
       </c>
       <c r="S20" s="9" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="T20" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="U20" s="13">
-        <v>10</v>
-      </c>
-      <c r="V20" s="9" t="s">
-        <v>71</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="V20" s="9"/>
       <c r="W20" s="13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X20" s="13">
         <v>0</v>
       </c>
       <c r="Y20" s="13">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="13">
-        <v>0</v>
-      </c>
-      <c r="AA20" s="9"/>
-      <c r="AB20" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="Z20" s="13"/>
+      <c r="AA20" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="AB20" s="13"/>
       <c r="AC20" s="9"/>
       <c r="AD20" s="9"/>
       <c r="AE20" s="9"/>
-      <c r="AF20" s="13">
-        <v>0</v>
-      </c>
-      <c r="AG20" s="13">
-        <v>0</v>
-      </c>
-      <c r="AH20" s="13">
-        <v>0</v>
-      </c>
+      <c r="AF20" s="13"/>
+      <c r="AG20" s="13"/>
+      <c r="AH20" s="13"/>
       <c r="AI20" s="20" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
-    <row r="21" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:35" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21"/>
       <c r="C21" s="8">
-        <v>2100001</v>
+        <v>2000011</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F21" s="9"/>
       <c r="G21" s="9"/>
       <c r="H21" s="9"/>
       <c r="I21" s="22" t="s">
-        <v>141</v>
-      </c>
-      <c r="J21" s="8"/>
-      <c r="K21" s="8">
-        <v>6</v>
-      </c>
-      <c r="L21" s="8">
-        <v>100001</v>
+        <v>156</v>
+      </c>
+      <c r="J21" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="K21" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="L21" s="13">
+        <v>102</v>
       </c>
       <c r="M21" s="13">
         <v>0</v>
       </c>
       <c r="N21" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O21" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P21" s="13">
         <v>0</v>
@@ -3348,55 +3380,67 @@
         <v>1</v>
       </c>
       <c r="S21" s="9" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="T21" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="U21" s="13">
-        <v>1</v>
-      </c>
-      <c r="V21" s="9"/>
+        <v>10</v>
+      </c>
+      <c r="V21" s="9" t="s">
+        <v>71</v>
+      </c>
       <c r="W21" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X21" s="13">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y21" s="13">
         <v>0</v>
       </c>
-      <c r="Z21" s="13"/>
-      <c r="AA21" s="8"/>
-      <c r="AB21" s="13"/>
+      <c r="Z21" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="9"/>
+      <c r="AB21" s="9"/>
       <c r="AC21" s="9"/>
       <c r="AD21" s="9"/>
       <c r="AE21" s="9"/>
-      <c r="AF21" s="13"/>
-      <c r="AG21" s="13"/>
-      <c r="AH21" s="13"/>
-      <c r="AI21" s="20"/>
+      <c r="AF21" s="13">
+        <v>0</v>
+      </c>
+      <c r="AG21" s="13">
+        <v>0</v>
+      </c>
+      <c r="AH21" s="13">
+        <v>0</v>
+      </c>
+      <c r="AI21" s="20" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="22" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22"/>
       <c r="C22" s="8">
-        <v>2100002</v>
+        <v>2100001</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="F22" s="9"/>
       <c r="G22" s="9"/>
       <c r="H22" s="9"/>
       <c r="I22" s="22" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="J22" s="8"/>
       <c r="K22" s="8">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L22" s="8">
         <v>100001</v>
@@ -3420,7 +3464,7 @@
         <v>1</v>
       </c>
       <c r="S22" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="T22" s="9" t="s">
         <v>70</v>
@@ -3433,7 +3477,7 @@
         <v>1</v>
       </c>
       <c r="X22" s="13">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Y22" s="13">
         <v>0</v>
@@ -3452,26 +3496,26 @@
     <row r="23" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23"/>
       <c r="C23" s="8">
-        <v>2200001</v>
+        <v>2100002</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F23" s="9"/>
       <c r="G23" s="9"/>
       <c r="H23" s="9"/>
       <c r="I23" s="22" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="J23" s="8"/>
       <c r="K23" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L23" s="8">
-        <v>10007</v>
+        <v>100001</v>
       </c>
       <c r="M23" s="13">
         <v>0</v>
@@ -3492,7 +3536,7 @@
         <v>1</v>
       </c>
       <c r="S23" s="9" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="T23" s="9" t="s">
         <v>70</v>
@@ -3505,14 +3549,14 @@
         <v>1</v>
       </c>
       <c r="X23" s="13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Y23" s="13">
         <v>0</v>
       </c>
       <c r="Z23" s="13"/>
-      <c r="AA23" s="9"/>
-      <c r="AB23" s="9"/>
+      <c r="AA23" s="8"/>
+      <c r="AB23" s="13"/>
       <c r="AC23" s="9"/>
       <c r="AD23" s="9"/>
       <c r="AE23" s="9"/>
@@ -3521,42 +3565,41 @@
       <c r="AH23" s="13"/>
       <c r="AI23" s="20"/>
     </row>
-    <row r="24" spans="2:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B24"/>
       <c r="C24" s="8">
-        <v>3000001</v>
+        <v>2200001</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F24" s="9"/>
       <c r="G24" s="9"/>
       <c r="H24" s="9"/>
       <c r="I24" s="22" t="s">
-        <v>168</v>
-      </c>
-      <c r="J24" s="17" t="s">
-        <v>169</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="J24" s="8"/>
       <c r="K24" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L24" s="8">
-        <v>201</v>
+        <v>10007</v>
       </c>
       <c r="M24" s="13">
         <v>0</v>
       </c>
       <c r="N24" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O24" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P24" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="13">
         <v>0</v>
@@ -3565,19 +3608,17 @@
         <v>1</v>
       </c>
       <c r="S24" s="9" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="T24" s="9" t="s">
         <v>70</v>
       </c>
       <c r="U24" s="13">
-        <v>10</v>
-      </c>
-      <c r="V24" s="9" t="s">
-        <v>170</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="V24" s="9"/>
       <c r="W24" s="13">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="X24" s="13">
         <v>0</v>
@@ -3586,38 +3627,34 @@
         <v>0</v>
       </c>
       <c r="Z24" s="13"/>
-      <c r="AA24" s="8"/>
-      <c r="AB24" s="25" t="s">
-        <v>171</v>
-      </c>
+      <c r="AA24" s="9"/>
+      <c r="AB24" s="9"/>
       <c r="AC24" s="9"/>
       <c r="AD24" s="9"/>
       <c r="AE24" s="9"/>
       <c r="AF24" s="13"/>
       <c r="AG24" s="13"/>
       <c r="AH24" s="13"/>
-      <c r="AI24" s="20" t="s">
-        <v>157</v>
-      </c>
+      <c r="AI24" s="20"/>
     </row>
     <row r="25" spans="2:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C25" s="8">
-        <v>3000002</v>
+        <v>3000001</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F25" s="9"/>
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
       <c r="I25" s="22" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="J25" s="17" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="K25" s="8">
         <v>12</v>
@@ -3644,16 +3681,16 @@
         <v>1</v>
       </c>
       <c r="S25" s="9" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="T25" s="9" t="s">
         <v>70</v>
       </c>
       <c r="U25" s="13">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="V25" s="9" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="W25" s="13">
         <v>40</v>
@@ -3667,7 +3704,7 @@
       <c r="Z25" s="13"/>
       <c r="AA25" s="8"/>
       <c r="AB25" s="25" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AC25" s="9"/>
       <c r="AD25" s="9"/>
@@ -3676,44 +3713,45 @@
       <c r="AG25" s="13"/>
       <c r="AH25" s="13"/>
       <c r="AI25" s="20" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
-    <row r="26" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B26"/>
+    <row r="26" spans="2:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C26" s="8">
-        <v>4000001</v>
+        <v>3000002</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="F26" s="9"/>
       <c r="G26" s="9"/>
       <c r="H26" s="9"/>
       <c r="I26" s="22" t="s">
-        <v>141</v>
-      </c>
-      <c r="J26" s="8"/>
+        <v>165</v>
+      </c>
+      <c r="J26" s="17" t="s">
+        <v>166</v>
+      </c>
       <c r="K26" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L26" s="8">
-        <v>2000004</v>
+        <v>201</v>
       </c>
       <c r="M26" s="13">
         <v>0</v>
       </c>
       <c r="N26" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O26" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P26" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q26" s="13">
         <v>0</v>
@@ -3722,17 +3760,19 @@
         <v>1</v>
       </c>
       <c r="S26" s="9" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="T26" s="9" t="s">
         <v>70</v>
       </c>
       <c r="U26" s="13">
-        <v>10</v>
-      </c>
-      <c r="V26" s="9"/>
+        <v>30</v>
+      </c>
+      <c r="V26" s="9" t="s">
+        <v>170</v>
+      </c>
       <c r="W26" s="13">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="X26" s="13">
         <v>0</v>
@@ -3741,34 +3781,36 @@
         <v>0</v>
       </c>
       <c r="Z26" s="13"/>
-      <c r="AA26" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="AB26" s="13"/>
+      <c r="AA26" s="8"/>
+      <c r="AB26" s="25" t="s">
+        <v>171</v>
+      </c>
       <c r="AC26" s="9"/>
       <c r="AD26" s="9"/>
       <c r="AE26" s="9"/>
       <c r="AF26" s="13"/>
       <c r="AG26" s="13"/>
       <c r="AH26" s="13"/>
-      <c r="AI26" s="20"/>
+      <c r="AI26" s="20" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="27" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27"/>
       <c r="C27" s="8">
-        <v>5000001</v>
+        <v>4000001</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="F27" s="9"/>
       <c r="G27" s="9"/>
       <c r="H27" s="9"/>
       <c r="I27" s="22" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="J27" s="8"/>
       <c r="K27" s="8">
@@ -3796,7 +3838,7 @@
         <v>1</v>
       </c>
       <c r="S27" s="9" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="T27" s="9" t="s">
         <v>70</v>
@@ -3816,7 +3858,7 @@
       </c>
       <c r="Z27" s="13"/>
       <c r="AA27" s="8" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="AB27" s="13"/>
       <c r="AC27" s="9"/>
@@ -3827,40 +3869,41 @@
       <c r="AH27" s="13"/>
       <c r="AI27" s="20"/>
     </row>
-    <row r="28" spans="2:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B28"/>
       <c r="C28" s="8">
-        <v>6000001</v>
-      </c>
-      <c r="D28" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="E28" s="10" t="s">
-        <v>206</v>
+        <v>5000001</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>202</v>
       </c>
       <c r="F28" s="9"/>
       <c r="G28" s="9"/>
       <c r="H28" s="9"/>
       <c r="I28" s="22" t="s">
-        <v>177</v>
+        <v>138</v>
       </c>
       <c r="J28" s="8"/>
       <c r="K28" s="8">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L28" s="8">
-        <v>2000006</v>
+        <v>2000004</v>
       </c>
       <c r="M28" s="13">
         <v>0</v>
       </c>
       <c r="N28" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O28" s="13">
         <v>1</v>
       </c>
       <c r="P28" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q28" s="13">
         <v>0</v>
@@ -3869,19 +3912,17 @@
         <v>1</v>
       </c>
       <c r="S28" s="9" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="T28" s="9" t="s">
         <v>70</v>
       </c>
       <c r="U28" s="13">
-        <v>12</v>
-      </c>
-      <c r="V28" s="9" t="s">
-        <v>147</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="V28" s="9"/>
       <c r="W28" s="13">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X28" s="13">
         <v>0</v>
@@ -3891,7 +3932,7 @@
       </c>
       <c r="Z28" s="13"/>
       <c r="AA28" s="8" t="s">
-        <v>178</v>
+        <v>141</v>
       </c>
       <c r="AB28" s="13"/>
       <c r="AC28" s="9"/>
@@ -3900,106 +3941,105 @@
       <c r="AF28" s="13"/>
       <c r="AG28" s="13"/>
       <c r="AH28" s="13"/>
-      <c r="AI28" s="20" t="s">
-        <v>179</v>
-      </c>
+      <c r="AI28" s="20"/>
     </row>
-    <row r="29" spans="2:35" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B29"/>
-      <c r="C29" s="11">
-        <v>6000002</v>
-      </c>
-      <c r="D29" s="12" t="s">
-        <v>180</v>
-      </c>
-      <c r="E29" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="26" t="s">
-        <v>181</v>
-      </c>
-      <c r="J29" s="11"/>
-      <c r="K29" s="11">
-        <v>22</v>
-      </c>
-      <c r="L29" s="11">
-        <v>2000011</v>
-      </c>
-      <c r="M29" s="18">
-        <v>0</v>
-      </c>
-      <c r="N29" s="18">
-        <v>0</v>
-      </c>
-      <c r="O29" s="18">
-        <v>1</v>
-      </c>
-      <c r="P29" s="18">
-        <v>1</v>
-      </c>
-      <c r="Q29" s="18">
-        <v>0</v>
-      </c>
-      <c r="R29" s="18">
-        <v>1</v>
-      </c>
-      <c r="S29" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="T29" s="12" t="s">
+    <row r="29" spans="2:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C29" s="8">
+        <v>6000001</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="22" t="s">
+        <v>174</v>
+      </c>
+      <c r="J29" s="8"/>
+      <c r="K29" s="8">
+        <v>15</v>
+      </c>
+      <c r="L29" s="8">
+        <v>2000006</v>
+      </c>
+      <c r="M29" s="13">
+        <v>0</v>
+      </c>
+      <c r="N29" s="13">
+        <v>1</v>
+      </c>
+      <c r="O29" s="13">
+        <v>1</v>
+      </c>
+      <c r="P29" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q29" s="13">
+        <v>0</v>
+      </c>
+      <c r="R29" s="13">
+        <v>1</v>
+      </c>
+      <c r="S29" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="T29" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="U29" s="18">
-        <v>1</v>
-      </c>
-      <c r="V29" s="12"/>
-      <c r="W29" s="18">
-        <v>0</v>
-      </c>
-      <c r="X29" s="18">
-        <v>0</v>
-      </c>
-      <c r="Y29" s="18">
-        <v>1</v>
-      </c>
-      <c r="Z29" s="18"/>
-      <c r="AA29" s="11"/>
-      <c r="AB29" s="18">
-        <v>100101</v>
-      </c>
-      <c r="AC29" s="12"/>
-      <c r="AD29" s="12"/>
-      <c r="AE29" s="12"/>
-      <c r="AF29" s="18"/>
-      <c r="AG29" s="18"/>
-      <c r="AH29" s="18"/>
-      <c r="AI29" s="21" t="s">
-        <v>179</v>
+      <c r="U29" s="13">
+        <v>12</v>
+      </c>
+      <c r="V29" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="W29" s="13">
+        <v>100</v>
+      </c>
+      <c r="X29" s="13">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="13">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="13"/>
+      <c r="AA29" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="AB29" s="13"/>
+      <c r="AC29" s="9"/>
+      <c r="AD29" s="9"/>
+      <c r="AE29" s="9"/>
+      <c r="AF29" s="13"/>
+      <c r="AG29" s="13"/>
+      <c r="AH29" s="13"/>
+      <c r="AI29" s="20" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="30" spans="2:35" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30"/>
       <c r="C30" s="11">
-        <v>6000003</v>
+        <v>6000002</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="F30" s="12"/>
       <c r="G30" s="12"/>
       <c r="H30" s="12"/>
       <c r="I30" s="26" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="J30" s="11"/>
       <c r="K30" s="11">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L30" s="11">
         <v>2000011</v>
@@ -4023,7 +4063,7 @@
         <v>1</v>
       </c>
       <c r="S30" s="12" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="T30" s="12" t="s">
         <v>70</v>
@@ -4043,7 +4083,9 @@
       </c>
       <c r="Z30" s="18"/>
       <c r="AA30" s="11"/>
-      <c r="AB30" s="18"/>
+      <c r="AB30" s="18">
+        <v>100101</v>
+      </c>
       <c r="AC30" s="12"/>
       <c r="AD30" s="12"/>
       <c r="AE30" s="12"/>
@@ -4051,106 +4093,106 @@
       <c r="AG30" s="18"/>
       <c r="AH30" s="18"/>
       <c r="AI30" s="21" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="31" spans="2:35" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B31"/>
+      <c r="C31" s="11">
+        <v>6000003</v>
+      </c>
+      <c r="D31" s="12" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="31" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B31"/>
-      <c r="C31" s="8">
-        <v>7000001</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="22" t="s">
-        <v>141</v>
-      </c>
-      <c r="J31" s="8"/>
-      <c r="K31" s="8">
-        <v>20</v>
-      </c>
-      <c r="L31" s="8">
-        <v>2000004</v>
-      </c>
-      <c r="M31" s="13">
-        <v>0</v>
-      </c>
-      <c r="N31" s="13">
-        <v>0</v>
-      </c>
-      <c r="O31" s="13">
-        <v>1</v>
-      </c>
-      <c r="P31" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="13">
-        <v>0</v>
-      </c>
-      <c r="R31" s="13">
-        <v>1</v>
-      </c>
-      <c r="S31" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="T31" s="9" t="s">
+      <c r="E31" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="12"/>
+      <c r="I31" s="26" t="s">
+        <v>178</v>
+      </c>
+      <c r="J31" s="11"/>
+      <c r="K31" s="11">
+        <v>23</v>
+      </c>
+      <c r="L31" s="11">
+        <v>2000011</v>
+      </c>
+      <c r="M31" s="18">
+        <v>0</v>
+      </c>
+      <c r="N31" s="18">
+        <v>0</v>
+      </c>
+      <c r="O31" s="18">
+        <v>1</v>
+      </c>
+      <c r="P31" s="18">
+        <v>1</v>
+      </c>
+      <c r="Q31" s="18">
+        <v>0</v>
+      </c>
+      <c r="R31" s="18">
+        <v>1</v>
+      </c>
+      <c r="S31" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="T31" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="U31" s="13">
-        <v>1</v>
-      </c>
-      <c r="V31" s="9"/>
-      <c r="W31" s="13">
-        <v>0</v>
-      </c>
-      <c r="X31" s="13">
-        <v>0</v>
-      </c>
-      <c r="Y31" s="13">
-        <v>0</v>
-      </c>
-      <c r="Z31" s="13"/>
-      <c r="AA31" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="AB31" s="13"/>
-      <c r="AC31" s="9"/>
-      <c r="AD31" s="9"/>
-      <c r="AE31" s="9"/>
-      <c r="AF31" s="13"/>
-      <c r="AG31" s="13"/>
-      <c r="AH31" s="13"/>
-      <c r="AI31" s="20"/>
+      <c r="U31" s="18">
+        <v>1</v>
+      </c>
+      <c r="V31" s="12"/>
+      <c r="W31" s="18">
+        <v>0</v>
+      </c>
+      <c r="X31" s="18">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="18">
+        <v>1</v>
+      </c>
+      <c r="Z31" s="18"/>
+      <c r="AA31" s="11"/>
+      <c r="AB31" s="18"/>
+      <c r="AC31" s="12"/>
+      <c r="AD31" s="12"/>
+      <c r="AE31" s="12"/>
+      <c r="AF31" s="18"/>
+      <c r="AG31" s="18"/>
+      <c r="AH31" s="18"/>
+      <c r="AI31" s="21" t="s">
+        <v>176</v>
+      </c>
     </row>
     <row r="32" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32"/>
       <c r="C32" s="8">
-        <v>8000001</v>
+        <v>7000001</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="F32" s="9"/>
       <c r="G32" s="9"/>
       <c r="H32" s="9"/>
       <c r="I32" s="22" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="J32" s="8"/>
       <c r="K32" s="8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L32" s="8">
-        <v>2000010</v>
+        <v>2000004</v>
       </c>
       <c r="M32" s="13">
         <v>0</v>
@@ -4171,7 +4213,7 @@
         <v>1</v>
       </c>
       <c r="S32" s="9" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="T32" s="9" t="s">
         <v>70</v>
@@ -4190,7 +4232,9 @@
         <v>0</v>
       </c>
       <c r="Z32" s="13"/>
-      <c r="AA32" s="8"/>
+      <c r="AA32" s="8" t="s">
+        <v>141</v>
+      </c>
       <c r="AB32" s="13"/>
       <c r="AC32" s="9"/>
       <c r="AD32" s="9"/>
@@ -4198,33 +4242,31 @@
       <c r="AF32" s="13"/>
       <c r="AG32" s="13"/>
       <c r="AH32" s="13"/>
-      <c r="AI32" s="20" t="s">
-        <v>179</v>
-      </c>
+      <c r="AI32" s="20"/>
     </row>
     <row r="33" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B33"/>
       <c r="C33" s="8">
-        <v>2400001</v>
+        <v>8000001</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="F33" s="9"/>
       <c r="G33" s="9"/>
       <c r="H33" s="9"/>
       <c r="I33" s="22" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="J33" s="8"/>
       <c r="K33" s="8">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="L33" s="8">
-        <v>100001</v>
+        <v>2000010</v>
       </c>
       <c r="M33" s="13">
         <v>0</v>
@@ -4245,7 +4287,7 @@
         <v>1</v>
       </c>
       <c r="S33" s="9" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="T33" s="9" t="s">
         <v>70</v>
@@ -4255,10 +4297,10 @@
       </c>
       <c r="V33" s="9"/>
       <c r="W33" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X33" s="13">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y33" s="13">
         <v>0</v>
@@ -4272,31 +4314,33 @@
       <c r="AF33" s="13"/>
       <c r="AG33" s="13"/>
       <c r="AH33" s="13"/>
-      <c r="AI33" s="20"/>
+      <c r="AI33" s="20" t="s">
+        <v>176</v>
+      </c>
     </row>
     <row r="34" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34"/>
       <c r="C34" s="8">
-        <v>2500001</v>
+        <v>2400001</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="F34" s="9"/>
       <c r="G34" s="9"/>
       <c r="H34" s="9"/>
       <c r="I34" s="22" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="J34" s="8"/>
       <c r="K34" s="8">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L34" s="8">
-        <v>2000004</v>
+        <v>100001</v>
       </c>
       <c r="M34" s="13">
         <v>0</v>
@@ -4317,7 +4361,7 @@
         <v>1</v>
       </c>
       <c r="S34" s="9" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="T34" s="9" t="s">
         <v>70</v>
@@ -4327,18 +4371,16 @@
       </c>
       <c r="V34" s="9"/>
       <c r="W34" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X34" s="13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Y34" s="13">
         <v>0</v>
       </c>
       <c r="Z34" s="13"/>
-      <c r="AA34" s="8" t="s">
-        <v>144</v>
-      </c>
+      <c r="AA34" s="8"/>
       <c r="AB34" s="13"/>
       <c r="AC34" s="9"/>
       <c r="AD34" s="9"/>
@@ -4348,40 +4390,41 @@
       <c r="AH34" s="13"/>
       <c r="AI34" s="20"/>
     </row>
-    <row r="35" spans="2:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B35"/>
       <c r="C35" s="8">
-        <v>2600001</v>
-      </c>
-      <c r="D35" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="E35" s="10" t="s">
-        <v>211</v>
+        <v>2500001</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>207</v>
       </c>
       <c r="F35" s="9"/>
       <c r="G35" s="9"/>
       <c r="H35" s="9"/>
       <c r="I35" s="22" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="J35" s="8"/>
       <c r="K35" s="8">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L35" s="8">
-        <v>2000003</v>
+        <v>2000004</v>
       </c>
       <c r="M35" s="13">
         <v>0</v>
       </c>
       <c r="N35" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O35" s="13">
         <v>1</v>
       </c>
       <c r="P35" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q35" s="13">
         <v>0</v>
@@ -4390,7 +4433,7 @@
         <v>1</v>
       </c>
       <c r="S35" s="9" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="T35" s="9" t="s">
         <v>70</v>
@@ -4400,16 +4443,18 @@
       </c>
       <c r="V35" s="9"/>
       <c r="W35" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X35" s="13">
         <v>0</v>
       </c>
       <c r="Y35" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z35" s="13"/>
-      <c r="AA35" s="8"/>
+      <c r="AA35" s="8" t="s">
+        <v>141</v>
+      </c>
       <c r="AB35" s="13"/>
       <c r="AC35" s="9"/>
       <c r="AD35" s="9"/>
@@ -4417,11 +4462,82 @@
       <c r="AF35" s="13"/>
       <c r="AG35" s="13"/>
       <c r="AH35" s="13"/>
-      <c r="AI35" s="20" t="s">
-        <v>157</v>
-      </c>
+      <c r="AI35" s="20"/>
     </row>
-    <row r="36" spans="2:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="36" spans="2:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C36" s="8">
+        <v>2600001</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="E36" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="F36" s="9"/>
+      <c r="G36" s="9"/>
+      <c r="H36" s="9"/>
+      <c r="I36" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="J36" s="8"/>
+      <c r="K36" s="8">
+        <v>26</v>
+      </c>
+      <c r="L36" s="8">
+        <v>2000003</v>
+      </c>
+      <c r="M36" s="13">
+        <v>0</v>
+      </c>
+      <c r="N36" s="13">
+        <v>1</v>
+      </c>
+      <c r="O36" s="13">
+        <v>1</v>
+      </c>
+      <c r="P36" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q36" s="13">
+        <v>0</v>
+      </c>
+      <c r="R36" s="13">
+        <v>1</v>
+      </c>
+      <c r="S36" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="T36" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="U36" s="13">
+        <v>1</v>
+      </c>
+      <c r="V36" s="9"/>
+      <c r="W36" s="13">
+        <v>2</v>
+      </c>
+      <c r="X36" s="13">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="13">
+        <v>1</v>
+      </c>
+      <c r="Z36" s="13"/>
+      <c r="AA36" s="8"/>
+      <c r="AB36" s="13"/>
+      <c r="AC36" s="9"/>
+      <c r="AD36" s="9"/>
+      <c r="AE36" s="9"/>
+      <c r="AF36" s="13"/>
+      <c r="AG36" s="13"/>
+      <c r="AH36" s="13"/>
+      <c r="AI36" s="20" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="37" spans="2:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/SceneConfig.xlsx
+++ b/Excel/SceneConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCF514FD-ABDF-4E89-97C1-4D748700D83A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{247B12A3-6648-420F-A811-E4240E16E09C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -286,7 +286,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="242">
   <si>
     <t>c</t>
   </si>
@@ -1086,10 +1086,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>110006</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>68</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -1100,6 +1096,64 @@
   <si>
     <t>72,72</t>
     <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>110007</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>2000001</t>
+  </si>
+  <si>
+    <t>2000002</t>
+  </si>
+  <si>
+    <t>2000003</t>
+  </si>
+  <si>
+    <t>2000004</t>
+  </si>
+  <si>
+    <t>2000008</t>
+  </si>
+  <si>
+    <t>2000009</t>
+  </si>
+  <si>
+    <t>2000010</t>
+  </si>
+  <si>
+    <t>2000011</t>
+  </si>
+  <si>
+    <t>2100001</t>
+  </si>
+  <si>
+    <t>2100002</t>
+  </si>
+  <si>
+    <t>2200001</t>
+  </si>
+  <si>
+    <t>3000001</t>
+  </si>
+  <si>
+    <t>3000002</t>
+  </si>
+  <si>
+    <t>4000001</t>
+  </si>
+  <si>
+    <t>5000001</t>
+  </si>
+  <si>
+    <t>6000001</t>
+  </si>
+  <si>
+    <t>6000002</t>
+  </si>
+  <si>
+    <t>6000003</t>
   </si>
 </sst>
 </file>
@@ -1286,7 +1340,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1360,9 +1414,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2595,7 +2646,7 @@
         <v>72005013</v>
       </c>
       <c r="AA11" s="9"/>
-      <c r="AB11" s="27">
+      <c r="AB11" s="13">
         <v>40001</v>
       </c>
       <c r="AC11" s="9" t="s">
@@ -2668,10 +2719,10 @@
         <v>118</v>
       </c>
       <c r="T12" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="U12" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="V12" s="9" t="s">
         <v>126</v>
@@ -2689,7 +2740,7 @@
         <v>72006013</v>
       </c>
       <c r="AA12" s="9"/>
-      <c r="AB12" s="27">
+      <c r="AB12" s="13">
         <v>41001</v>
       </c>
       <c r="AC12" s="9" t="s">
@@ -2727,7 +2778,7 @@
         <v>219</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="H13" s="9"/>
       <c r="I13" s="22" t="s">
@@ -2762,13 +2813,13 @@
         <v>118</v>
       </c>
       <c r="T13" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="U13" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="V13" s="9" t="s">
         <v>222</v>
-      </c>
-      <c r="U13" s="9" t="s">
-        <v>222</v>
-      </c>
-      <c r="V13" s="9" t="s">
-        <v>223</v>
       </c>
       <c r="W13" s="13">
         <v>2</v>
@@ -2780,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="Z13" s="13">
-        <v>72006013</v>
+        <v>70006014</v>
       </c>
       <c r="AA13" s="9"/>
-      <c r="AB13" s="27">
+      <c r="AB13" s="13">
         <v>41001</v>
       </c>
       <c r="AC13" s="9" t="s">

--- a/Excel/SceneConfig.xlsx
+++ b/Excel/SceneConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{247B12A3-6648-420F-A811-E4240E16E09C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F657967-CD21-4A70-AFC9-EBA344930DA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -286,7 +286,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="218">
   <si>
     <t>c</t>
   </si>
@@ -513,9 +513,6 @@
     <t>ImgBig_13</t>
   </si>
   <si>
-    <t>110001</t>
-  </si>
-  <si>
     <t>-4501,0,13033</t>
   </si>
   <si>
@@ -546,15 +543,9 @@
     <t>ImgBig_12</t>
   </si>
   <si>
-    <t>110002</t>
-  </si>
-  <si>
     <t>-6786,0,-4897</t>
   </si>
   <si>
-    <t>Back_14</t>
-  </si>
-  <si>
     <t>shamo_1</t>
   </si>
   <si>
@@ -576,9 +567,6 @@
     <t>ImgBig_14</t>
   </si>
   <si>
-    <t>110003</t>
-  </si>
-  <si>
     <t>-1378,0,2202</t>
   </si>
   <si>
@@ -606,9 +594,6 @@
     <t>ImgBig_11</t>
   </si>
   <si>
-    <t>110004</t>
-  </si>
-  <si>
     <t>-7000,0,-3025</t>
   </si>
   <si>
@@ -636,9 +621,6 @@
     <t>ImgBig_15</t>
   </si>
   <si>
-    <t>110005</t>
-  </si>
-  <si>
     <t>16420,0,-4998</t>
   </si>
   <si>
@@ -658,9 +640,6 @@
   </si>
   <si>
     <t>ImgBig_16</t>
-  </si>
-  <si>
-    <t>110006</t>
   </si>
   <si>
     <t>15545,2978,25967</t>
@@ -1098,62 +1077,12 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>110007</t>
+    <t>16059,2815,27078</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>2000001</t>
-  </si>
-  <si>
-    <t>2000002</t>
-  </si>
-  <si>
-    <t>2000003</t>
-  </si>
-  <si>
-    <t>2000004</t>
-  </si>
-  <si>
-    <t>2000008</t>
-  </si>
-  <si>
-    <t>2000009</t>
-  </si>
-  <si>
-    <t>2000010</t>
-  </si>
-  <si>
-    <t>2000011</t>
-  </si>
-  <si>
-    <t>2100001</t>
-  </si>
-  <si>
-    <t>2100002</t>
-  </si>
-  <si>
-    <t>2200001</t>
-  </si>
-  <si>
-    <t>3000001</t>
-  </si>
-  <si>
-    <t>3000002</t>
-  </si>
-  <si>
-    <t>4000001</t>
-  </si>
-  <si>
-    <t>5000001</t>
-  </si>
-  <si>
-    <t>6000001</t>
-  </si>
-  <si>
-    <t>6000002</t>
-  </si>
-  <si>
-    <t>6000003</t>
+    <t>Back_14</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1340,7 +1269,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1414,6 +1343,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1779,14 +1711,16 @@
     <col min="5" max="5" width="26.75" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="17.125" customWidth="1"/>
     <col min="8" max="8" width="16.75" customWidth="1"/>
-    <col min="9" max="9" width="13.25" customWidth="1"/>
+    <col min="9" max="9" width="16.875" customWidth="1"/>
     <col min="10" max="10" width="31.625" customWidth="1"/>
     <col min="11" max="11" width="28.125" customWidth="1"/>
     <col min="12" max="13" width="16.75" customWidth="1"/>
+    <col min="14" max="14" width="12.25" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13.875" customWidth="1"/>
     <col min="17" max="17" width="14.875" customWidth="1"/>
     <col min="18" max="18" width="18.625" customWidth="1"/>
-    <col min="19" max="19" width="10.25" customWidth="1"/>
+    <col min="19" max="19" width="17.5" customWidth="1"/>
+    <col min="20" max="20" width="12.75" customWidth="1"/>
     <col min="21" max="21" width="13.125" customWidth="1"/>
     <col min="22" max="23" width="9" customWidth="1"/>
     <col min="24" max="25" width="11.375" customWidth="1"/>
@@ -1796,18 +1730,18 @@
     <col min="31" max="31" width="16.375" customWidth="1"/>
     <col min="32" max="32" width="18" customWidth="1"/>
     <col min="34" max="34" width="9.375" customWidth="1"/>
-    <col min="35" max="35" width="14.125" customWidth="1"/>
+    <col min="35" max="35" width="24.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:35" x14ac:dyDescent="0.15">
       <c r="E2" s="4" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>0</v>
       </c>
       <c r="AD2" s="4" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3" spans="2:35" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -1919,7 +1853,7 @@
         <v>31</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>32</v>
@@ -1994,7 +1928,7 @@
         <v>55</v>
       </c>
       <c r="AD4" s="6" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="AE4" s="6" t="s">
         <v>56</v>
@@ -2122,7 +2056,7 @@
         <v>65</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="F6" s="9"/>
       <c r="G6" s="9"/>
@@ -2208,17 +2142,17 @@
         <v>73</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="G7" s="9" t="s">
-        <v>75</v>
+      <c r="G7" s="27">
+        <v>110001</v>
       </c>
       <c r="H7" s="9"/>
       <c r="I7" s="22" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J7" s="14"/>
       <c r="K7" s="15">
@@ -2228,34 +2162,34 @@
         <v>100101</v>
       </c>
       <c r="M7" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="N7" s="13">
+        <v>1</v>
+      </c>
+      <c r="O7" s="13">
+        <v>0</v>
+      </c>
+      <c r="P7" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="13">
+        <v>0</v>
+      </c>
+      <c r="R7" s="13">
+        <v>0</v>
+      </c>
+      <c r="S7" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="N7" s="13">
-        <v>1</v>
-      </c>
-      <c r="O7" s="13">
-        <v>0</v>
-      </c>
-      <c r="P7" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="13">
-        <v>0</v>
-      </c>
-      <c r="R7" s="13">
-        <v>0</v>
-      </c>
-      <c r="S7" s="9" t="s">
+      <c r="T7" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="T7" s="9" t="s">
+      <c r="U7" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="V7" s="9" t="s">
         <v>79</v>
-      </c>
-      <c r="U7" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="V7" s="9" t="s">
-        <v>80</v>
       </c>
       <c r="W7" s="13">
         <v>2</v>
@@ -2270,14 +2204,14 @@
         <v>72001013</v>
       </c>
       <c r="AA7" s="22" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AB7" s="9"/>
       <c r="AC7" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AD7" s="9" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="AE7" s="9"/>
       <c r="AF7" s="13">
@@ -2290,7 +2224,7 @@
         <v>601500201</v>
       </c>
       <c r="AI7" s="20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -2299,20 +2233,20 @@
         <v>110002</v>
       </c>
       <c r="D8" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="F8" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="E8" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>86</v>
+      <c r="G8" s="27">
+        <v>110002</v>
       </c>
       <c r="H8" s="9"/>
       <c r="I8" s="22" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="J8" s="8"/>
       <c r="K8" s="8">
@@ -2322,34 +2256,34 @@
         <v>1000002</v>
       </c>
       <c r="M8" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="N8" s="13">
+        <v>1</v>
+      </c>
+      <c r="O8" s="13">
+        <v>0</v>
+      </c>
+      <c r="P8" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="13">
+        <v>0</v>
+      </c>
+      <c r="R8" s="13">
+        <v>0</v>
+      </c>
+      <c r="S8" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="T8" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="U8" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="V8" s="9" t="s">
         <v>88</v>
-      </c>
-      <c r="N8" s="13">
-        <v>1</v>
-      </c>
-      <c r="O8" s="13">
-        <v>0</v>
-      </c>
-      <c r="P8" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="13">
-        <v>0</v>
-      </c>
-      <c r="R8" s="13">
-        <v>0</v>
-      </c>
-      <c r="S8" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="T8" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="U8" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="V8" s="9" t="s">
-        <v>91</v>
       </c>
       <c r="W8" s="13">
         <v>2</v>
@@ -2364,14 +2298,14 @@
         <v>72002013</v>
       </c>
       <c r="AA8" s="22" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="AB8" s="9"/>
       <c r="AC8" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AD8" s="9" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="AE8" s="9"/>
       <c r="AF8" s="13">
@@ -2384,7 +2318,7 @@
         <v>601500301</v>
       </c>
       <c r="AI8" s="20" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -2393,20 +2327,20 @@
         <v>110003</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>96</v>
+        <v>92</v>
+      </c>
+      <c r="G9" s="27">
+        <v>110003</v>
       </c>
       <c r="H9" s="9"/>
       <c r="I9" s="22" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="J9" s="8"/>
       <c r="K9" s="8">
@@ -2416,7 +2350,7 @@
         <v>100102</v>
       </c>
       <c r="M9" s="16" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="N9" s="13">
         <v>1</v>
@@ -2434,16 +2368,16 @@
         <v>0</v>
       </c>
       <c r="S9" s="9" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="T9" s="9" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="U9" s="9" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="V9" s="9" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="W9" s="13">
         <v>2</v>
@@ -2458,14 +2392,14 @@
         <v>72003013</v>
       </c>
       <c r="AA9" s="22" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="AB9" s="9"/>
       <c r="AC9" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AD9" s="9" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="AE9" s="9"/>
       <c r="AF9" s="13">
@@ -2478,7 +2412,7 @@
         <v>601500401</v>
       </c>
       <c r="AI9" s="20" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -2487,20 +2421,20 @@
         <v>110004</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>106</v>
+        <v>101</v>
+      </c>
+      <c r="G10" s="27">
+        <v>110004</v>
       </c>
       <c r="H10" s="9"/>
       <c r="I10" s="22" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="J10" s="14"/>
       <c r="K10" s="15">
@@ -2510,7 +2444,7 @@
         <v>1000001</v>
       </c>
       <c r="M10" s="16" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="N10" s="13">
         <v>1</v>
@@ -2528,16 +2462,16 @@
         <v>0</v>
       </c>
       <c r="S10" s="9" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="T10" s="9" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="U10" s="9" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="V10" s="9" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="W10" s="13">
         <v>2</v>
@@ -2552,14 +2486,14 @@
         <v>72004013</v>
       </c>
       <c r="AA10" s="22" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="AB10" s="9"/>
       <c r="AC10" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AD10" s="9" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="AE10" s="9"/>
       <c r="AF10" s="13">
@@ -2572,7 +2506,7 @@
         <v>601500501</v>
       </c>
       <c r="AI10" s="20" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -2581,20 +2515,20 @@
         <v>110005</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>116</v>
+        <v>110</v>
+      </c>
+      <c r="G11" s="27">
+        <v>110005</v>
       </c>
       <c r="H11" s="9"/>
       <c r="I11" s="22" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="J11" s="14"/>
       <c r="K11" s="15">
@@ -2604,7 +2538,7 @@
         <v>2000007</v>
       </c>
       <c r="M11" s="16" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="N11" s="13">
         <v>1</v>
@@ -2622,16 +2556,16 @@
         <v>0</v>
       </c>
       <c r="S11" s="9" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="T11" s="9" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="U11" s="9" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="V11" s="9" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="W11" s="13">
         <v>2</v>
@@ -2650,10 +2584,10 @@
         <v>40001</v>
       </c>
       <c r="AC11" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AD11" s="9" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="AE11" s="9"/>
       <c r="AF11" s="13">
@@ -2666,7 +2600,7 @@
         <v>601500501</v>
       </c>
       <c r="AI11" s="20" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -2675,20 +2609,20 @@
         <v>110006</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>124</v>
+        <v>117</v>
+      </c>
+      <c r="G12" s="27">
+        <v>110006</v>
       </c>
       <c r="H12" s="9"/>
       <c r="I12" s="22" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="J12" s="14"/>
       <c r="K12" s="15">
@@ -2698,7 +2632,7 @@
         <v>2000012</v>
       </c>
       <c r="M12" s="16" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="N12" s="13">
         <v>1</v>
@@ -2716,16 +2650,16 @@
         <v>0</v>
       </c>
       <c r="S12" s="9" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="T12" s="9" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="U12" s="9" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="V12" s="9" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="W12" s="13">
         <v>2</v>
@@ -2744,10 +2678,10 @@
         <v>41001</v>
       </c>
       <c r="AC12" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AD12" s="9" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="AE12" s="9"/>
       <c r="AF12" s="13">
@@ -2760,7 +2694,7 @@
         <v>601500501</v>
       </c>
       <c r="AI12" s="20" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -2769,30 +2703,30 @@
         <v>110007</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>223</v>
+        <v>212</v>
+      </c>
+      <c r="G13" s="27">
+        <v>110007</v>
       </c>
       <c r="H13" s="9"/>
       <c r="I13" s="22" t="s">
-        <v>125</v>
+        <v>216</v>
       </c>
       <c r="J13" s="14"/>
       <c r="K13" s="15">
         <v>5</v>
       </c>
       <c r="L13" s="8">
-        <v>2000012</v>
+        <v>2000013</v>
       </c>
       <c r="M13" s="16" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="N13" s="13">
         <v>1</v>
@@ -2810,16 +2744,16 @@
         <v>0</v>
       </c>
       <c r="S13" s="9" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="T13" s="9" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="U13" s="9" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="V13" s="9" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="W13" s="13">
         <v>2</v>
@@ -2835,13 +2769,13 @@
       </c>
       <c r="AA13" s="9"/>
       <c r="AB13" s="13">
-        <v>41001</v>
+        <v>42001</v>
       </c>
       <c r="AC13" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AD13" s="9" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="AE13" s="9"/>
       <c r="AF13" s="13">
@@ -2854,7 +2788,7 @@
         <v>601500501</v>
       </c>
       <c r="AI13" s="20" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -2863,16 +2797,16 @@
         <v>2000001</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="F14" s="9"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
       <c r="I14" s="22" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="J14" s="8"/>
       <c r="K14" s="8">
@@ -2882,7 +2816,7 @@
         <v>2000001</v>
       </c>
       <c r="M14" s="16" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="N14" s="13">
         <v>1</v>
@@ -2900,7 +2834,7 @@
         <v>1</v>
       </c>
       <c r="S14" s="9" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="T14" s="9" t="s">
         <v>70</v>
@@ -2920,7 +2854,7 @@
       </c>
       <c r="Z14" s="13"/>
       <c r="AA14" s="19" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="AB14" s="9"/>
       <c r="AC14" s="9"/>
@@ -2930,7 +2864,7 @@
       <c r="AG14" s="13"/>
       <c r="AH14" s="13"/>
       <c r="AI14" s="23" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -2939,16 +2873,16 @@
         <v>2000002</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="F15" s="9"/>
       <c r="G15" s="9"/>
       <c r="H15" s="9"/>
       <c r="I15" s="22" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="J15" s="8"/>
       <c r="K15" s="8">
@@ -2958,7 +2892,7 @@
         <v>2000002</v>
       </c>
       <c r="M15" s="16" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="N15" s="13">
         <v>1</v>
@@ -2976,7 +2910,7 @@
         <v>1</v>
       </c>
       <c r="S15" s="9" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="T15" s="9" t="s">
         <v>70</v>
@@ -3004,7 +2938,7 @@
       <c r="AG15" s="13"/>
       <c r="AH15" s="13"/>
       <c r="AI15" s="20" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -3013,16 +2947,16 @@
         <v>2000003</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="F16" s="9"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
       <c r="I16" s="22" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="J16" s="8"/>
       <c r="K16" s="8">
@@ -3032,7 +2966,7 @@
         <v>2000003</v>
       </c>
       <c r="M16" s="16" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="N16" s="13">
         <v>0</v>
@@ -3050,7 +2984,7 @@
         <v>1</v>
       </c>
       <c r="S16" s="9" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="T16" s="9" t="s">
         <v>70</v>
@@ -3085,16 +3019,16 @@
         <v>2000004</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="F17" s="9"/>
       <c r="G17" s="9"/>
       <c r="H17" s="9"/>
       <c r="I17" s="22" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="J17" s="8"/>
       <c r="K17" s="8">
@@ -3104,7 +3038,7 @@
         <v>2000003</v>
       </c>
       <c r="M17" s="16" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="N17" s="13">
         <v>0</v>
@@ -3122,7 +3056,7 @@
         <v>1</v>
       </c>
       <c r="S17" s="9" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="T17" s="9" t="s">
         <v>70</v>
@@ -3142,7 +3076,7 @@
       </c>
       <c r="Z17" s="13"/>
       <c r="AA17" s="8" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="AB17" s="13"/>
       <c r="AC17" s="9"/>
@@ -3158,16 +3092,16 @@
         <v>2000008</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="F18" s="9"/>
       <c r="G18" s="9"/>
       <c r="H18" s="9"/>
       <c r="I18" s="22" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="J18" s="8">
         <v>20000038</v>
@@ -3179,7 +3113,7 @@
         <v>2000008</v>
       </c>
       <c r="M18" s="16" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="N18" s="13">
         <v>1</v>
@@ -3197,7 +3131,7 @@
         <v>1</v>
       </c>
       <c r="S18" s="9" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="T18" s="9" t="s">
         <v>70</v>
@@ -3206,7 +3140,7 @@
         <v>12</v>
       </c>
       <c r="V18" s="9" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="W18" s="13">
         <v>0</v>
@@ -3219,7 +3153,7 @@
       </c>
       <c r="Z18" s="13"/>
       <c r="AA18" s="8" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="AB18" s="13"/>
       <c r="AC18" s="9"/>
@@ -3229,7 +3163,7 @@
       <c r="AG18" s="13"/>
       <c r="AH18" s="13"/>
       <c r="AI18" s="23" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19" spans="2:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -3237,19 +3171,19 @@
         <v>2000009</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="F19" s="9"/>
       <c r="G19" s="9"/>
       <c r="H19" s="9"/>
       <c r="I19" s="22" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="J19" s="24" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="K19" s="8">
         <v>17</v>
@@ -3258,7 +3192,7 @@
         <v>2000009</v>
       </c>
       <c r="M19" s="16" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="N19" s="13">
         <v>1</v>
@@ -3276,7 +3210,7 @@
         <v>1</v>
       </c>
       <c r="S19" s="9" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="T19" s="9" t="s">
         <v>70</v>
@@ -3285,7 +3219,7 @@
         <v>12</v>
       </c>
       <c r="V19" s="9" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="W19" s="13">
         <v>0</v>
@@ -3308,7 +3242,7 @@
       <c r="AG19" s="13"/>
       <c r="AH19" s="13"/>
       <c r="AI19" s="23" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
     </row>
     <row r="20" spans="2:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -3316,16 +3250,16 @@
         <v>2000010</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="F20" s="9"/>
       <c r="G20" s="9"/>
       <c r="H20" s="9"/>
       <c r="I20" s="22" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="J20" s="8"/>
       <c r="K20" s="8">
@@ -3353,7 +3287,7 @@
         <v>1</v>
       </c>
       <c r="S20" s="9" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="T20" s="9" t="s">
         <v>70</v>
@@ -3373,7 +3307,7 @@
       </c>
       <c r="Z20" s="13"/>
       <c r="AA20" s="8" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="AB20" s="13"/>
       <c r="AC20" s="9"/>
@@ -3383,7 +3317,7 @@
       <c r="AG20" s="13"/>
       <c r="AH20" s="13"/>
       <c r="AI20" s="20" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
     </row>
     <row r="21" spans="2:35" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -3392,19 +3326,19 @@
         <v>2000011</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="F21" s="9"/>
       <c r="G21" s="9"/>
       <c r="H21" s="9"/>
       <c r="I21" s="22" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="K21" s="9" t="s">
         <v>69</v>
@@ -3431,7 +3365,7 @@
         <v>1</v>
       </c>
       <c r="S21" s="9" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="T21" s="9" t="s">
         <v>71</v>
@@ -3469,7 +3403,7 @@
         <v>0</v>
       </c>
       <c r="AI21" s="20" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
     </row>
     <row r="22" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -3478,16 +3412,16 @@
         <v>2100001</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="F22" s="9"/>
       <c r="G22" s="9"/>
       <c r="H22" s="9"/>
       <c r="I22" s="22" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="J22" s="8"/>
       <c r="K22" s="8">
@@ -3515,7 +3449,7 @@
         <v>1</v>
       </c>
       <c r="S22" s="9" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="T22" s="9" t="s">
         <v>70</v>
@@ -3550,16 +3484,16 @@
         <v>2100002</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="F23" s="9"/>
       <c r="G23" s="9"/>
       <c r="H23" s="9"/>
       <c r="I23" s="22" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="J23" s="8"/>
       <c r="K23" s="8">
@@ -3587,7 +3521,7 @@
         <v>1</v>
       </c>
       <c r="S23" s="9" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="T23" s="9" t="s">
         <v>70</v>
@@ -3622,16 +3556,16 @@
         <v>2200001</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="F24" s="9"/>
       <c r="G24" s="9"/>
       <c r="H24" s="9"/>
       <c r="I24" s="22" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="J24" s="8"/>
       <c r="K24" s="8">
@@ -3659,7 +3593,7 @@
         <v>1</v>
       </c>
       <c r="S24" s="9" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="T24" s="9" t="s">
         <v>70</v>
@@ -3693,19 +3627,19 @@
         <v>3000001</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="F25" s="9"/>
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
       <c r="I25" s="22" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="J25" s="17" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="K25" s="8">
         <v>12</v>
@@ -3732,7 +3666,7 @@
         <v>1</v>
       </c>
       <c r="S25" s="9" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="T25" s="9" t="s">
         <v>70</v>
@@ -3741,7 +3675,7 @@
         <v>10</v>
       </c>
       <c r="V25" s="9" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="W25" s="13">
         <v>40</v>
@@ -3755,7 +3689,7 @@
       <c r="Z25" s="13"/>
       <c r="AA25" s="8"/>
       <c r="AB25" s="25" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="AC25" s="9"/>
       <c r="AD25" s="9"/>
@@ -3764,7 +3698,7 @@
       <c r="AG25" s="13"/>
       <c r="AH25" s="13"/>
       <c r="AI25" s="20" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
     </row>
     <row r="26" spans="2:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -3772,19 +3706,19 @@
         <v>3000002</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="F26" s="9"/>
       <c r="G26" s="9"/>
       <c r="H26" s="9"/>
       <c r="I26" s="22" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="J26" s="17" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="K26" s="8">
         <v>12</v>
@@ -3811,7 +3745,7 @@
         <v>1</v>
       </c>
       <c r="S26" s="9" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="T26" s="9" t="s">
         <v>70</v>
@@ -3820,7 +3754,7 @@
         <v>30</v>
       </c>
       <c r="V26" s="9" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="W26" s="13">
         <v>40</v>
@@ -3834,7 +3768,7 @@
       <c r="Z26" s="13"/>
       <c r="AA26" s="8"/>
       <c r="AB26" s="25" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="AC26" s="9"/>
       <c r="AD26" s="9"/>
@@ -3843,7 +3777,7 @@
       <c r="AG26" s="13"/>
       <c r="AH26" s="13"/>
       <c r="AI26" s="20" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
     </row>
     <row r="27" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -3852,16 +3786,16 @@
         <v>4000001</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="F27" s="9"/>
       <c r="G27" s="9"/>
       <c r="H27" s="9"/>
       <c r="I27" s="22" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="J27" s="8"/>
       <c r="K27" s="8">
@@ -3889,7 +3823,7 @@
         <v>1</v>
       </c>
       <c r="S27" s="9" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="T27" s="9" t="s">
         <v>70</v>
@@ -3909,7 +3843,7 @@
       </c>
       <c r="Z27" s="13"/>
       <c r="AA27" s="8" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="AB27" s="13"/>
       <c r="AC27" s="9"/>
@@ -3926,16 +3860,16 @@
         <v>5000001</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="F28" s="9"/>
       <c r="G28" s="9"/>
       <c r="H28" s="9"/>
       <c r="I28" s="22" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="J28" s="8"/>
       <c r="K28" s="8">
@@ -3963,7 +3897,7 @@
         <v>1</v>
       </c>
       <c r="S28" s="9" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="T28" s="9" t="s">
         <v>70</v>
@@ -3983,7 +3917,7 @@
       </c>
       <c r="Z28" s="13"/>
       <c r="AA28" s="8" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="AB28" s="13"/>
       <c r="AC28" s="9"/>
@@ -3999,16 +3933,16 @@
         <v>6000001</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="F29" s="9"/>
       <c r="G29" s="9"/>
       <c r="H29" s="9"/>
       <c r="I29" s="22" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="J29" s="8"/>
       <c r="K29" s="8">
@@ -4036,7 +3970,7 @@
         <v>1</v>
       </c>
       <c r="S29" s="9" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="T29" s="9" t="s">
         <v>70</v>
@@ -4045,7 +3979,7 @@
         <v>12</v>
       </c>
       <c r="V29" s="9" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="W29" s="13">
         <v>100</v>
@@ -4058,7 +3992,7 @@
       </c>
       <c r="Z29" s="13"/>
       <c r="AA29" s="8" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="AB29" s="13"/>
       <c r="AC29" s="9"/>
@@ -4068,7 +4002,7 @@
       <c r="AG29" s="13"/>
       <c r="AH29" s="13"/>
       <c r="AI29" s="20" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
     </row>
     <row r="30" spans="2:35" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -4077,16 +4011,16 @@
         <v>6000002</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="F30" s="12"/>
       <c r="G30" s="12"/>
       <c r="H30" s="12"/>
       <c r="I30" s="26" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="J30" s="11"/>
       <c r="K30" s="11">
@@ -4114,7 +4048,7 @@
         <v>1</v>
       </c>
       <c r="S30" s="12" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="T30" s="12" t="s">
         <v>70</v>
@@ -4144,7 +4078,7 @@
       <c r="AG30" s="18"/>
       <c r="AH30" s="18"/>
       <c r="AI30" s="21" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
     </row>
     <row r="31" spans="2:35" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -4153,16 +4087,16 @@
         <v>6000003</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="F31" s="12"/>
       <c r="G31" s="12"/>
       <c r="H31" s="12"/>
       <c r="I31" s="26" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="J31" s="11"/>
       <c r="K31" s="11">
@@ -4190,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="S31" s="12" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="T31" s="12" t="s">
         <v>70</v>
@@ -4218,7 +4152,7 @@
       <c r="AG31" s="18"/>
       <c r="AH31" s="18"/>
       <c r="AI31" s="21" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
     </row>
     <row r="32" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -4227,16 +4161,16 @@
         <v>7000001</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="F32" s="9"/>
       <c r="G32" s="9"/>
       <c r="H32" s="9"/>
       <c r="I32" s="22" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="J32" s="8"/>
       <c r="K32" s="8">
@@ -4264,7 +4198,7 @@
         <v>1</v>
       </c>
       <c r="S32" s="9" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="T32" s="9" t="s">
         <v>70</v>
@@ -4284,7 +4218,7 @@
       </c>
       <c r="Z32" s="13"/>
       <c r="AA32" s="8" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="AB32" s="13"/>
       <c r="AC32" s="9"/>
@@ -4301,16 +4235,16 @@
         <v>8000001</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="F33" s="9"/>
       <c r="G33" s="9"/>
       <c r="H33" s="9"/>
       <c r="I33" s="22" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="J33" s="8"/>
       <c r="K33" s="8">
@@ -4338,7 +4272,7 @@
         <v>1</v>
       </c>
       <c r="S33" s="9" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="T33" s="9" t="s">
         <v>70</v>
@@ -4366,7 +4300,7 @@
       <c r="AG33" s="13"/>
       <c r="AH33" s="13"/>
       <c r="AI33" s="20" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
     </row>
     <row r="34" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -4375,16 +4309,16 @@
         <v>2400001</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="F34" s="9"/>
       <c r="G34" s="9"/>
       <c r="H34" s="9"/>
       <c r="I34" s="22" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="J34" s="8"/>
       <c r="K34" s="8">
@@ -4412,7 +4346,7 @@
         <v>1</v>
       </c>
       <c r="S34" s="9" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="T34" s="9" t="s">
         <v>70</v>
@@ -4447,16 +4381,16 @@
         <v>2500001</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="F35" s="9"/>
       <c r="G35" s="9"/>
       <c r="H35" s="9"/>
       <c r="I35" s="22" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="J35" s="8"/>
       <c r="K35" s="8">
@@ -4484,7 +4418,7 @@
         <v>1</v>
       </c>
       <c r="S35" s="9" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="T35" s="9" t="s">
         <v>70</v>
@@ -4504,7 +4438,7 @@
       </c>
       <c r="Z35" s="13"/>
       <c r="AA35" s="8" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="AB35" s="13"/>
       <c r="AC35" s="9"/>
@@ -4520,16 +4454,16 @@
         <v>2600001</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="F36" s="9"/>
       <c r="G36" s="9"/>
       <c r="H36" s="9"/>
       <c r="I36" s="22" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="J36" s="8"/>
       <c r="K36" s="8">
@@ -4557,7 +4491,7 @@
         <v>1</v>
       </c>
       <c r="S36" s="9" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="T36" s="9" t="s">
         <v>70</v>
@@ -4585,7 +4519,7 @@
       <c r="AG36" s="13"/>
       <c r="AH36" s="13"/>
       <c r="AI36" s="20" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
     </row>
     <row r="37" spans="2:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>

--- a/Excel/SceneConfig.xlsx
+++ b/Excel/SceneConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F657967-CD21-4A70-AFC9-EBA344930DA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C23E88D-AC6D-4FAE-934C-46789AEBFAAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SceneProto" sheetId="1" r:id="rId1"/>
@@ -1065,10 +1065,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>68</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>72</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -1082,6 +1078,10 @@
   </si>
   <si>
     <t>Back_14</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>69</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -1269,7 +1269,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1343,9 +1343,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2147,7 +2144,7 @@
       <c r="F7" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="G7" s="27">
+      <c r="G7" s="13">
         <v>110001</v>
       </c>
       <c r="H7" s="9"/>
@@ -2241,7 +2238,7 @@
       <c r="F8" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="G8" s="27">
+      <c r="G8" s="13">
         <v>110002</v>
       </c>
       <c r="H8" s="9"/>
@@ -2256,7 +2253,7 @@
         <v>1000002</v>
       </c>
       <c r="M8" s="13" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N8" s="13">
         <v>1</v>
@@ -2335,7 +2332,7 @@
       <c r="F9" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="G9" s="27">
+      <c r="G9" s="13">
         <v>110003</v>
       </c>
       <c r="H9" s="9"/>
@@ -2429,7 +2426,7 @@
       <c r="F10" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="G10" s="27">
+      <c r="G10" s="13">
         <v>110004</v>
       </c>
       <c r="H10" s="9"/>
@@ -2523,7 +2520,7 @@
       <c r="F11" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="G11" s="27">
+      <c r="G11" s="13">
         <v>110005</v>
       </c>
       <c r="H11" s="9"/>
@@ -2617,7 +2614,7 @@
       <c r="F12" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="G12" s="27">
+      <c r="G12" s="13">
         <v>110006</v>
       </c>
       <c r="H12" s="9"/>
@@ -2653,10 +2650,10 @@
         <v>112</v>
       </c>
       <c r="T12" s="9" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="U12" s="9" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="V12" s="9" t="s">
         <v>119</v>
@@ -2711,12 +2708,12 @@
       <c r="F13" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="G13" s="27">
+      <c r="G13" s="13">
         <v>110007</v>
       </c>
       <c r="H13" s="9"/>
       <c r="I13" s="22" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J13" s="14"/>
       <c r="K13" s="15">
@@ -2747,16 +2744,16 @@
         <v>112</v>
       </c>
       <c r="T13" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="U13" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="V13" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="U13" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="V13" s="9" t="s">
-        <v>215</v>
-      </c>
       <c r="W13" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X13" s="13">
         <v>0</v>

--- a/Excel/SceneConfig.xlsx
+++ b/Excel/SceneConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C23E88D-AC6D-4FAE-934C-46789AEBFAAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E20BACEC-9BE7-4AB3-99EF-B162AC5E8AF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2753,7 +2753,7 @@
         <v>214</v>
       </c>
       <c r="W13" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X13" s="13">
         <v>0</v>

--- a/Excel/SceneConfig.xlsx
+++ b/Excel/SceneConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E20BACEC-9BE7-4AB3-99EF-B162AC5E8AF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFBF93A0-DA2A-4BB1-8ACC-B102FA7D26C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -286,7 +286,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="219">
   <si>
     <t>c</t>
   </si>
@@ -1082,6 +1082,10 @@
   </si>
   <si>
     <t>69</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>142,89,81.8,0,230</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -2762,7 +2766,7 @@
         <v>0</v>
       </c>
       <c r="Z13" s="13">
-        <v>70006014</v>
+        <v>72007013</v>
       </c>
       <c r="AA13" s="9"/>
       <c r="AB13" s="13">
@@ -2785,7 +2789,7 @@
         <v>601500501</v>
       </c>
       <c r="AI13" s="20" t="s">
-        <v>120</v>
+        <v>218</v>
       </c>
     </row>
     <row r="14" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">

--- a/Excel/SceneConfig.xlsx
+++ b/Excel/SceneConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFBF93A0-DA2A-4BB1-8ACC-B102FA7D26C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3C10571-6F88-4364-A7AD-F81F4F3B4B42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -286,7 +286,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="215">
   <si>
     <t>c</t>
   </si>
@@ -510,15 +510,9 @@
     <t>绿谷村</t>
   </si>
   <si>
-    <t>ImgBig_13</t>
-  </si>
-  <si>
     <t>-4501,0,13033</t>
   </si>
   <si>
-    <t>Back_11</t>
-  </si>
-  <si>
     <t>jiaowai_1</t>
   </si>
   <si>
@@ -531,9 +525,6 @@
     <t>1;15.83,0.05,-69.15;72001003;1@1;53.82,0.05,-67.31;72001004;1@1;-43.27,0.02,101.65;72001003;1@1;-29.75,0.05,55.92;72001003;1@1;-19.51,0.02,61.98;72001002;1@1;90.89,0.06,63.31;72001013;1@1;35.00,0.08,-63.73;72001012;1@1;-24.23,0.15,6.05;72001011;1@1;-34.08,0.05,121.12;72001001;1@1;-31.42,0.03,116.10;72001001;1@1;-30.16,0.04,111.97;72001001;1@1;-28.55,0.03,106.66;72001001;1@1;-27.29,0.04,102.53;72001001;1@1;-27.80,0.04,90.87;72001001;1@1;-29.06,0.03,95.00;72001001;1@1;-41.42,0.03,93.67;72001001;1@1;-40.16,0.04,89.54;72001001;1@1;-13.78,0.03,-36.14;72001001;1@1;-12.52,0.04,-40.27;72001001;1@1;-24.60,0.04,-38.69;72001001;1@1;-25.86,0.03,-34.55;72001001;1@1;-23.05,0.04,-48.54;72001001;1@1;-24.31,0.03,-44.41;72001001;1@1;-3.99,0.04,-51.50;72001001;1@1;-8.19,0.03,-49.74;72001001;1@1;-13.84,0.04,-59.26;72001001;1@1;-18.04,0.03,-57.50;72001001;1@1;58.35,0.04,-27.84;72001001;1@1;58.47,0.03,-23.88;72001001;1@1;71.76,0.04,-28.74;72001001;1@1;71.88,0.03,-24.78;72001001;1@1;71.32,0.04,-13.76;72001001;1@1;71.44,0.03,-9.80;72001001;1@1;60.80,0.04,-14.32;72001001;1@1;60.92,0.03,-10.36;72001001;1@1;87.37,0.03,46.68;72001001;1@1;83.34,0.04,41.53;72001001;1@1;81.91,0.03,47.71;72001001;1@1;75.57,0.03,45.78;72001001;1@1;83.25,0.03,53.93;72001001;1@1;74.54,0.03,71.98;72001001;1@1;75.88,0.03,78.20;72001001;1@1;75.97,0.04,65.80;72001001;1@1;-27.64,0.02,61.98;72001002;1@1;-17.63,0.02,50.00;72001002;1@1;-25.76,0.02,50.00;72001002;1@1;-13.19,0.05,55.74;72001003;1@1;-28.97,0.05,68.46;72001001;1@1;-16.77,0.05,69.24;72001001;1@1;-25.02,0.05,81.74;72001001;1@1;-42.70,0.02,109.76;72001002;1@1;-42.21,0.02,113.21;72001002;1@1;-38.99,0.02,85.59;72001003;1@1;-32.83,0.02,73.98;72001003;1@1;-20.69,0.02,75.10;72001003;1@1;-25.80,0.02,42.21;72001002;1@1;-16.57,0.02,41.06;72001002;1@1;-16.57,0.02,37.23;72001002;1@1;-25.80,0.02,38.38;72001002;1@1;-18.17,0.02,25.93;72001002;1@1;-26.30,0.02,25.93;72001002;1@1;-26.30,0.02,22.10;72001002;1@1;-18.17,0.02,22.10;72001002;1@1;-19.56,0.02,-14.21;72001002;1@1;-27.69,0.02,-14.21;72001002;1@1;-27.69,0.02,-10.38;72001002;1@1;-19.56,0.02,-10.38;72001002;1@1;-19.56,0.02,-20.77;72001002;1@1;-27.69,0.02,-20.77;72001002;1@1;-27.69,0.02,-24.60;72001002;1@1;-19.56,0.02,-24.60;72001002;1@1;19.42,0.05,-69.15;72001003;1@1;22.84,0.05,-69.15;72001003;1@1;15.83,0.05,-55.83;72001003;1@1;19.42,0.05,-55.83;72001003;1@1;22.84,0.05,-55.83;72001003;1@1;5.96,0.05,-54.84;72001003;1@1;2.54,0.05,-54.84;72001003;1@1;3.98,0.05,-67.26;72001003;1@1;7.40,0.05,-67.26;72001003;1@1;48.98,0.05,-54.24;72001004;1@1;68.83,0.05,-59.24;72001004;1@1;70.55,0.05,-44.22;72001004;1@1;63.15,0.05,-65.04;72001004;1@1;54.28,0.05,-49.76;72001004;1@1;70.55,0.05,-51.83;72001004;1@1;57.12,0.05,-42.69;72001004;1@1;67.07,0.02,-35.95;72001002;1@1;57.23,0.02,-35.04;72001002;1@1;60.58,0.02,2.08;72001002;1@1;70.56,0.02,2.08;72001002;1@1;60.58,0.02,5.77;72001002;1@1;70.56,0.02,5.77;72001002;1@1;63.26,0.02,21.87;72001002;1@1;72.07,0.02,18.16;72001002;1@1;72.07,0.02,21.85;72001002;1@1;63.26,0.02,25.56;72001002;1@1;60.30,0.05,14.63;72001004;1@1;72.32,0.05,12.44;72001004;1@1;62.65,0.05,33.72;72001004;1@1;74.67,0.05,31.53;72001004;1@1;80.25,0.05,36.90;72001004;1@1;65.09,0.05,50.98;72001004;1@1;65.90,0.02,65.19;72001002;1@1;65.90,0.02,60.08;72001002;1@1;62.90,0.02,41.10;72001002;1@1;80.50,0.02,74.00;72001002;1@1;91.21,0.05,50.10;72001003;1@1;68.40,0.05,69.29;72001003;1@1;80.25,0.05,69.29;72001003;1</t>
   </si>
   <si>
-    <t>在人们眼中,这片区域有很深未知的东西,亲爱的冒险者,你准备好开始探险了嘛</t>
-  </si>
-  <si>
     <t>21.4,100,35.5,0,105</t>
   </si>
   <si>
@@ -570,9 +561,6 @@
     <t>-1378,0,2202</t>
   </si>
   <si>
-    <t>Back_15</t>
-  </si>
-  <si>
     <t>jiaowai_2</t>
   </si>
   <si>
@@ -595,9 +583,6 @@
   </si>
   <si>
     <t>-7000,0,-3025</t>
-  </si>
-  <si>
-    <t>Back_13</t>
   </si>
   <si>
     <t>jiaowai_3</t>
@@ -1077,15 +1062,19 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>Back_14</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>69</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>142,89,81.8,0,230</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>在人们眼中,这片区域有很深未知的东西,亲爱的冒险者,你准备好开始探险了嘛?</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>ImgBig_13</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -1736,13 +1725,13 @@
   <sheetData>
     <row r="2" spans="2:35" x14ac:dyDescent="0.15">
       <c r="E2" s="4" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>0</v>
       </c>
       <c r="AD2" s="4" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="2:35" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -1854,7 +1843,7 @@
         <v>31</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>32</v>
@@ -1929,7 +1918,7 @@
         <v>55</v>
       </c>
       <c r="AD4" s="6" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="AE4" s="6" t="s">
         <v>56</v>
@@ -2057,7 +2046,7 @@
         <v>65</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="F6" s="9"/>
       <c r="G6" s="9"/>
@@ -2143,17 +2132,17 @@
         <v>73</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>74</v>
+        <v>214</v>
       </c>
       <c r="G7" s="13">
         <v>110001</v>
       </c>
       <c r="H7" s="9"/>
       <c r="I7" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J7" s="14"/>
       <c r="K7" s="15">
@@ -2162,35 +2151,35 @@
       <c r="L7" s="8">
         <v>100101</v>
       </c>
-      <c r="M7" s="16" t="s">
+      <c r="M7" s="8">
+        <v>110001</v>
+      </c>
+      <c r="N7" s="13">
+        <v>1</v>
+      </c>
+      <c r="O7" s="13">
+        <v>0</v>
+      </c>
+      <c r="P7" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="13">
+        <v>0</v>
+      </c>
+      <c r="R7" s="13">
+        <v>0</v>
+      </c>
+      <c r="S7" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="T7" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="N7" s="13">
-        <v>1</v>
-      </c>
-      <c r="O7" s="13">
-        <v>0</v>
-      </c>
-      <c r="P7" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="13">
-        <v>0</v>
-      </c>
-      <c r="R7" s="13">
-        <v>0</v>
-      </c>
-      <c r="S7" s="9" t="s">
+      <c r="U7" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="V7" s="9" t="s">
         <v>77</v>
-      </c>
-      <c r="T7" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="U7" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="V7" s="9" t="s">
-        <v>79</v>
       </c>
       <c r="W7" s="13">
         <v>2</v>
@@ -2205,14 +2194,14 @@
         <v>72001013</v>
       </c>
       <c r="AA7" s="22" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AB7" s="9"/>
       <c r="AC7" s="9" t="s">
-        <v>81</v>
+        <v>213</v>
       </c>
       <c r="AD7" s="9" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="AE7" s="9"/>
       <c r="AF7" s="13">
@@ -2225,7 +2214,7 @@
         <v>601500201</v>
       </c>
       <c r="AI7" s="20" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -2234,20 +2223,20 @@
         <v>110002</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G8" s="13">
         <v>110002</v>
       </c>
       <c r="H8" s="9"/>
       <c r="I8" s="22" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="J8" s="8"/>
       <c r="K8" s="8">
@@ -2256,8 +2245,8 @@
       <c r="L8" s="8">
         <v>1000002</v>
       </c>
-      <c r="M8" s="13" t="s">
-        <v>216</v>
+      <c r="M8" s="8">
+        <v>110002</v>
       </c>
       <c r="N8" s="13">
         <v>1</v>
@@ -2275,16 +2264,16 @@
         <v>0</v>
       </c>
       <c r="S8" s="9" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="T8" s="9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="U8" s="9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="V8" s="9" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="W8" s="13">
         <v>2</v>
@@ -2299,14 +2288,14 @@
         <v>72002013</v>
       </c>
       <c r="AA8" s="22" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="AB8" s="9"/>
       <c r="AC8" s="9" t="s">
-        <v>81</v>
+        <v>213</v>
       </c>
       <c r="AD8" s="9" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="AE8" s="9"/>
       <c r="AF8" s="13">
@@ -2319,7 +2308,7 @@
         <v>601500301</v>
       </c>
       <c r="AI8" s="20" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -2328,20 +2317,20 @@
         <v>110003</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="G9" s="13">
         <v>110003</v>
       </c>
       <c r="H9" s="9"/>
       <c r="I9" s="22" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="J9" s="8"/>
       <c r="K9" s="8">
@@ -2350,8 +2339,8 @@
       <c r="L9" s="8">
         <v>100102</v>
       </c>
-      <c r="M9" s="16" t="s">
-        <v>94</v>
+      <c r="M9" s="8">
+        <v>110003</v>
       </c>
       <c r="N9" s="13">
         <v>1</v>
@@ -2369,16 +2358,16 @@
         <v>0</v>
       </c>
       <c r="S9" s="9" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="T9" s="9" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="U9" s="9" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="V9" s="9" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="W9" s="13">
         <v>2</v>
@@ -2393,14 +2382,14 @@
         <v>72003013</v>
       </c>
       <c r="AA9" s="22" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="AB9" s="9"/>
       <c r="AC9" s="9" t="s">
-        <v>81</v>
+        <v>213</v>
       </c>
       <c r="AD9" s="9" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="AE9" s="9"/>
       <c r="AF9" s="13">
@@ -2413,7 +2402,7 @@
         <v>601500401</v>
       </c>
       <c r="AI9" s="20" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -2422,20 +2411,20 @@
         <v>110004</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G10" s="13">
         <v>110004</v>
       </c>
       <c r="H10" s="9"/>
       <c r="I10" s="22" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="J10" s="14"/>
       <c r="K10" s="15">
@@ -2444,8 +2433,8 @@
       <c r="L10" s="8">
         <v>1000001</v>
       </c>
-      <c r="M10" s="16" t="s">
-        <v>103</v>
+      <c r="M10" s="8">
+        <v>110004</v>
       </c>
       <c r="N10" s="13">
         <v>1</v>
@@ -2463,16 +2452,16 @@
         <v>0</v>
       </c>
       <c r="S10" s="9" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="T10" s="9" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="U10" s="9" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="V10" s="9" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="W10" s="13">
         <v>2</v>
@@ -2487,14 +2476,14 @@
         <v>72004013</v>
       </c>
       <c r="AA10" s="22" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AB10" s="9"/>
       <c r="AC10" s="9" t="s">
-        <v>81</v>
+        <v>213</v>
       </c>
       <c r="AD10" s="9" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="AE10" s="9"/>
       <c r="AF10" s="13">
@@ -2507,7 +2496,7 @@
         <v>601500501</v>
       </c>
       <c r="AI10" s="20" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -2516,20 +2505,20 @@
         <v>110005</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="G11" s="13">
         <v>110005</v>
       </c>
       <c r="H11" s="9"/>
       <c r="I11" s="22" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="J11" s="14"/>
       <c r="K11" s="15">
@@ -2538,8 +2527,8 @@
       <c r="L11" s="8">
         <v>2000007</v>
       </c>
-      <c r="M11" s="16" t="s">
-        <v>103</v>
+      <c r="M11" s="8">
+        <v>110005</v>
       </c>
       <c r="N11" s="13">
         <v>1</v>
@@ -2557,16 +2546,16 @@
         <v>0</v>
       </c>
       <c r="S11" s="9" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="T11" s="9" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="U11" s="9" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="V11" s="9" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="W11" s="13">
         <v>2</v>
@@ -2585,10 +2574,10 @@
         <v>40001</v>
       </c>
       <c r="AC11" s="9" t="s">
-        <v>81</v>
+        <v>213</v>
       </c>
       <c r="AD11" s="9" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="AE11" s="9"/>
       <c r="AF11" s="13">
@@ -2601,7 +2590,7 @@
         <v>601500501</v>
       </c>
       <c r="AI11" s="20" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -2610,20 +2599,20 @@
         <v>110006</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="G12" s="13">
         <v>110006</v>
       </c>
       <c r="H12" s="9"/>
       <c r="I12" s="22" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="J12" s="14"/>
       <c r="K12" s="15">
@@ -2632,8 +2621,8 @@
       <c r="L12" s="8">
         <v>2000012</v>
       </c>
-      <c r="M12" s="16" t="s">
-        <v>103</v>
+      <c r="M12" s="8">
+        <v>110006</v>
       </c>
       <c r="N12" s="13">
         <v>1</v>
@@ -2651,16 +2640,16 @@
         <v>0</v>
       </c>
       <c r="S12" s="9" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="T12" s="9" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="U12" s="9" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="V12" s="9" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="W12" s="13">
         <v>2</v>
@@ -2679,10 +2668,10 @@
         <v>41001</v>
       </c>
       <c r="AC12" s="9" t="s">
-        <v>81</v>
+        <v>213</v>
       </c>
       <c r="AD12" s="9" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="AE12" s="9"/>
       <c r="AF12" s="13">
@@ -2695,7 +2684,7 @@
         <v>601500501</v>
       </c>
       <c r="AI12" s="20" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
     <row r="13" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -2704,20 +2693,20 @@
         <v>110007</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="G13" s="13">
         <v>110007</v>
       </c>
       <c r="H13" s="9"/>
       <c r="I13" s="22" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="J13" s="14"/>
       <c r="K13" s="15">
@@ -2726,8 +2715,8 @@
       <c r="L13" s="8">
         <v>2000013</v>
       </c>
-      <c r="M13" s="16" t="s">
-        <v>94</v>
+      <c r="M13" s="8">
+        <v>110007</v>
       </c>
       <c r="N13" s="13">
         <v>1</v>
@@ -2745,16 +2734,16 @@
         <v>0</v>
       </c>
       <c r="S13" s="9" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="T13" s="9" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="U13" s="9" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="V13" s="9" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="W13" s="13">
         <v>2</v>
@@ -2773,10 +2762,10 @@
         <v>42001</v>
       </c>
       <c r="AC13" s="9" t="s">
-        <v>81</v>
+        <v>213</v>
       </c>
       <c r="AD13" s="9" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="AE13" s="9"/>
       <c r="AF13" s="13">
@@ -2789,7 +2778,7 @@
         <v>601500501</v>
       </c>
       <c r="AI13" s="20" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="14" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -2798,16 +2787,16 @@
         <v>2000001</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="F14" s="9"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
       <c r="I14" s="22" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="J14" s="8"/>
       <c r="K14" s="8">
@@ -2817,7 +2806,7 @@
         <v>2000001</v>
       </c>
       <c r="M14" s="16" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="N14" s="13">
         <v>1</v>
@@ -2835,7 +2824,7 @@
         <v>1</v>
       </c>
       <c r="S14" s="9" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="T14" s="9" t="s">
         <v>70</v>
@@ -2855,7 +2844,7 @@
       </c>
       <c r="Z14" s="13"/>
       <c r="AA14" s="19" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="AB14" s="9"/>
       <c r="AC14" s="9"/>
@@ -2865,7 +2854,7 @@
       <c r="AG14" s="13"/>
       <c r="AH14" s="13"/>
       <c r="AI14" s="23" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -2874,16 +2863,16 @@
         <v>2000002</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="F15" s="9"/>
       <c r="G15" s="9"/>
       <c r="H15" s="9"/>
       <c r="I15" s="22" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="J15" s="8"/>
       <c r="K15" s="8">
@@ -2893,25 +2882,25 @@
         <v>2000002</v>
       </c>
       <c r="M15" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="N15" s="13">
+        <v>1</v>
+      </c>
+      <c r="O15" s="13">
+        <v>0</v>
+      </c>
+      <c r="P15" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="13">
+        <v>0</v>
+      </c>
+      <c r="R15" s="13">
+        <v>1</v>
+      </c>
+      <c r="S15" s="9" t="s">
         <v>123</v>
-      </c>
-      <c r="N15" s="13">
-        <v>1</v>
-      </c>
-      <c r="O15" s="13">
-        <v>0</v>
-      </c>
-      <c r="P15" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="13">
-        <v>0</v>
-      </c>
-      <c r="R15" s="13">
-        <v>1</v>
-      </c>
-      <c r="S15" s="9" t="s">
-        <v>128</v>
       </c>
       <c r="T15" s="9" t="s">
         <v>70</v>
@@ -2939,7 +2928,7 @@
       <c r="AG15" s="13"/>
       <c r="AH15" s="13"/>
       <c r="AI15" s="20" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="16" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -2948,16 +2937,16 @@
         <v>2000003</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="F16" s="9"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
       <c r="I16" s="22" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="J16" s="8"/>
       <c r="K16" s="8">
@@ -2966,8 +2955,8 @@
       <c r="L16" s="8">
         <v>2000003</v>
       </c>
-      <c r="M16" s="16" t="s">
-        <v>123</v>
+      <c r="M16" s="16">
+        <v>2000003</v>
       </c>
       <c r="N16" s="13">
         <v>0</v>
@@ -2985,7 +2974,7 @@
         <v>1</v>
       </c>
       <c r="S16" s="9" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="T16" s="9" t="s">
         <v>70</v>
@@ -3020,16 +3009,16 @@
         <v>2000004</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="F17" s="9"/>
       <c r="G17" s="9"/>
       <c r="H17" s="9"/>
       <c r="I17" s="22" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="J17" s="8"/>
       <c r="K17" s="8">
@@ -3038,8 +3027,8 @@
       <c r="L17" s="8">
         <v>2000003</v>
       </c>
-      <c r="M17" s="16" t="s">
-        <v>123</v>
+      <c r="M17" s="16">
+        <v>2000003</v>
       </c>
       <c r="N17" s="13">
         <v>0</v>
@@ -3057,7 +3046,7 @@
         <v>1</v>
       </c>
       <c r="S17" s="9" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="T17" s="9" t="s">
         <v>70</v>
@@ -3077,7 +3066,7 @@
       </c>
       <c r="Z17" s="13"/>
       <c r="AA17" s="8" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="AB17" s="13"/>
       <c r="AC17" s="9"/>
@@ -3093,16 +3082,16 @@
         <v>2000008</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="F18" s="9"/>
       <c r="G18" s="9"/>
       <c r="H18" s="9"/>
       <c r="I18" s="22" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="J18" s="8">
         <v>20000038</v>
@@ -3114,25 +3103,25 @@
         <v>2000008</v>
       </c>
       <c r="M18" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="N18" s="13">
+        <v>1</v>
+      </c>
+      <c r="O18" s="13">
+        <v>0</v>
+      </c>
+      <c r="P18" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="13">
+        <v>0</v>
+      </c>
+      <c r="R18" s="13">
+        <v>1</v>
+      </c>
+      <c r="S18" s="9" t="s">
         <v>123</v>
-      </c>
-      <c r="N18" s="13">
-        <v>1</v>
-      </c>
-      <c r="O18" s="13">
-        <v>0</v>
-      </c>
-      <c r="P18" s="13">
-        <v>1</v>
-      </c>
-      <c r="Q18" s="13">
-        <v>0</v>
-      </c>
-      <c r="R18" s="13">
-        <v>1</v>
-      </c>
-      <c r="S18" s="9" t="s">
-        <v>128</v>
       </c>
       <c r="T18" s="9" t="s">
         <v>70</v>
@@ -3141,7 +3130,7 @@
         <v>12</v>
       </c>
       <c r="V18" s="9" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="W18" s="13">
         <v>0</v>
@@ -3154,7 +3143,7 @@
       </c>
       <c r="Z18" s="13"/>
       <c r="AA18" s="8" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="AB18" s="13"/>
       <c r="AC18" s="9"/>
@@ -3164,7 +3153,7 @@
       <c r="AG18" s="13"/>
       <c r="AH18" s="13"/>
       <c r="AI18" s="23" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="19" spans="2:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -3172,19 +3161,19 @@
         <v>2000009</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="F19" s="9"/>
       <c r="G19" s="9"/>
       <c r="H19" s="9"/>
       <c r="I19" s="22" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J19" s="24" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="K19" s="8">
         <v>17</v>
@@ -3193,7 +3182,7 @@
         <v>2000009</v>
       </c>
       <c r="M19" s="16" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="N19" s="13">
         <v>1</v>
@@ -3211,7 +3200,7 @@
         <v>1</v>
       </c>
       <c r="S19" s="9" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="T19" s="9" t="s">
         <v>70</v>
@@ -3220,7 +3209,7 @@
         <v>12</v>
       </c>
       <c r="V19" s="9" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="W19" s="13">
         <v>0</v>
@@ -3243,7 +3232,7 @@
       <c r="AG19" s="13"/>
       <c r="AH19" s="13"/>
       <c r="AI19" s="23" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="20" spans="2:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -3251,16 +3240,16 @@
         <v>2000010</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="F20" s="9"/>
       <c r="G20" s="9"/>
       <c r="H20" s="9"/>
       <c r="I20" s="22" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="J20" s="8"/>
       <c r="K20" s="8">
@@ -3288,7 +3277,7 @@
         <v>1</v>
       </c>
       <c r="S20" s="9" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="T20" s="9" t="s">
         <v>70</v>
@@ -3308,7 +3297,7 @@
       </c>
       <c r="Z20" s="13"/>
       <c r="AA20" s="8" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="AB20" s="13"/>
       <c r="AC20" s="9"/>
@@ -3318,7 +3307,7 @@
       <c r="AG20" s="13"/>
       <c r="AH20" s="13"/>
       <c r="AI20" s="20" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="21" spans="2:35" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -3327,19 +3316,19 @@
         <v>2000011</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="F21" s="9"/>
       <c r="G21" s="9"/>
       <c r="H21" s="9"/>
       <c r="I21" s="22" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="K21" s="9" t="s">
         <v>69</v>
@@ -3366,7 +3355,7 @@
         <v>1</v>
       </c>
       <c r="S21" s="9" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="T21" s="9" t="s">
         <v>71</v>
@@ -3404,7 +3393,7 @@
         <v>0</v>
       </c>
       <c r="AI21" s="20" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="22" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -3413,16 +3402,16 @@
         <v>2100001</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="F22" s="9"/>
       <c r="G22" s="9"/>
       <c r="H22" s="9"/>
       <c r="I22" s="22" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="J22" s="8"/>
       <c r="K22" s="8">
@@ -3450,7 +3439,7 @@
         <v>1</v>
       </c>
       <c r="S22" s="9" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="T22" s="9" t="s">
         <v>70</v>
@@ -3485,16 +3474,16 @@
         <v>2100002</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="F23" s="9"/>
       <c r="G23" s="9"/>
       <c r="H23" s="9"/>
       <c r="I23" s="22" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="J23" s="8"/>
       <c r="K23" s="8">
@@ -3522,7 +3511,7 @@
         <v>1</v>
       </c>
       <c r="S23" s="9" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="T23" s="9" t="s">
         <v>70</v>
@@ -3557,16 +3546,16 @@
         <v>2200001</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="F24" s="9"/>
       <c r="G24" s="9"/>
       <c r="H24" s="9"/>
       <c r="I24" s="22" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="J24" s="8"/>
       <c r="K24" s="8">
@@ -3594,7 +3583,7 @@
         <v>1</v>
       </c>
       <c r="S24" s="9" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="T24" s="9" t="s">
         <v>70</v>
@@ -3628,19 +3617,19 @@
         <v>3000001</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F25" s="9"/>
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
       <c r="I25" s="22" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="J25" s="17" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="K25" s="8">
         <v>12</v>
@@ -3667,7 +3656,7 @@
         <v>1</v>
       </c>
       <c r="S25" s="9" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="T25" s="9" t="s">
         <v>70</v>
@@ -3676,7 +3665,7 @@
         <v>10</v>
       </c>
       <c r="V25" s="9" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="W25" s="13">
         <v>40</v>
@@ -3690,7 +3679,7 @@
       <c r="Z25" s="13"/>
       <c r="AA25" s="8"/>
       <c r="AB25" s="25" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="AC25" s="9"/>
       <c r="AD25" s="9"/>
@@ -3699,7 +3688,7 @@
       <c r="AG25" s="13"/>
       <c r="AH25" s="13"/>
       <c r="AI25" s="20" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="26" spans="2:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -3707,19 +3696,19 @@
         <v>3000002</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="F26" s="9"/>
       <c r="G26" s="9"/>
       <c r="H26" s="9"/>
       <c r="I26" s="22" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="J26" s="17" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="K26" s="8">
         <v>12</v>
@@ -3746,7 +3735,7 @@
         <v>1</v>
       </c>
       <c r="S26" s="9" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="T26" s="9" t="s">
         <v>70</v>
@@ -3755,7 +3744,7 @@
         <v>30</v>
       </c>
       <c r="V26" s="9" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="W26" s="13">
         <v>40</v>
@@ -3769,7 +3758,7 @@
       <c r="Z26" s="13"/>
       <c r="AA26" s="8"/>
       <c r="AB26" s="25" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="AC26" s="9"/>
       <c r="AD26" s="9"/>
@@ -3778,7 +3767,7 @@
       <c r="AG26" s="13"/>
       <c r="AH26" s="13"/>
       <c r="AI26" s="20" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="27" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -3787,16 +3776,16 @@
         <v>4000001</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F27" s="9"/>
       <c r="G27" s="9"/>
       <c r="H27" s="9"/>
       <c r="I27" s="22" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="J27" s="8"/>
       <c r="K27" s="8">
@@ -3805,8 +3794,8 @@
       <c r="L27" s="8">
         <v>2000004</v>
       </c>
-      <c r="M27" s="13">
-        <v>0</v>
+      <c r="M27" s="8">
+        <v>2000004</v>
       </c>
       <c r="N27" s="13">
         <v>0</v>
@@ -3824,7 +3813,7 @@
         <v>1</v>
       </c>
       <c r="S27" s="9" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="T27" s="9" t="s">
         <v>70</v>
@@ -3844,7 +3833,7 @@
       </c>
       <c r="Z27" s="13"/>
       <c r="AA27" s="8" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="AB27" s="13"/>
       <c r="AC27" s="9"/>
@@ -3861,16 +3850,16 @@
         <v>5000001</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F28" s="9"/>
       <c r="G28" s="9"/>
       <c r="H28" s="9"/>
       <c r="I28" s="22" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="J28" s="8"/>
       <c r="K28" s="8">
@@ -3879,8 +3868,8 @@
       <c r="L28" s="8">
         <v>2000004</v>
       </c>
-      <c r="M28" s="13">
-        <v>0</v>
+      <c r="M28" s="8">
+        <v>2000004</v>
       </c>
       <c r="N28" s="13">
         <v>0</v>
@@ -3898,7 +3887,7 @@
         <v>1</v>
       </c>
       <c r="S28" s="9" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="T28" s="9" t="s">
         <v>70</v>
@@ -3918,7 +3907,7 @@
       </c>
       <c r="Z28" s="13"/>
       <c r="AA28" s="8" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="AB28" s="13"/>
       <c r="AC28" s="9"/>
@@ -3934,16 +3923,16 @@
         <v>6000001</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="F29" s="9"/>
       <c r="G29" s="9"/>
       <c r="H29" s="9"/>
       <c r="I29" s="22" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="J29" s="8"/>
       <c r="K29" s="8">
@@ -3952,8 +3941,8 @@
       <c r="L29" s="8">
         <v>2000006</v>
       </c>
-      <c r="M29" s="13">
-        <v>0</v>
+      <c r="M29" s="16" t="s">
+        <v>118</v>
       </c>
       <c r="N29" s="13">
         <v>1</v>
@@ -3971,7 +3960,7 @@
         <v>1</v>
       </c>
       <c r="S29" s="9" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="T29" s="9" t="s">
         <v>70</v>
@@ -3980,7 +3969,7 @@
         <v>12</v>
       </c>
       <c r="V29" s="9" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="W29" s="13">
         <v>100</v>
@@ -3993,7 +3982,7 @@
       </c>
       <c r="Z29" s="13"/>
       <c r="AA29" s="8" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="AB29" s="13"/>
       <c r="AC29" s="9"/>
@@ -4003,7 +3992,7 @@
       <c r="AG29" s="13"/>
       <c r="AH29" s="13"/>
       <c r="AI29" s="20" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="30" spans="2:35" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -4012,16 +4001,16 @@
         <v>6000002</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="F30" s="12"/>
       <c r="G30" s="12"/>
       <c r="H30" s="12"/>
       <c r="I30" s="26" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="J30" s="11"/>
       <c r="K30" s="11">
@@ -4049,7 +4038,7 @@
         <v>1</v>
       </c>
       <c r="S30" s="12" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="T30" s="12" t="s">
         <v>70</v>
@@ -4079,7 +4068,7 @@
       <c r="AG30" s="18"/>
       <c r="AH30" s="18"/>
       <c r="AI30" s="21" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="31" spans="2:35" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -4088,16 +4077,16 @@
         <v>6000003</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="F31" s="12"/>
       <c r="G31" s="12"/>
       <c r="H31" s="12"/>
       <c r="I31" s="26" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="J31" s="11"/>
       <c r="K31" s="11">
@@ -4125,7 +4114,7 @@
         <v>1</v>
       </c>
       <c r="S31" s="12" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="T31" s="12" t="s">
         <v>70</v>
@@ -4153,7 +4142,7 @@
       <c r="AG31" s="18"/>
       <c r="AH31" s="18"/>
       <c r="AI31" s="21" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="32" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -4162,16 +4151,16 @@
         <v>7000001</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="F32" s="9"/>
       <c r="G32" s="9"/>
       <c r="H32" s="9"/>
       <c r="I32" s="22" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="J32" s="8"/>
       <c r="K32" s="8">
@@ -4199,7 +4188,7 @@
         <v>1</v>
       </c>
       <c r="S32" s="9" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="T32" s="9" t="s">
         <v>70</v>
@@ -4219,7 +4208,7 @@
       </c>
       <c r="Z32" s="13"/>
       <c r="AA32" s="8" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="AB32" s="13"/>
       <c r="AC32" s="9"/>
@@ -4236,16 +4225,16 @@
         <v>8000001</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="F33" s="9"/>
       <c r="G33" s="9"/>
       <c r="H33" s="9"/>
       <c r="I33" s="22" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="J33" s="8"/>
       <c r="K33" s="8">
@@ -4273,7 +4262,7 @@
         <v>1</v>
       </c>
       <c r="S33" s="9" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="T33" s="9" t="s">
         <v>70</v>
@@ -4301,7 +4290,7 @@
       <c r="AG33" s="13"/>
       <c r="AH33" s="13"/>
       <c r="AI33" s="20" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="34" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -4310,16 +4299,16 @@
         <v>2400001</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="F34" s="9"/>
       <c r="G34" s="9"/>
       <c r="H34" s="9"/>
       <c r="I34" s="22" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="J34" s="8"/>
       <c r="K34" s="8">
@@ -4347,7 +4336,7 @@
         <v>1</v>
       </c>
       <c r="S34" s="9" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="T34" s="9" t="s">
         <v>70</v>
@@ -4382,16 +4371,16 @@
         <v>2500001</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="F35" s="9"/>
       <c r="G35" s="9"/>
       <c r="H35" s="9"/>
       <c r="I35" s="22" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="J35" s="8"/>
       <c r="K35" s="8">
@@ -4419,7 +4408,7 @@
         <v>1</v>
       </c>
       <c r="S35" s="9" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="T35" s="9" t="s">
         <v>70</v>
@@ -4439,7 +4428,7 @@
       </c>
       <c r="Z35" s="13"/>
       <c r="AA35" s="8" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="AB35" s="13"/>
       <c r="AC35" s="9"/>
@@ -4455,16 +4444,16 @@
         <v>2600001</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="F36" s="9"/>
       <c r="G36" s="9"/>
       <c r="H36" s="9"/>
       <c r="I36" s="22" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="J36" s="8"/>
       <c r="K36" s="8">
@@ -4492,7 +4481,7 @@
         <v>1</v>
       </c>
       <c r="S36" s="9" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="T36" s="9" t="s">
         <v>70</v>
@@ -4520,7 +4509,7 @@
       <c r="AG36" s="13"/>
       <c r="AH36" s="13"/>
       <c r="AI36" s="20" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="37" spans="2:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>

--- a/Excel/SceneConfig.xlsx
+++ b/Excel/SceneConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3C10571-6F88-4364-A7AD-F81F4F3B4B42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4FDA188-7370-4B51-8F3A-256DB5B9FD1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -492,9 +492,6 @@
     <t>-220,-25,4000</t>
   </si>
   <si>
-    <t>20000001,20000002,20000003,20000004,20000006,20000009,20000010,20000011,20000012,20000013,20000014,20000015,20000016,20000017,20000018,20000019,20000020,20000021,20000022,20000023,20000024,20000025,20000026,20000027,20000028,20000029,20000030,20000031,20000032,20000033,20000036,20000037,30000011,20000039,20000040,20000041,20000042,20000043</t>
-  </si>
-  <si>
     <t>3</t>
   </si>
   <si>
@@ -576,9 +573,6 @@
     <t>46.9,93.7,105,0,105</t>
   </si>
   <si>
-    <t>森林巢穴</t>
-  </si>
-  <si>
     <t>ImgBig_11</t>
   </si>
   <si>
@@ -600,9 +594,6 @@
     <t>4,100,4,0,65</t>
   </si>
   <si>
-    <t>上古遗迹</t>
-  </si>
-  <si>
     <t>ImgBig_15</t>
   </si>
   <si>
@@ -619,9 +610,6 @@
   </si>
   <si>
     <t>35,89,10,0,90</t>
-  </si>
-  <si>
-    <t>炙热熔炎</t>
   </si>
   <si>
     <t>ImgBig_16</t>
@@ -1075,6 +1063,22 @@
   </si>
   <si>
     <t>ImgBig_13</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>20000001,20000002,20000003,20000004,20000006,20000009,20000010,20000011,20000012,20000013,20000014,20000015,20000016,20000017,20000018,20000019,20000020,20000021,20000022,20000023,20000024,20000025,20000026,20000027,20000028,20000029,20000030,20000031,20000032,20000033,20000036,20000037,30000011,20000039,20000040,20000041,20000042,20000043,20000044</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>森林巢穴</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>上古遗迹</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>炙热熔炎</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -1725,13 +1729,13 @@
   <sheetData>
     <row r="2" spans="2:35" x14ac:dyDescent="0.15">
       <c r="E2" s="4" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>0</v>
       </c>
       <c r="AD2" s="4" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="2:35" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -1843,7 +1847,7 @@
         <v>31</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>32</v>
@@ -1918,7 +1922,7 @@
         <v>55</v>
       </c>
       <c r="AD4" s="6" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="AE4" s="6" t="s">
         <v>56</v>
@@ -2046,7 +2050,7 @@
         <v>65</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F6" s="9"/>
       <c r="G6" s="9"/>
@@ -2057,10 +2061,10 @@
         <v>67</v>
       </c>
       <c r="J6" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="K6" s="9" t="s">
         <v>68</v>
-      </c>
-      <c r="K6" s="9" t="s">
-        <v>69</v>
       </c>
       <c r="L6" s="13">
         <v>101</v>
@@ -2085,13 +2089,13 @@
       </c>
       <c r="S6" s="9"/>
       <c r="T6" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="U6" s="13">
+        <v>0</v>
+      </c>
+      <c r="V6" s="9" t="s">
         <v>70</v>
-      </c>
-      <c r="U6" s="13">
-        <v>0</v>
-      </c>
-      <c r="V6" s="9" t="s">
-        <v>71</v>
       </c>
       <c r="W6" s="13">
         <v>0</v>
@@ -2120,7 +2124,7 @@
         <v>0</v>
       </c>
       <c r="AI6" s="20" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -2129,20 +2133,20 @@
         <v>110001</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="G7" s="13">
         <v>110001</v>
       </c>
       <c r="H7" s="9"/>
       <c r="I7" s="22" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J7" s="14"/>
       <c r="K7" s="15">
@@ -2170,16 +2174,16 @@
         <v>0</v>
       </c>
       <c r="S7" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="T7" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="T7" s="9" t="s">
+      <c r="U7" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="V7" s="9" t="s">
         <v>76</v>
-      </c>
-      <c r="U7" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="V7" s="9" t="s">
-        <v>77</v>
       </c>
       <c r="W7" s="13">
         <v>2</v>
@@ -2194,14 +2198,14 @@
         <v>72001013</v>
       </c>
       <c r="AA7" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AB7" s="9"/>
       <c r="AC7" s="9" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="AD7" s="9" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="AE7" s="9"/>
       <c r="AF7" s="13">
@@ -2214,7 +2218,7 @@
         <v>601500201</v>
       </c>
       <c r="AI7" s="20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -2223,20 +2227,20 @@
         <v>110002</v>
       </c>
       <c r="D8" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="F8" s="9" t="s">
         <v>80</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>81</v>
       </c>
       <c r="G8" s="13">
         <v>110002</v>
       </c>
       <c r="H8" s="9"/>
       <c r="I8" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J8" s="8"/>
       <c r="K8" s="8">
@@ -2264,16 +2268,16 @@
         <v>0</v>
       </c>
       <c r="S8" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="T8" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="T8" s="9" t="s">
+      <c r="U8" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="V8" s="9" t="s">
         <v>84</v>
-      </c>
-      <c r="U8" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="V8" s="9" t="s">
-        <v>85</v>
       </c>
       <c r="W8" s="13">
         <v>2</v>
@@ -2288,14 +2292,14 @@
         <v>72002013</v>
       </c>
       <c r="AA8" s="22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AB8" s="9"/>
       <c r="AC8" s="9" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="AD8" s="9" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="AE8" s="9"/>
       <c r="AF8" s="13">
@@ -2308,7 +2312,7 @@
         <v>601500301</v>
       </c>
       <c r="AI8" s="20" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -2317,20 +2321,20 @@
         <v>110003</v>
       </c>
       <c r="D9" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="F9" s="9" t="s">
         <v>88</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>89</v>
       </c>
       <c r="G9" s="13">
         <v>110003</v>
       </c>
       <c r="H9" s="9"/>
       <c r="I9" s="22" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J9" s="8"/>
       <c r="K9" s="8">
@@ -2358,16 +2362,16 @@
         <v>0</v>
       </c>
       <c r="S9" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="T9" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="T9" s="9" t="s">
+      <c r="U9" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="V9" s="9" t="s">
         <v>92</v>
-      </c>
-      <c r="U9" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="V9" s="9" t="s">
-        <v>93</v>
       </c>
       <c r="W9" s="13">
         <v>2</v>
@@ -2382,14 +2386,14 @@
         <v>72003013</v>
       </c>
       <c r="AA9" s="22" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB9" s="9"/>
       <c r="AC9" s="9" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="AD9" s="9" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="AE9" s="9"/>
       <c r="AF9" s="13">
@@ -2402,7 +2406,7 @@
         <v>601500401</v>
       </c>
       <c r="AI9" s="20" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -2411,20 +2415,20 @@
         <v>110004</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>96</v>
+        <v>212</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G10" s="13">
         <v>110004</v>
       </c>
       <c r="H10" s="9"/>
       <c r="I10" s="22" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="J10" s="14"/>
       <c r="K10" s="15">
@@ -2452,16 +2456,16 @@
         <v>0</v>
       </c>
       <c r="S10" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="T10" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="U10" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="V10" s="9" t="s">
         <v>99</v>
-      </c>
-      <c r="T10" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="U10" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="V10" s="9" t="s">
-        <v>101</v>
       </c>
       <c r="W10" s="13">
         <v>2</v>
@@ -2476,14 +2480,14 @@
         <v>72004013</v>
       </c>
       <c r="AA10" s="22" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="AB10" s="9"/>
       <c r="AC10" s="9" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="AD10" s="9" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="AE10" s="9"/>
       <c r="AF10" s="13">
@@ -2496,7 +2500,7 @@
         <v>601500501</v>
       </c>
       <c r="AI10" s="20" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -2505,20 +2509,20 @@
         <v>110005</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>104</v>
+        <v>213</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G11" s="13">
         <v>110005</v>
       </c>
       <c r="H11" s="9"/>
       <c r="I11" s="22" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="J11" s="14"/>
       <c r="K11" s="15">
@@ -2546,16 +2550,16 @@
         <v>0</v>
       </c>
       <c r="S11" s="9" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="T11" s="9" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="U11" s="9" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="V11" s="9" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="W11" s="13">
         <v>2</v>
@@ -2574,10 +2578,10 @@
         <v>40001</v>
       </c>
       <c r="AC11" s="9" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="AD11" s="9" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="AE11" s="9"/>
       <c r="AF11" s="13">
@@ -2590,7 +2594,7 @@
         <v>601500501</v>
       </c>
       <c r="AI11" s="20" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -2599,20 +2603,20 @@
         <v>110006</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>111</v>
+        <v>214</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="G12" s="13">
         <v>110006</v>
       </c>
       <c r="H12" s="9"/>
       <c r="I12" s="22" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="J12" s="14"/>
       <c r="K12" s="15">
@@ -2640,16 +2644,16 @@
         <v>0</v>
       </c>
       <c r="S12" s="9" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="T12" s="9" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="U12" s="9" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="V12" s="9" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="W12" s="13">
         <v>2</v>
@@ -2668,10 +2672,10 @@
         <v>41001</v>
       </c>
       <c r="AC12" s="9" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="AD12" s="9" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="AE12" s="9"/>
       <c r="AF12" s="13">
@@ -2684,7 +2688,7 @@
         <v>601500501</v>
       </c>
       <c r="AI12" s="20" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -2693,20 +2697,20 @@
         <v>110007</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="G13" s="13">
         <v>110007</v>
       </c>
       <c r="H13" s="9"/>
       <c r="I13" s="22" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="J13" s="14"/>
       <c r="K13" s="15">
@@ -2734,16 +2738,16 @@
         <v>0</v>
       </c>
       <c r="S13" s="9" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="T13" s="9" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="U13" s="9" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="V13" s="9" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="W13" s="13">
         <v>2</v>
@@ -2762,10 +2766,10 @@
         <v>42001</v>
       </c>
       <c r="AC13" s="9" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="AD13" s="9" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="AE13" s="9"/>
       <c r="AF13" s="13">
@@ -2778,7 +2782,7 @@
         <v>601500501</v>
       </c>
       <c r="AI13" s="20" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="14" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -2787,16 +2791,16 @@
         <v>2000001</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="F14" s="9"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
       <c r="I14" s="22" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="J14" s="8"/>
       <c r="K14" s="8">
@@ -2806,7 +2810,7 @@
         <v>2000001</v>
       </c>
       <c r="M14" s="16" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="N14" s="13">
         <v>1</v>
@@ -2824,10 +2828,10 @@
         <v>1</v>
       </c>
       <c r="S14" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T14" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="U14" s="13">
         <v>1</v>
@@ -2844,7 +2848,7 @@
       </c>
       <c r="Z14" s="13"/>
       <c r="AA14" s="19" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AB14" s="9"/>
       <c r="AC14" s="9"/>
@@ -2854,7 +2858,7 @@
       <c r="AG14" s="13"/>
       <c r="AH14" s="13"/>
       <c r="AI14" s="23" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -2863,16 +2867,16 @@
         <v>2000002</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="F15" s="9"/>
       <c r="G15" s="9"/>
       <c r="H15" s="9"/>
       <c r="I15" s="22" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J15" s="8"/>
       <c r="K15" s="8">
@@ -2882,7 +2886,7 @@
         <v>2000002</v>
       </c>
       <c r="M15" s="16" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="N15" s="13">
         <v>1</v>
@@ -2900,10 +2904,10 @@
         <v>1</v>
       </c>
       <c r="S15" s="9" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="T15" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="U15" s="13">
         <v>1</v>
@@ -2928,7 +2932,7 @@
       <c r="AG15" s="13"/>
       <c r="AH15" s="13"/>
       <c r="AI15" s="20" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -2937,16 +2941,16 @@
         <v>2000003</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="F16" s="9"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
       <c r="I16" s="22" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="J16" s="8"/>
       <c r="K16" s="8">
@@ -2974,10 +2978,10 @@
         <v>1</v>
       </c>
       <c r="S16" s="9" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="T16" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="U16" s="13">
         <v>1</v>
@@ -3009,16 +3013,16 @@
         <v>2000004</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="F17" s="9"/>
       <c r="G17" s="9"/>
       <c r="H17" s="9"/>
       <c r="I17" s="22" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="J17" s="8"/>
       <c r="K17" s="8">
@@ -3046,10 +3050,10 @@
         <v>1</v>
       </c>
       <c r="S17" s="9" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="T17" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="U17" s="13">
         <v>1</v>
@@ -3066,7 +3070,7 @@
       </c>
       <c r="Z17" s="13"/>
       <c r="AA17" s="8" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="AB17" s="13"/>
       <c r="AC17" s="9"/>
@@ -3082,16 +3086,16 @@
         <v>2000008</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F18" s="9"/>
       <c r="G18" s="9"/>
       <c r="H18" s="9"/>
       <c r="I18" s="22" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="J18" s="8">
         <v>20000038</v>
@@ -3103,7 +3107,7 @@
         <v>2000008</v>
       </c>
       <c r="M18" s="16" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="N18" s="13">
         <v>1</v>
@@ -3121,16 +3125,16 @@
         <v>1</v>
       </c>
       <c r="S18" s="9" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="T18" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="U18" s="13">
         <v>12</v>
       </c>
       <c r="V18" s="9" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="W18" s="13">
         <v>0</v>
@@ -3143,7 +3147,7 @@
       </c>
       <c r="Z18" s="13"/>
       <c r="AA18" s="8" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="AB18" s="13"/>
       <c r="AC18" s="9"/>
@@ -3153,7 +3157,7 @@
       <c r="AG18" s="13"/>
       <c r="AH18" s="13"/>
       <c r="AI18" s="23" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="19" spans="2:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -3161,19 +3165,19 @@
         <v>2000009</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="F19" s="9"/>
       <c r="G19" s="9"/>
       <c r="H19" s="9"/>
       <c r="I19" s="22" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="J19" s="24" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="K19" s="8">
         <v>17</v>
@@ -3182,7 +3186,7 @@
         <v>2000009</v>
       </c>
       <c r="M19" s="16" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="N19" s="13">
         <v>1</v>
@@ -3200,16 +3204,16 @@
         <v>1</v>
       </c>
       <c r="S19" s="9" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="T19" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="U19" s="13">
         <v>12</v>
       </c>
       <c r="V19" s="9" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="W19" s="13">
         <v>0</v>
@@ -3232,7 +3236,7 @@
       <c r="AG19" s="13"/>
       <c r="AH19" s="13"/>
       <c r="AI19" s="23" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="20" spans="2:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -3240,16 +3244,16 @@
         <v>2000010</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="F20" s="9"/>
       <c r="G20" s="9"/>
       <c r="H20" s="9"/>
       <c r="I20" s="22" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="J20" s="8"/>
       <c r="K20" s="8">
@@ -3277,10 +3281,10 @@
         <v>1</v>
       </c>
       <c r="S20" s="9" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="T20" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="U20" s="13">
         <v>1</v>
@@ -3297,7 +3301,7 @@
       </c>
       <c r="Z20" s="13"/>
       <c r="AA20" s="8" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="AB20" s="13"/>
       <c r="AC20" s="9"/>
@@ -3307,7 +3311,7 @@
       <c r="AG20" s="13"/>
       <c r="AH20" s="13"/>
       <c r="AI20" s="20" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21" spans="2:35" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -3316,22 +3320,22 @@
         <v>2000011</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F21" s="9"/>
       <c r="G21" s="9"/>
       <c r="H21" s="9"/>
       <c r="I21" s="22" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="K21" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L21" s="13">
         <v>102</v>
@@ -3355,16 +3359,16 @@
         <v>1</v>
       </c>
       <c r="S21" s="9" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="T21" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="U21" s="13">
         <v>10</v>
       </c>
       <c r="V21" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="W21" s="13">
         <v>0</v>
@@ -3393,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="AI21" s="20" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="22" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -3402,16 +3406,16 @@
         <v>2100001</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="F22" s="9"/>
       <c r="G22" s="9"/>
       <c r="H22" s="9"/>
       <c r="I22" s="22" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="J22" s="8"/>
       <c r="K22" s="8">
@@ -3439,10 +3443,10 @@
         <v>1</v>
       </c>
       <c r="S22" s="9" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="T22" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="U22" s="13">
         <v>1</v>
@@ -3474,16 +3478,16 @@
         <v>2100002</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F23" s="9"/>
       <c r="G23" s="9"/>
       <c r="H23" s="9"/>
       <c r="I23" s="22" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="J23" s="8"/>
       <c r="K23" s="8">
@@ -3511,10 +3515,10 @@
         <v>1</v>
       </c>
       <c r="S23" s="9" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="T23" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="U23" s="13">
         <v>1</v>
@@ -3546,16 +3550,16 @@
         <v>2200001</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="F24" s="9"/>
       <c r="G24" s="9"/>
       <c r="H24" s="9"/>
       <c r="I24" s="22" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="J24" s="8"/>
       <c r="K24" s="8">
@@ -3583,10 +3587,10 @@
         <v>1</v>
       </c>
       <c r="S24" s="9" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="T24" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="U24" s="13">
         <v>1</v>
@@ -3617,19 +3621,19 @@
         <v>3000001</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F25" s="9"/>
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
       <c r="I25" s="22" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="J25" s="17" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="K25" s="8">
         <v>12</v>
@@ -3656,16 +3660,16 @@
         <v>1</v>
       </c>
       <c r="S25" s="9" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="T25" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="U25" s="13">
         <v>10</v>
       </c>
       <c r="V25" s="9" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="W25" s="13">
         <v>40</v>
@@ -3679,7 +3683,7 @@
       <c r="Z25" s="13"/>
       <c r="AA25" s="8"/>
       <c r="AB25" s="25" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="AC25" s="9"/>
       <c r="AD25" s="9"/>
@@ -3688,7 +3692,7 @@
       <c r="AG25" s="13"/>
       <c r="AH25" s="13"/>
       <c r="AI25" s="20" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="26" spans="2:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -3696,19 +3700,19 @@
         <v>3000002</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="F26" s="9"/>
       <c r="G26" s="9"/>
       <c r="H26" s="9"/>
       <c r="I26" s="22" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="J26" s="17" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="K26" s="8">
         <v>12</v>
@@ -3735,16 +3739,16 @@
         <v>1</v>
       </c>
       <c r="S26" s="9" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="T26" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="U26" s="13">
         <v>30</v>
       </c>
       <c r="V26" s="9" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="W26" s="13">
         <v>40</v>
@@ -3758,7 +3762,7 @@
       <c r="Z26" s="13"/>
       <c r="AA26" s="8"/>
       <c r="AB26" s="25" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="AC26" s="9"/>
       <c r="AD26" s="9"/>
@@ -3767,7 +3771,7 @@
       <c r="AG26" s="13"/>
       <c r="AH26" s="13"/>
       <c r="AI26" s="20" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="27" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -3776,16 +3780,16 @@
         <v>4000001</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F27" s="9"/>
       <c r="G27" s="9"/>
       <c r="H27" s="9"/>
       <c r="I27" s="22" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="J27" s="8"/>
       <c r="K27" s="8">
@@ -3813,10 +3817,10 @@
         <v>1</v>
       </c>
       <c r="S27" s="9" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="T27" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="U27" s="13">
         <v>10</v>
@@ -3833,7 +3837,7 @@
       </c>
       <c r="Z27" s="13"/>
       <c r="AA27" s="8" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="AB27" s="13"/>
       <c r="AC27" s="9"/>
@@ -3850,16 +3854,16 @@
         <v>5000001</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F28" s="9"/>
       <c r="G28" s="9"/>
       <c r="H28" s="9"/>
       <c r="I28" s="22" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="J28" s="8"/>
       <c r="K28" s="8">
@@ -3887,10 +3891,10 @@
         <v>1</v>
       </c>
       <c r="S28" s="9" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="T28" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="U28" s="13">
         <v>10</v>
@@ -3907,7 +3911,7 @@
       </c>
       <c r="Z28" s="13"/>
       <c r="AA28" s="8" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="AB28" s="13"/>
       <c r="AC28" s="9"/>
@@ -3923,16 +3927,16 @@
         <v>6000001</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="F29" s="9"/>
       <c r="G29" s="9"/>
       <c r="H29" s="9"/>
       <c r="I29" s="22" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="J29" s="8"/>
       <c r="K29" s="8">
@@ -3942,7 +3946,7 @@
         <v>2000006</v>
       </c>
       <c r="M29" s="16" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="N29" s="13">
         <v>1</v>
@@ -3960,16 +3964,16 @@
         <v>1</v>
       </c>
       <c r="S29" s="9" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="T29" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="U29" s="13">
         <v>12</v>
       </c>
       <c r="V29" s="9" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="W29" s="13">
         <v>100</v>
@@ -3982,7 +3986,7 @@
       </c>
       <c r="Z29" s="13"/>
       <c r="AA29" s="8" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="AB29" s="13"/>
       <c r="AC29" s="9"/>
@@ -3992,7 +3996,7 @@
       <c r="AG29" s="13"/>
       <c r="AH29" s="13"/>
       <c r="AI29" s="20" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="30" spans="2:35" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -4001,16 +4005,16 @@
         <v>6000002</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F30" s="12"/>
       <c r="G30" s="12"/>
       <c r="H30" s="12"/>
       <c r="I30" s="26" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="J30" s="11"/>
       <c r="K30" s="11">
@@ -4038,10 +4042,10 @@
         <v>1</v>
       </c>
       <c r="S30" s="12" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="T30" s="12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="U30" s="18">
         <v>1</v>
@@ -4068,7 +4072,7 @@
       <c r="AG30" s="18"/>
       <c r="AH30" s="18"/>
       <c r="AI30" s="21" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="31" spans="2:35" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -4077,16 +4081,16 @@
         <v>6000003</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F31" s="12"/>
       <c r="G31" s="12"/>
       <c r="H31" s="12"/>
       <c r="I31" s="26" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="J31" s="11"/>
       <c r="K31" s="11">
@@ -4114,10 +4118,10 @@
         <v>1</v>
       </c>
       <c r="S31" s="12" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="T31" s="12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="U31" s="18">
         <v>1</v>
@@ -4142,7 +4146,7 @@
       <c r="AG31" s="18"/>
       <c r="AH31" s="18"/>
       <c r="AI31" s="21" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="32" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -4151,16 +4155,16 @@
         <v>7000001</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F32" s="9"/>
       <c r="G32" s="9"/>
       <c r="H32" s="9"/>
       <c r="I32" s="22" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="J32" s="8"/>
       <c r="K32" s="8">
@@ -4188,10 +4192,10 @@
         <v>1</v>
       </c>
       <c r="S32" s="9" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="T32" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="U32" s="13">
         <v>1</v>
@@ -4208,7 +4212,7 @@
       </c>
       <c r="Z32" s="13"/>
       <c r="AA32" s="8" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="AB32" s="13"/>
       <c r="AC32" s="9"/>
@@ -4225,16 +4229,16 @@
         <v>8000001</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="F33" s="9"/>
       <c r="G33" s="9"/>
       <c r="H33" s="9"/>
       <c r="I33" s="22" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="J33" s="8"/>
       <c r="K33" s="8">
@@ -4262,10 +4266,10 @@
         <v>1</v>
       </c>
       <c r="S33" s="9" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="T33" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="U33" s="13">
         <v>1</v>
@@ -4290,7 +4294,7 @@
       <c r="AG33" s="13"/>
       <c r="AH33" s="13"/>
       <c r="AI33" s="20" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="34" spans="2:35" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -4299,16 +4303,16 @@
         <v>2400001</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="F34" s="9"/>
       <c r="G34" s="9"/>
       <c r="H34" s="9"/>
       <c r="I34" s="22" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="J34" s="8"/>
       <c r="K34" s="8">
@@ -4336,10 +4340,10 @@
         <v>1</v>
       </c>
       <c r="S34" s="9" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="T34" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="U34" s="13">
         <v>1</v>
@@ -4371,16 +4375,16 @@
         <v>2500001</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="F35" s="9"/>
       <c r="G35" s="9"/>
       <c r="H35" s="9"/>
       <c r="I35" s="22" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="J35" s="8"/>
       <c r="K35" s="8">
@@ -4408,10 +4412,10 @@
         <v>1</v>
       </c>
       <c r="S35" s="9" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="T35" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="U35" s="13">
         <v>1</v>
@@ -4428,7 +4432,7 @@
       </c>
       <c r="Z35" s="13"/>
       <c r="AA35" s="8" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="AB35" s="13"/>
       <c r="AC35" s="9"/>
@@ -4444,16 +4448,16 @@
         <v>2600001</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="F36" s="9"/>
       <c r="G36" s="9"/>
       <c r="H36" s="9"/>
       <c r="I36" s="22" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="J36" s="8"/>
       <c r="K36" s="8">
@@ -4481,10 +4485,10 @@
         <v>1</v>
       </c>
       <c r="S36" s="9" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="T36" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="U36" s="13">
         <v>1</v>
@@ -4509,7 +4513,7 @@
       <c r="AG36" s="13"/>
       <c r="AH36" s="13"/>
       <c r="AI36" s="20" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="37" spans="2:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
